--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -672,25 +672,25 @@
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 958 + 종속사 272 + 연결조정 -166</t>
+별도(조선기자재) 961 + 종속사 273 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 1321 + 종속사 358 + 연결조정 -166</t>
+별도(조선기자재) 1325 + 종속사 359 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 979 + 종속사 240 + 연결조정 -166</t>
+별도(조선기자재) 982 + 종속사 241 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 1134 + 종속사 257 + 연결조정 -166</t>
+별도(조선기자재) 1138 + 종속사 257 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
@@ -924,25 +924,25 @@
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2216억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2217억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2358억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2360억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2397억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2400억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2537억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2539억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1770,37 +1770,37 @@
     <comment ref="AH44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87563억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87836억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87134억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87401억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 86401억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 86661억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 85524억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 85778억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 84762억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 84735억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 83550억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 83524억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC45" authorId="0" shapeId="0">
@@ -2139,25 +2139,25 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 958 + 종속사 272 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 961 + 종속사 273 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1321 + 종속사 358 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 1325 + 종속사 359 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 979 + 종속사 240 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 982 + 종속사 241 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1134 + 종속사 257 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 1138 + 종속사 257 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
@@ -2606,25 +2606,25 @@
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2216억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2217억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2358억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2360억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2397억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2400억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2537억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2539억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4262,37 +4262,37 @@
     </comment>
     <comment ref="AH35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87563억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87836억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87134억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87401억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 86401억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 86661억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 85524억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 85778억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 84762억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 84735억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 83550억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 83524억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
@@ -7566,26 +7566,26 @@
         <v>0.192782</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.341808</v>
+        <v>0.342686</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.149618</v>
+        <v>0.153746</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.079011</v>
+        <v>0.082663</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.011426</v>
+        <v>0.014943</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.023626</v>
+        <v>-0.021643</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.039343</v>
+        <v>-0.043127</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.047997</v>
+        <v>-0.051545</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7718,26 +7718,26 @@
         <v>0.06132</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.061322</v>
+        <v>0.061318</v>
       </c>
       <c r="AI22" s="24" t="n">
-        <v>0.061319</v>
+        <v>0.061316</v>
       </c>
       <c r="AJ22" s="25">
         <f>IFERROR(subQ!AJ8/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.06132</v>
+        <v>0.061316</v>
       </c>
       <c r="AL22" s="24" t="n">
-        <v>0.061318</v>
+        <v>0.061316</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.061318</v>
+        <v>0.061321</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.06132</v>
+        <v>0.061321</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -7867,32 +7867,32 @@
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.168534</v>
+        <v>0.168525</v>
       </c>
       <c r="AG23" s="24" t="n">
-        <v>0.168528</v>
+        <v>0.168529</v>
       </c>
       <c r="AH23" s="24" t="n">
+        <v>0.168526</v>
+      </c>
+      <c r="AI23" s="24" t="n">
         <v>0.16853</v>
-      </c>
-      <c r="AI23" s="24" t="n">
-        <v>0.168526</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.16853</v>
+        <v>0.168524</v>
       </c>
       <c r="AL23" s="24" t="n">
-        <v>0.168532</v>
+        <v>0.168528</v>
       </c>
       <c r="AM23" s="24" t="n">
-        <v>0.168533</v>
+        <v>0.168525</v>
       </c>
       <c r="AN23" s="24" t="n">
-        <v>0.168529</v>
+        <v>0.168526</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8157,16 +8157,16 @@
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>-0.99</v>
+        <v>-0.98</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>0.11</v>
+        <v>0.13</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>0.42</v>
+        <v>0.44</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -8609,29 +8609,29 @@
         <v>0.191145</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.191158</v>
+        <v>0.191174</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.19116</v>
+        <v>0.191136</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.191154</v>
+        <v>0.191168</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.191143</v>
+        <v>0.191152</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.191168</v>
+        <v>0.191173</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.191136</v>
+        <v>0.19118</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.191153</v>
+        <v>0.191167</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8764,29 +8764,29 @@
         <v>0.821766</v>
       </c>
       <c r="AG29" s="24" t="n">
-        <v>0.82172</v>
+        <v>0.821777</v>
       </c>
       <c r="AH29" s="24" t="n">
-        <v>0.821761</v>
+        <v>0.821722</v>
       </c>
       <c r="AI29" s="24" t="n">
-        <v>0.8217370000000001</v>
+        <v>0.82176</v>
       </c>
       <c r="AJ29" s="25">
         <f>IFERROR(subQ!AJ17/subQ!AJ16,"")</f>
         <v/>
       </c>
       <c r="AK29" s="24" t="n">
-        <v>0.821789</v>
+        <v>0.8217950000000001</v>
       </c>
       <c r="AL29" s="24" t="n">
-        <v>0.821779</v>
+        <v>0.821791</v>
       </c>
       <c r="AM29" s="24" t="n">
-        <v>0.8217179999999999</v>
+        <v>0.82181</v>
       </c>
       <c r="AN29" s="24" t="n">
-        <v>0.821754</v>
+        <v>0.821751</v>
       </c>
       <c r="AO29" s="25">
         <f>IFERROR(subQ!AO17/subQ!AO16,"")</f>
@@ -9135,7 +9135,7 @@
       </c>
       <c r="AJ32" s="30" t="n"/>
       <c r="AK32" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AL32" s="29" t="n">
         <v>127.91</v>
@@ -9144,7 +9144,7 @@
         <v>0</v>
       </c>
       <c r="AN32" s="29" t="n">
-        <v>0.01</v>
+        <v>-0.01</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -9253,26 +9253,26 @@
         <v>0</v>
       </c>
       <c r="AG33" s="29" t="n">
-        <v>127.91</v>
+        <v>127.92</v>
       </c>
       <c r="AH33" s="29" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AI33" s="29" t="n">
         <v>-0.01</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
-        <v>-0</v>
+        <v>0.01</v>
       </c>
       <c r="AL33" s="29" t="n">
-        <v>127.92</v>
+        <v>127.91</v>
       </c>
       <c r="AM33" s="29" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AN33" s="29" t="n">
         <v>-0.01</v>
-      </c>
-      <c r="AN33" s="29" t="n">
-        <v>0</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -9509,26 +9509,26 @@
         <v>-0.116686</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>-0.038228</v>
+        <v>-0.038334</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>-0.141599</v>
+        <v>-0.142133</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>-0.237074</v>
+        <v>-0.238073</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>-0.217191</v>
+        <v>-0.218413</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>-0.07613200000000001</v>
+        <v>-0.07728500000000001</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>-0.293913</v>
+        <v>-0.29528</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>-0.588842</v>
+        <v>-0.592675</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9637,26 +9637,26 @@
         <v>0.08140600000000001</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.021784</v>
+        <v>0.021844</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.075951</v>
+        <v>0.07623000000000001</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.101451</v>
+        <v>0.101766</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.06438099999999999</v>
+        <v>0.064568</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.016592</v>
+        <v>0.016774</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.058232</v>
+        <v>0.058159</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.077837</v>
+        <v>0.077748</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -10295,26 +10295,26 @@
         <v>-0.486166</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.266043</v>
+        <v>-0.266711</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>0.283293</v>
+        <v>0.280872</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>0.041456</v>
+        <v>0.039434</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.017308</v>
+        <v>-0.020192</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.06830600000000001</v>
+        <v>-0.070191</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.031132</v>
+        <v>-0.031191</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0.006796</v>
+        <v>0.007782</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -10424,7 +10424,7 @@
       </c>
       <c r="AJ43" s="25" t="n"/>
       <c r="AK43" s="24" t="n">
-        <v>-0.123077</v>
+        <v>-0.128205</v>
       </c>
       <c r="AL43" s="24" t="n">
         <v>-0.128205</v>
@@ -10563,29 +10563,29 @@
         <v>0.925179</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.920889</v>
+        <v>0.92028</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.9007270000000001</v>
+        <v>0.900304</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.873535</v>
+        <v>0.87325</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.930271</v>
+        <v>0.929841</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.925922</v>
+        <v>0.9261779999999999</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>0.9076109999999999</v>
+        <v>0.907666</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>0.8798319999999999</v>
+        <v>0.879866</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO5,"")</f>
@@ -10718,29 +10718,29 @@
         <v>0.157267</v>
       </c>
       <c r="AG45" s="24" t="n">
-        <v>0.157272</v>
+        <v>0.157274</v>
       </c>
       <c r="AH45" s="24" t="n">
-        <v>0.157265</v>
+        <v>0.157264</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.157269</v>
+        <v>0.157273</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.157274</v>
+        <v>0.15727</v>
       </c>
       <c r="AL45" s="24" t="n">
-        <v>0.157266</v>
+        <v>0.157268</v>
       </c>
       <c r="AM45" s="24" t="n">
-        <v>0.157267</v>
+        <v>0.157271</v>
       </c>
       <c r="AN45" s="24" t="n">
-        <v>0.157267</v>
+        <v>0.15727</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -10873,29 +10873,29 @@
         <v>0.234745</v>
       </c>
       <c r="AG46" s="24" t="n">
-        <v>0.211762</v>
+        <v>0.212285</v>
       </c>
       <c r="AH46" s="24" t="n">
-        <v>0.255732</v>
+        <v>0.255595</v>
       </c>
       <c r="AI46" s="24" t="n">
-        <v>0.236488</v>
+        <v>0.236402</v>
       </c>
       <c r="AJ46" s="25">
         <f>IFERROR(subQ!AJ37/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK46" s="24" t="n">
-        <v>0.227846</v>
+        <v>0.227728</v>
       </c>
       <c r="AL46" s="24" t="n">
-        <v>0.209947</v>
+        <v>0.209319</v>
       </c>
       <c r="AM46" s="24" t="n">
-        <v>0.255245</v>
+        <v>0.255259</v>
       </c>
       <c r="AN46" s="24" t="n">
-        <v>0.235738</v>
+        <v>0.235745</v>
       </c>
       <c r="AO46" s="25">
         <f>IFERROR(subQ!AO37/subQ!AO5,"")</f>
@@ -11028,29 +11028,29 @@
         <v>0.188718</v>
       </c>
       <c r="AG47" s="24" t="n">
-        <v>0.18858</v>
+        <v>0.188593</v>
       </c>
       <c r="AH47" s="24" t="n">
-        <v>0.188141</v>
+        <v>0.188155</v>
       </c>
       <c r="AI47" s="24" t="n">
-        <v>0.188197</v>
+        <v>0.188216</v>
       </c>
       <c r="AJ47" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ37,"")</f>
         <v/>
       </c>
       <c r="AK47" s="24" t="n">
-        <v>0.188733</v>
+        <v>0.188716</v>
       </c>
       <c r="AL47" s="24" t="n">
-        <v>0.188591</v>
+        <v>0.188572</v>
       </c>
       <c r="AM47" s="24" t="n">
-        <v>0.188169</v>
+        <v>0.18815</v>
       </c>
       <c r="AN47" s="24" t="n">
-        <v>0.188211</v>
+        <v>0.188213</v>
       </c>
       <c r="AO47" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO37,"")</f>
@@ -11183,29 +11183,29 @@
         <v>-0.159924</v>
       </c>
       <c r="AG48" s="24" t="n">
-        <v>-0.132651</v>
+        <v>-0.132564</v>
       </c>
       <c r="AH48" s="24" t="n">
-        <v>-0.156449</v>
+        <v>-0.15589</v>
       </c>
       <c r="AI48" s="24" t="n">
-        <v>-0.110023</v>
+        <v>-0.109652</v>
       </c>
       <c r="AJ48" s="25">
         <f>IFERROR(subQ!AJ39/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK48" s="24" t="n">
-        <v>-0.158117</v>
+        <v>-0.157569</v>
       </c>
       <c r="AL48" s="24" t="n">
-        <v>-0.135861</v>
+        <v>-0.135497</v>
       </c>
       <c r="AM48" s="24" t="n">
-        <v>-0.162857</v>
+        <v>-0.162916</v>
       </c>
       <c r="AN48" s="24" t="n">
-        <v>-0.11557</v>
+        <v>-0.115611</v>
       </c>
       <c r="AO48" s="25">
         <f>IFERROR(subQ!AO39/subQ!AO5,"")</f>
@@ -11338,29 +11338,29 @@
         <v>0.133037</v>
       </c>
       <c r="AG49" s="24" t="n">
-        <v>0.122341</v>
+        <v>0.122521</v>
       </c>
       <c r="AH49" s="24" t="n">
-        <v>0.135741</v>
+        <v>0.135681</v>
       </c>
       <c r="AI49" s="24" t="n">
-        <v>0.12138</v>
+        <v>0.12132</v>
       </c>
       <c r="AJ49" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK49" s="24" t="n">
-        <v>0.131414</v>
+        <v>0.131234</v>
       </c>
       <c r="AL49" s="24" t="n">
-        <v>0.122822</v>
+        <v>0.122521</v>
       </c>
       <c r="AM49" s="24" t="n">
-        <v>0.136582</v>
+        <v>0.136522</v>
       </c>
       <c r="AN49" s="24" t="n">
-        <v>0.122942</v>
+        <v>0.123002</v>
       </c>
       <c r="AO49" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO39,"")</f>
@@ -44233,7 +44233,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>883.8</v>
+        <v>884</v>
       </c>
     </row>
     <row r="30">
@@ -44253,7 +44253,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.98</v>
+        <v>10.97</v>
       </c>
     </row>
     <row r="32">
@@ -44273,7 +44273,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2045</v>
+        <v>0.2046</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -21,7 +21,7 @@
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
     <definedName name="환율">변수!$C$6:$AO$13</definedName>
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
-    <definedName name="BS연결">BS연결!$C$5:$AO$100</definedName>
+    <definedName name="BS연결">BS연결!$C$5:$AO$109</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
     <definedName name="BS별도">BS별도!$C$5:$AO$95</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
@@ -654,55 +654,55 @@
     <comment ref="AD21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 1217 + 종속사 352 + 연결조정 -166</t>
+별도(조선기자재) 1217 + 종속사 353 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AF21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 963 + 종속사 244 + 연결조정 -166</t>
+별도(조선기자재) 967 + 종속사 249 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AG21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 1155 + 종속사 266 + 연결조정 -166</t>
+별도(조선기자재) 1176 + 종속사 279 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AH21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 961 + 종속사 273 + 연결조정 -166</t>
+별도(조선기자재) 1007 + 종속사 299 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AI21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 1325 + 종속사 359 + 연결조정 -166</t>
+별도(조선기자재) 1454 + 종속사 418 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AK21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 982 + 종속사 241 + 연결조정 -166</t>
+별도(조선기자재) 1145 + 종속사 300 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AL21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 1138 + 종속사 257 + 연결조정 -166</t>
+별도(조선기자재) 1420 + 종속사 345 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AM21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 927 + 종속사 261 + 연결조정 -166</t>
+별도(조선기자재) 1243 + 종속사 375 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AN21" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 전년동기 − 1
-별도(조선기자재) 1267 + 종속사 339 + 연결조정 -166</t>
+별도(조선기자재) 1820 + 종속사 521 + 연결조정 -166</t>
       </text>
     </comment>
     <comment ref="AC22" authorId="0" shapeId="0">
@@ -906,43 +906,43 @@
     <comment ref="AG25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1830억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1831억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AH25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 1870억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 1876억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AI25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2012억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2028억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AK25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2217억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2258억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AL25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2360억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2432억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AM25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2400억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2523억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AN25" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): 모델 v 그대로
-이자손익 = 이자발생자산 2539억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
+이자손익 = 이자발생자산 2722억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정</t>
       </text>
     </comment>
     <comment ref="AC26" authorId="0" shapeId="0">
@@ -1758,49 +1758,49 @@
     <comment ref="AF44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 84957억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 85287억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AG44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87118억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 88687억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AH44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87836억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 92009억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AI44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87401억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 95873억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AK44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 86661억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 101010억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AL44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 85778억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 107090억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AM44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 84735억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 113604억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AN44" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출액
-weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 83524억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
+weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 120051억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)</t>
       </text>
     </comment>
     <comment ref="AC45" authorId="0" shapeId="0">
@@ -2121,55 +2121,55 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1217 + 종속사 352 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 1217 + 종속사 353 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 963 + 종속사 244 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 967 + 종속사 249 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1155 + 종속사 266 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 1176 + 종속사 279 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 961 + 종속사 273 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 1007 + 종속사 299 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1325 + 종속사 359 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 1454 + 종속사 418 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 982 + 종속사 241 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 1145 + 종속사 300 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1138 + 종속사 257 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 1420 + 종속사 345 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 927 + 종속사 261 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 1243 + 종속사 375 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1267 + 종속사 339 + 연결조정 -166
+        <t>추정: 별도(조선기자재) 1820 + 종속사 521 + 연결조정 -166
 [yoy]</t>
       </text>
     </comment>
@@ -2588,43 +2588,43 @@
     </comment>
     <comment ref="AG11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1830억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1831억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AH11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 1870억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 1876억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AI11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2012억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2028억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AK11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2217억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2258억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AL11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2360억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2432억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AM11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2400억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2523억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
     <comment ref="AN11" authorId="0" shapeId="0">
       <text>
-        <t>추정: 이자손익 = 이자발생자산 2539억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
+        <t>추정: 이자손익 = 이자발생자산 2722억 × 3.10% − 총차입금 2508억 × 2.90% (연율, CF 실측) ÷ 4; 환·평가손익 0 가정
 [abs]</t>
       </text>
     </comment>
@@ -4250,49 +4250,49 @@
     </comment>
     <comment ref="AF35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 84957억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 85287억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87118억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 88687억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AH35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87836억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 92009억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AI35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 87401억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 95873억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AK35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 86661억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 101010억 × 비례계수 0.0507 × 계절비중 Q1 0.224(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 85778억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 107090억 × 비례계수 0.0507 × 계절비중 Q2 0.262(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 84735억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 113604억 × 비례계수 0.0507 × 계절비중 Q3 0.216(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN35" authorId="0" shapeId="0">
       <text>
-        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 83524억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
+        <t>추정: weighted 고객 매출(ref_base: HD현대미포 0.82 · HD현대중공업 0.18, t−1, 4분기 이동합, 창 8분기, r=0.91) — 레퍼런스 `연간예상` 방식을 격자 탐색으로 일반화; 010620(HD현대미포) fin 은 2025Q3 까지(2025Q4 329180 에 흡수합병, 이후 보고서 없음) → 2025Q4 부터 010620 비중 0.818 은 329180(HD현대중공업) 모델 매출 × 체인링크 k=0.334 로 대체(k = 합병 전 4분기 [w·010620 + w·329180 매출] ÷ 두 회사 매출 합). 미래 고객 매출은 assets/models/329180.json 추정(kind estimate) 을 쓴다 — 고객지수 4분기 이동합(t−1) 120051억 × 비례계수 0.0507 × 계절비중 Q4 0.299(계절비중 — 최근 3개 연도(2026, 2025, 2024) 분기/연간 비중 평균; 격자 lag0~4×창8/12/19×수준·YoY·4Q합 중 최대 r=0.91, n=8, 창 8)
 [ratio]</t>
       </text>
     </comment>
@@ -5380,7 +5380,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-09-30</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.7, "op_wape_pct": 52.6, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식", "detail": [{"q": "2025Q3", "rev_pred": 786.34, "rev_act": 903.68, "op_pred": 73.77, "op_act": 121.44}, {"q": "2025Q4", "rev_pred": 1188.52, "rev_act": 1156.51, "op_pred": 111.51, "op_act": 346.8}, {"q": "2026Q1", "rev_pred": 1054.55, "rev_act": 872.43, "op_pred": 98.94, "op_act": 136.39}, {"q": "2026Q2", "rev_pred": 1057.51, "rev_act": 934.98, "op_pred": 99.22, "op_act": 203.68}]}</t>
+          <t>백테스트: {"freeze": "2025Q2", "horizon": 4, "revenue_wape_pct": 11.7, "op_wape_pct": 52.6, "n": 4, "note": "단일 회사 4분기 — 통계 아님", "driver_at_freeze": "trend_seasonal", "selection_oos_at_freeze": {"wape_link": null, "wape_trend": null, "adopted": false, "note": "유의성 조건 미달 → OOS 비교 전 기각"}, "frozen_inputs": "fin(연결/별도)·고객 조선사 모델·지주 자회사 모델은 2025Q2 까지의 분기만; 선표는 체결일 ≤ 2025Q2 말일 계약(원장 최신 금액·코호트 등급, 환산 없음); 잔고는 yards_cache 2025Q2; 시세·환율 forward·prices·forecast_panel 신규수주 미사용. 고객 가중치(suppliers.json 언급 비중)와 합병 체인링크는 현재 지식; 고객 연동 채택은 동결 모델 안에서도 자기 la−4분기 OOS 규칙(selection_oos_at_freeze)", "detail": [{"q": "2025Q3", "rev_pred": 786.34, "rev_act": 903.68, "op_pred": 73.77, "op_act": 121.44}, {"q": "2025Q4", "rev_pred": 1188.52, "rev_act": 1156.51, "op_pred": 111.51, "op_act": 346.8}, {"q": "2026Q1", "rev_pred": 1054.55, "rev_act": 872.43, "op_pred": 98.94, "op_act": 136.39}, {"q": "2026Q2", "rev_pred": 1057.51, "rev_act": 934.98, "op_pred": 99.22, "op_act": 203.68}]}</t>
         </is>
       </c>
     </row>
@@ -7559,33 +7559,33 @@
         <v>0.023918</v>
       </c>
       <c r="AD21" s="24" t="n">
-        <v>0.212116</v>
+        <v>0.213301</v>
       </c>
       <c r="AE21" s="25" t="n"/>
       <c r="AF21" s="24" t="n">
-        <v>0.192782</v>
+        <v>0.202101</v>
       </c>
       <c r="AG21" s="24" t="n">
-        <v>0.342686</v>
+        <v>0.378483</v>
       </c>
       <c r="AH21" s="24" t="n">
-        <v>0.153746</v>
+        <v>0.231679</v>
       </c>
       <c r="AI21" s="24" t="n">
-        <v>0.082663</v>
+        <v>0.2155</v>
       </c>
       <c r="AJ21" s="25" t="n"/>
       <c r="AK21" s="24" t="n">
-        <v>0.014943</v>
+        <v>0.219108</v>
       </c>
       <c r="AL21" s="24" t="n">
-        <v>-0.021643</v>
+        <v>0.240197</v>
       </c>
       <c r="AM21" s="24" t="n">
-        <v>-0.043127</v>
+        <v>0.273564</v>
       </c>
       <c r="AN21" s="24" t="n">
-        <v>-0.051545</v>
+        <v>0.275049</v>
       </c>
       <c r="AO21" s="25" t="n"/>
     </row>
@@ -7705,20 +7705,20 @@
         <v>0.061321</v>
       </c>
       <c r="AD22" s="24" t="n">
-        <v>0.06132</v>
+        <v>0.061317</v>
       </c>
       <c r="AE22" s="25">
         <f>IFERROR(subQ!AE8/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF22" s="24" t="n">
-        <v>0.061319</v>
+        <v>0.061321</v>
       </c>
       <c r="AG22" s="24" t="n">
-        <v>0.06132</v>
+        <v>0.061318</v>
       </c>
       <c r="AH22" s="24" t="n">
-        <v>0.061318</v>
+        <v>0.061317</v>
       </c>
       <c r="AI22" s="24" t="n">
         <v>0.061316</v>
@@ -7728,16 +7728,16 @@
         <v/>
       </c>
       <c r="AK22" s="24" t="n">
-        <v>0.061316</v>
+        <v>0.06132</v>
       </c>
       <c r="AL22" s="24" t="n">
         <v>0.061316</v>
       </c>
       <c r="AM22" s="24" t="n">
-        <v>0.061321</v>
+        <v>0.061319</v>
       </c>
       <c r="AN22" s="24" t="n">
-        <v>0.061321</v>
+        <v>0.061319</v>
       </c>
       <c r="AO22" s="25">
         <f>IFERROR(subQ!AO8/subQ!AO5,"")</f>
@@ -7860,39 +7860,39 @@
         <v>0.168531</v>
       </c>
       <c r="AD23" s="24" t="n">
-        <v>0.16853</v>
+        <v>0.168529</v>
       </c>
       <c r="AE23" s="25">
         <f>IFERROR(subQ!AE9/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF23" s="24" t="n">
-        <v>0.168525</v>
+        <v>0.168534</v>
       </c>
       <c r="AG23" s="24" t="n">
         <v>0.168529</v>
       </c>
       <c r="AH23" s="24" t="n">
-        <v>0.168526</v>
+        <v>0.168533</v>
       </c>
       <c r="AI23" s="24" t="n">
-        <v>0.16853</v>
+        <v>0.168528</v>
       </c>
       <c r="AJ23" s="25">
         <f>IFERROR(subQ!AJ9/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK23" s="24" t="n">
-        <v>0.168524</v>
+        <v>0.168528</v>
       </c>
       <c r="AL23" s="24" t="n">
+        <v>0.168527</v>
+      </c>
+      <c r="AM23" s="24" t="n">
+        <v>0.16853</v>
+      </c>
+      <c r="AN23" s="24" t="n">
         <v>0.168528</v>
-      </c>
-      <c r="AM23" s="24" t="n">
-        <v>0.168525</v>
-      </c>
-      <c r="AN23" s="24" t="n">
-        <v>0.168526</v>
       </c>
       <c r="AO23" s="25">
         <f>IFERROR(subQ!AO9/subQ!AO5,"")</f>
@@ -8144,29 +8144,29 @@
         <v>-5.05</v>
       </c>
       <c r="AG25" s="29" t="n">
-        <v>-3.98</v>
+        <v>-3.97</v>
       </c>
       <c r="AH25" s="29" t="n">
-        <v>-3.67</v>
+        <v>-3.63</v>
       </c>
       <c r="AI25" s="29" t="n">
-        <v>-2.57</v>
+        <v>-2.45</v>
       </c>
       <c r="AJ25" s="30">
         <f>subQ!AJ11</f>
         <v/>
       </c>
       <c r="AK25" s="29" t="n">
-        <v>-0.98</v>
+        <v>-0.66</v>
       </c>
       <c r="AL25" s="29" t="n">
-        <v>0.13</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="AM25" s="29" t="n">
-        <v>0.44</v>
+        <v>1.39</v>
       </c>
       <c r="AN25" s="29" t="n">
-        <v>1.52</v>
+        <v>2.93</v>
       </c>
       <c r="AO25" s="30">
         <f>subQ!AO11</f>
@@ -8599,39 +8599,39 @@
         <v>0.191137</v>
       </c>
       <c r="AD28" s="24" t="n">
-        <v>0.191137</v>
+        <v>0.191164</v>
       </c>
       <c r="AE28" s="25">
         <f>IFERROR(subQ!AE15/subQ!AE14,"")</f>
         <v/>
       </c>
       <c r="AF28" s="24" t="n">
-        <v>0.191145</v>
+        <v>0.191134</v>
       </c>
       <c r="AG28" s="24" t="n">
-        <v>0.191174</v>
+        <v>0.191173</v>
       </c>
       <c r="AH28" s="24" t="n">
-        <v>0.191136</v>
+        <v>0.191179</v>
       </c>
       <c r="AI28" s="24" t="n">
-        <v>0.191168</v>
+        <v>0.19115</v>
       </c>
       <c r="AJ28" s="25">
         <f>IFERROR(subQ!AJ15/subQ!AJ14,"")</f>
         <v/>
       </c>
       <c r="AK28" s="24" t="n">
-        <v>0.191152</v>
+        <v>0.191172</v>
       </c>
       <c r="AL28" s="24" t="n">
-        <v>0.191173</v>
+        <v>0.191157</v>
       </c>
       <c r="AM28" s="24" t="n">
-        <v>0.19118</v>
+        <v>0.191162</v>
       </c>
       <c r="AN28" s="24" t="n">
-        <v>0.191167</v>
+        <v>0.191148</v>
       </c>
       <c r="AO28" s="25">
         <f>IFERROR(subQ!AO15/subQ!AO14,"")</f>
@@ -8754,39 +8754,39 @@
         <v>0.821732</v>
       </c>
       <c r="AD29" s="24" t="n">
-        <v>0.821753</v>
+        <v>0.821774</v>
       </c>
       <c r="AE29" s="25">
         <f>IFERROR(subQ!AE17/subQ!AE16,"")</f>
         <v/>
       </c>
       <c r="AF29" s="24" t="n">
-        <v>0.821766</v>
+        <v>0.82175</v>
       </c>
       <c r="AG29" s="24" t="n">
-        <v>0.821777</v>
+        <v>0.8217449999999999</v>
       </c>
       <c r="AH29" s="24" t="n">
-        <v>0.821722</v>
+        <v>0.821773</v>
       </c>
       <c r="AI29" s="24" t="n">
-        <v>0.82176</v>
+        <v>0.821771</v>
       </c>
       <c r="AJ29" s="25">
         <f>IFERROR(subQ!AJ17/subQ!AJ16,"")</f>
         <v/>
       </c>
       <c r="AK29" s="24" t="n">
-        <v>0.8217950000000001</v>
+        <v>0.821782</v>
       </c>
       <c r="AL29" s="24" t="n">
-        <v>0.821791</v>
+        <v>0.821765</v>
       </c>
       <c r="AM29" s="24" t="n">
-        <v>0.82181</v>
+        <v>0.821764</v>
       </c>
       <c r="AN29" s="24" t="n">
-        <v>0.821751</v>
+        <v>0.821748</v>
       </c>
       <c r="AO29" s="25">
         <f>IFERROR(subQ!AO17/subQ!AO16,"")</f>
@@ -9141,10 +9141,10 @@
         <v>127.91</v>
       </c>
       <c r="AM32" s="29" t="n">
+        <v>-0</v>
+      </c>
+      <c r="AN32" s="29" t="n">
         <v>0</v>
-      </c>
-      <c r="AN32" s="29" t="n">
-        <v>-0.01</v>
       </c>
       <c r="AO32" s="30" t="n"/>
     </row>
@@ -9246,33 +9246,33 @@
         <v>-0.0077</v>
       </c>
       <c r="AD33" s="29" t="n">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AE33" s="30" t="n"/>
       <c r="AF33" s="29" t="n">
         <v>0</v>
       </c>
       <c r="AG33" s="29" t="n">
-        <v>127.92</v>
+        <v>127.91</v>
       </c>
       <c r="AH33" s="29" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="AI33" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AJ33" s="30" t="n"/>
       <c r="AK33" s="29" t="n">
-        <v>0.01</v>
+        <v>-0</v>
       </c>
       <c r="AL33" s="29" t="n">
-        <v>127.91</v>
+        <v>127.92</v>
       </c>
       <c r="AM33" s="29" t="n">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AN33" s="29" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="AO33" s="30" t="n"/>
     </row>
@@ -9502,33 +9502,33 @@
         <v>-0.080803</v>
       </c>
       <c r="AD35" s="24" t="n">
-        <v>-0.136001</v>
+        <v>-0.13614</v>
       </c>
       <c r="AE35" s="25" t="n"/>
       <c r="AF35" s="24" t="n">
-        <v>-0.116686</v>
+        <v>-0.117646</v>
       </c>
       <c r="AG35" s="24" t="n">
-        <v>-0.038334</v>
+        <v>-0.04277</v>
       </c>
       <c r="AH35" s="24" t="n">
-        <v>-0.142133</v>
+        <v>-0.152872</v>
       </c>
       <c r="AI35" s="24" t="n">
-        <v>-0.238073</v>
+        <v>-0.272944</v>
       </c>
       <c r="AJ35" s="25" t="n"/>
       <c r="AK35" s="24" t="n">
-        <v>-0.218413</v>
+        <v>-0.282945</v>
       </c>
       <c r="AL35" s="24" t="n">
-        <v>-0.07728500000000001</v>
+        <v>-0.205588</v>
       </c>
       <c r="AM35" s="24" t="n">
-        <v>-0.29528</v>
+        <v>-0.568851</v>
       </c>
       <c r="AN35" s="24" t="n">
-        <v>-0.592675</v>
+        <v>-1.981497</v>
       </c>
       <c r="AO35" s="25" t="n"/>
     </row>
@@ -9630,33 +9630,33 @@
         <v>0.086644</v>
       </c>
       <c r="AD36" s="24" t="n">
-        <v>0.123363</v>
+        <v>0.123489</v>
       </c>
       <c r="AE36" s="25" t="n"/>
       <c r="AF36" s="24" t="n">
-        <v>0.08140600000000001</v>
+        <v>0.082052</v>
       </c>
       <c r="AG36" s="24" t="n">
-        <v>0.021844</v>
+        <v>0.024325</v>
       </c>
       <c r="AH36" s="24" t="n">
-        <v>0.07623000000000001</v>
+        <v>0.081249</v>
       </c>
       <c r="AI36" s="24" t="n">
-        <v>0.101766</v>
+        <v>0.113654</v>
       </c>
       <c r="AJ36" s="25" t="n"/>
       <c r="AK36" s="24" t="n">
-        <v>0.064568</v>
+        <v>0.076919</v>
       </c>
       <c r="AL36" s="24" t="n">
-        <v>0.016774</v>
+        <v>0.037213</v>
       </c>
       <c r="AM36" s="24" t="n">
-        <v>0.058159</v>
+        <v>0.078864</v>
       </c>
       <c r="AN36" s="24" t="n">
-        <v>0.077748</v>
+        <v>0.109782</v>
       </c>
       <c r="AO36" s="25" t="n"/>
     </row>
@@ -10288,33 +10288,33 @@
         <v>-0.63354</v>
       </c>
       <c r="AD42" s="24" t="n">
-        <v>-0.549636</v>
+        <v>-0.550091</v>
       </c>
       <c r="AE42" s="25" t="n"/>
       <c r="AF42" s="24" t="n">
-        <v>-0.486166</v>
+        <v>-0.487154</v>
       </c>
       <c r="AG42" s="24" t="n">
-        <v>-0.266711</v>
+        <v>-0.273396</v>
       </c>
       <c r="AH42" s="24" t="n">
-        <v>0.280872</v>
+        <v>0.250605</v>
       </c>
       <c r="AI42" s="24" t="n">
-        <v>0.039434</v>
+        <v>-0.021255</v>
       </c>
       <c r="AJ42" s="25" t="n"/>
       <c r="AK42" s="24" t="n">
-        <v>-0.020192</v>
+        <v>-0.11368</v>
       </c>
       <c r="AL42" s="24" t="n">
-        <v>-0.070191</v>
+        <v>-0.203312</v>
       </c>
       <c r="AM42" s="24" t="n">
-        <v>-0.031191</v>
+        <v>-0.2091</v>
       </c>
       <c r="AN42" s="24" t="n">
-        <v>0.007782</v>
+        <v>-0.220269</v>
       </c>
       <c r="AO42" s="25" t="n"/>
     </row>
@@ -10414,26 +10414,26 @@
         <v>-0.574236</v>
       </c>
       <c r="AG43" s="24" t="n">
-        <v>-0.5</v>
+        <v>-0.502564</v>
       </c>
       <c r="AH43" s="24" t="n">
-        <v>-0.134259</v>
+        <v>-0.138889</v>
       </c>
       <c r="AI43" s="24" t="n">
-        <v>-0.132353</v>
+        <v>-0.142157</v>
       </c>
       <c r="AJ43" s="25" t="n"/>
       <c r="AK43" s="24" t="n">
-        <v>-0.128205</v>
+        <v>-0.14359</v>
       </c>
       <c r="AL43" s="24" t="n">
-        <v>-0.128205</v>
+        <v>-0.149485</v>
       </c>
       <c r="AM43" s="24" t="n">
-        <v>-0.122995</v>
+        <v>-0.155914</v>
       </c>
       <c r="AN43" s="24" t="n">
-        <v>-0.112994</v>
+        <v>-0.16</v>
       </c>
       <c r="AO43" s="25" t="n"/>
     </row>
@@ -10553,39 +10553,39 @@
         <v>0.909196</v>
       </c>
       <c r="AD44" s="24" t="n">
-        <v>0.8678090000000001</v>
+        <v>0.866961</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE35/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF44" s="24" t="n">
-        <v>0.925179</v>
+        <v>0.921573</v>
       </c>
       <c r="AG44" s="24" t="n">
-        <v>0.92028</v>
+        <v>0.912527</v>
       </c>
       <c r="AH44" s="24" t="n">
-        <v>0.900304</v>
+        <v>0.883395</v>
       </c>
       <c r="AI44" s="24" t="n">
-        <v>0.87325</v>
+        <v>0.8523849999999999</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ35/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK44" s="24" t="n">
-        <v>0.929841</v>
+        <v>0.895302</v>
       </c>
       <c r="AL44" s="24" t="n">
-        <v>0.9261779999999999</v>
+        <v>0.888479</v>
       </c>
       <c r="AM44" s="24" t="n">
-        <v>0.907666</v>
+        <v>0.856438</v>
       </c>
       <c r="AN44" s="24" t="n">
-        <v>0.879866</v>
+        <v>0.837105</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO35/subQ!AO5,"")</f>
@@ -10715,32 +10715,32 @@
         <v/>
       </c>
       <c r="AF45" s="24" t="n">
-        <v>0.157267</v>
+        <v>0.157268</v>
       </c>
       <c r="AG45" s="24" t="n">
-        <v>0.157274</v>
+        <v>0.157271</v>
       </c>
       <c r="AH45" s="24" t="n">
-        <v>0.157264</v>
+        <v>0.157265</v>
       </c>
       <c r="AI45" s="24" t="n">
-        <v>0.157273</v>
+        <v>0.157268</v>
       </c>
       <c r="AJ45" s="25">
         <f>IFERROR(subQ!AJ36/subQ!AJ35,"")</f>
         <v/>
       </c>
       <c r="AK45" s="24" t="n">
-        <v>0.15727</v>
+        <v>0.157267</v>
       </c>
       <c r="AL45" s="24" t="n">
+        <v>0.157269</v>
+      </c>
+      <c r="AM45" s="24" t="n">
+        <v>0.157273</v>
+      </c>
+      <c r="AN45" s="24" t="n">
         <v>0.157268</v>
-      </c>
-      <c r="AM45" s="24" t="n">
-        <v>0.157271</v>
-      </c>
-      <c r="AN45" s="24" t="n">
-        <v>0.15727</v>
       </c>
       <c r="AO45" s="25">
         <f>IFERROR(subQ!AO36/subQ!AO35,"")</f>
@@ -10863,39 +10863,39 @@
         <v>0.270672</v>
       </c>
       <c r="AD46" s="24" t="n">
-        <v>0.250908</v>
+        <v>0.251639</v>
       </c>
       <c r="AE46" s="25">
         <f>IFERROR(subQ!AE37/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF46" s="24" t="n">
-        <v>0.234745</v>
+        <v>0.237111</v>
       </c>
       <c r="AG46" s="24" t="n">
-        <v>0.212285</v>
+        <v>0.216595</v>
       </c>
       <c r="AH46" s="24" t="n">
-        <v>0.255595</v>
+        <v>0.262631</v>
       </c>
       <c r="AI46" s="24" t="n">
-        <v>0.236402</v>
+        <v>0.245194</v>
       </c>
       <c r="AJ46" s="25">
         <f>IFERROR(subQ!AJ37/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK46" s="24" t="n">
-        <v>0.227728</v>
+        <v>0.234862</v>
       </c>
       <c r="AL46" s="24" t="n">
-        <v>0.209319</v>
+        <v>0.215635</v>
       </c>
       <c r="AM46" s="24" t="n">
-        <v>0.255259</v>
+        <v>0.258221</v>
       </c>
       <c r="AN46" s="24" t="n">
-        <v>0.235745</v>
+        <v>0.239425</v>
       </c>
       <c r="AO46" s="25">
         <f>IFERROR(subQ!AO37/subQ!AO5,"")</f>
@@ -11018,39 +11018,39 @@
         <v>0.188141</v>
       </c>
       <c r="AD47" s="24" t="n">
-        <v>0.188213</v>
+        <v>0.188219</v>
       </c>
       <c r="AE47" s="25">
         <f>IFERROR(subQ!AE38/subQ!AE37,"")</f>
         <v/>
       </c>
       <c r="AF47" s="24" t="n">
-        <v>0.188718</v>
+        <v>0.188724</v>
       </c>
       <c r="AG47" s="24" t="n">
-        <v>0.188593</v>
+        <v>0.188566</v>
       </c>
       <c r="AH47" s="24" t="n">
-        <v>0.188155</v>
+        <v>0.188133</v>
       </c>
       <c r="AI47" s="24" t="n">
-        <v>0.188216</v>
+        <v>0.188211</v>
       </c>
       <c r="AJ47" s="25">
         <f>IFERROR(subQ!AJ38/subQ!AJ37,"")</f>
         <v/>
       </c>
       <c r="AK47" s="24" t="n">
-        <v>0.188716</v>
+        <v>0.188724</v>
       </c>
       <c r="AL47" s="24" t="n">
-        <v>0.188572</v>
+        <v>0.188581</v>
       </c>
       <c r="AM47" s="24" t="n">
-        <v>0.18815</v>
+        <v>0.188159</v>
       </c>
       <c r="AN47" s="24" t="n">
-        <v>0.188213</v>
+        <v>0.188215</v>
       </c>
       <c r="AO47" s="25">
         <f>IFERROR(subQ!AO38/subQ!AO37,"")</f>
@@ -11173,39 +11173,39 @@
         <v>-0.179857</v>
       </c>
       <c r="AD48" s="24" t="n">
-        <v>-0.118716</v>
+        <v>-0.1186</v>
       </c>
       <c r="AE48" s="25">
         <f>IFERROR(subQ!AE39/subQ!AE5,"")</f>
         <v/>
       </c>
       <c r="AF48" s="24" t="n">
-        <v>-0.159924</v>
+        <v>-0.158684</v>
       </c>
       <c r="AG48" s="24" t="n">
-        <v>-0.132564</v>
+        <v>-0.129122</v>
       </c>
       <c r="AH48" s="24" t="n">
-        <v>-0.15589</v>
+        <v>-0.146026</v>
       </c>
       <c r="AI48" s="24" t="n">
-        <v>-0.109652</v>
+        <v>-0.09757299999999999</v>
       </c>
       <c r="AJ48" s="25">
         <f>IFERROR(subQ!AJ39/subQ!AJ5,"")</f>
         <v/>
       </c>
       <c r="AK48" s="24" t="n">
-        <v>-0.157569</v>
+        <v>-0.130164</v>
       </c>
       <c r="AL48" s="24" t="n">
-        <v>-0.135497</v>
+        <v>-0.104114</v>
       </c>
       <c r="AM48" s="24" t="n">
-        <v>-0.162916</v>
+        <v>-0.114659</v>
       </c>
       <c r="AN48" s="24" t="n">
-        <v>-0.115611</v>
+        <v>-0.076525</v>
       </c>
       <c r="AO48" s="25">
         <f>IFERROR(subQ!AO39/subQ!AO5,"")</f>
@@ -11328,39 +11328,39 @@
         <v>0.141149</v>
       </c>
       <c r="AD49" s="24" t="n">
-        <v>0.127809</v>
+        <v>0.127989</v>
       </c>
       <c r="AE49" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF49" s="24" t="n">
-        <v>0.133037</v>
+        <v>0.133337</v>
       </c>
       <c r="AG49" s="24" t="n">
-        <v>0.122521</v>
+        <v>0.122581</v>
       </c>
       <c r="AH49" s="24" t="n">
         <v>0.135681</v>
       </c>
       <c r="AI49" s="24" t="n">
-        <v>0.12132</v>
+        <v>0.119637</v>
       </c>
       <c r="AJ49" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK49" s="24" t="n">
-        <v>0.131234</v>
+        <v>0.127509</v>
       </c>
       <c r="AL49" s="24" t="n">
-        <v>0.122521</v>
+        <v>0.113989</v>
       </c>
       <c r="AM49" s="24" t="n">
-        <v>0.136522</v>
+        <v>0.12865</v>
       </c>
       <c r="AN49" s="24" t="n">
-        <v>0.123002</v>
+        <v>0.106958</v>
       </c>
       <c r="AO49" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO39,"")</f>
@@ -11855,7 +11855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO100"/>
+  <dimension ref="A1:AO109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -12103,7 +12103,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -14805,16 +14805,16 @@
         <v>144891</v>
       </c>
       <c r="Y31" s="18" t="n">
-        <v>127381</v>
+        <v>47801</v>
       </c>
       <c r="Z31" s="34" t="n">
-        <v>127381</v>
+        <v>47801</v>
       </c>
       <c r="AA31" s="18" t="n">
         <v>132331</v>
       </c>
       <c r="AB31" s="19" t="n">
-        <v>131281</v>
+        <v>45801</v>
       </c>
       <c r="AC31" s="10" t="n"/>
       <c r="AD31" s="10" t="n"/>
@@ -14899,18 +14899,11 @@
       <c r="X32" s="18" t="n">
         <v>144891</v>
       </c>
-      <c r="Y32" s="18" t="n">
-        <v>127381</v>
-      </c>
-      <c r="Z32" s="34" t="n">
-        <v>127381</v>
-      </c>
+      <c r="Z32" s="9" t="n"/>
       <c r="AA32" s="18" t="n">
         <v>132331</v>
       </c>
-      <c r="AB32" s="19" t="n">
-        <v>131281</v>
-      </c>
+      <c r="AB32" s="5" t="n"/>
       <c r="AC32" s="10" t="n"/>
       <c r="AD32" s="10" t="n"/>
       <c r="AE32" s="11" t="n"/>
@@ -15659,18 +15652,11 @@
       <c r="X40" s="18" t="n">
         <v>133500</v>
       </c>
-      <c r="Y40" s="18" t="n">
-        <v>125500</v>
-      </c>
-      <c r="Z40" s="34" t="n">
-        <v>125500</v>
-      </c>
+      <c r="Z40" s="9" t="n"/>
       <c r="AA40" s="18" t="n">
         <v>119500</v>
       </c>
-      <c r="AB40" s="19" t="n">
-        <v>119500</v>
-      </c>
+      <c r="AB40" s="5" t="n"/>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
       <c r="AE40" s="11" t="n"/>
@@ -17440,78 +17426,21 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
-        </is>
-      </c>
-      <c r="E60" s="18" t="n">
-        <v>81901.42</v>
+          <t>유동성장기부채</t>
+        </is>
       </c>
       <c r="F60" s="9" t="n"/>
-      <c r="G60" s="18" t="n">
-        <v>139922.87</v>
-      </c>
-      <c r="H60" s="18" t="n">
-        <v>88872.42999999999</v>
-      </c>
-      <c r="I60" s="18" t="n">
-        <v>79905</v>
-      </c>
-      <c r="J60" s="18" t="n">
-        <v>101190.53</v>
-      </c>
-      <c r="K60" s="34" t="n">
-        <v>409890.83</v>
-      </c>
-      <c r="L60" s="18" t="n">
-        <v>71702.28</v>
-      </c>
-      <c r="M60" s="18" t="n">
-        <v>120491.49</v>
-      </c>
-      <c r="N60" s="18" t="n">
-        <v>81986.97</v>
-      </c>
-      <c r="O60" s="18" t="n">
-        <v>110615.72</v>
-      </c>
-      <c r="P60" s="34" t="n">
-        <v>384796.46</v>
-      </c>
-      <c r="Q60" s="18" t="n">
-        <v>86078.31</v>
-      </c>
-      <c r="R60" s="18" t="n">
-        <v>80837.89</v>
-      </c>
-      <c r="S60" s="18" t="n">
-        <v>74151.66</v>
-      </c>
-      <c r="T60" s="18" t="n">
-        <v>111308.71</v>
-      </c>
-      <c r="U60" s="34" t="n">
-        <v>352376.57</v>
-      </c>
-      <c r="V60" s="18" t="n">
-        <v>98495.97</v>
-      </c>
-      <c r="W60" s="18" t="n">
-        <v>98171.23</v>
-      </c>
-      <c r="X60" s="18" t="n">
-        <v>90367.62</v>
-      </c>
+      <c r="K60" s="9" t="n"/>
+      <c r="P60" s="9" t="n"/>
+      <c r="U60" s="9" t="n"/>
       <c r="Y60" s="18" t="n">
-        <v>115651.44</v>
+        <v>79580</v>
       </c>
       <c r="Z60" s="34" t="n">
-        <v>402686.26</v>
-      </c>
-      <c r="AA60" s="18" t="n">
-        <v>87243.09</v>
+        <v>79580</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>93498.44</v>
+        <v>85480</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -17533,78 +17462,78 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>매출액(수익)</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>86831.55</v>
+        <v>81901.42</v>
       </c>
       <c r="F61" s="9" t="n"/>
       <c r="G61" s="18" t="n">
-        <v>141186.13</v>
+        <v>139922.87</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>70635.39999999999</v>
+        <v>88872.42999999999</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>69460.77</v>
+        <v>79905</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>81216.71000000001</v>
+        <v>101190.53</v>
       </c>
       <c r="K61" s="34" t="n">
-        <v>362499.01</v>
+        <v>409890.83</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>72913.55</v>
+        <v>71702.28</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>93810.07000000001</v>
+        <v>120491.49</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>82334.88</v>
+        <v>81986.97</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>79153.39999999999</v>
+        <v>110615.72</v>
       </c>
       <c r="P61" s="34" t="n">
-        <v>328211.9</v>
+        <v>384796.46</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>76060.99000000001</v>
+        <v>86078.31</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>67462.41</v>
+        <v>80837.89</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>68006.92999999999</v>
+        <v>74151.66</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>82318.69</v>
+        <v>111308.71</v>
       </c>
       <c r="U61" s="34" t="n">
-        <v>293849.02</v>
+        <v>352376.57</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>74721.46000000001</v>
+        <v>98495.97</v>
       </c>
       <c r="W61" s="18" t="n">
-        <v>83099.11</v>
+        <v>98171.23</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>72766.24000000001</v>
+        <v>90367.62</v>
       </c>
       <c r="Y61" s="18" t="n">
-        <v>74138.25</v>
+        <v>115651.44</v>
       </c>
       <c r="Z61" s="34" t="n">
-        <v>304725.06</v>
+        <v>402686.26</v>
       </c>
       <c r="AA61" s="18" t="n">
-        <v>67090.32000000001</v>
+        <v>87243.09</v>
       </c>
       <c r="AB61" s="19" t="n">
-        <v>67311.53</v>
+        <v>93498.44</v>
       </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
@@ -17626,78 +17555,78 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>-4930.13</v>
+        <v>86831.55</v>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="G62" s="18" t="n">
-        <v>-1263.26</v>
+        <v>141186.13</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>18237.04</v>
+        <v>70635.39999999999</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>10444.23</v>
+        <v>69460.77</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>19973.82</v>
+        <v>81216.71000000001</v>
       </c>
       <c r="K62" s="34" t="n">
-        <v>47391.83</v>
+        <v>362499.01</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>-1211.28</v>
+        <v>72913.55</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>26681.42</v>
+        <v>93810.07000000001</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>-347.92</v>
+        <v>82334.88</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>31462.31</v>
+        <v>79153.39999999999</v>
       </c>
       <c r="P62" s="34" t="n">
-        <v>56584.53</v>
+        <v>328211.9</v>
       </c>
       <c r="Q62" s="18" t="n">
-        <v>10017.32</v>
+        <v>76060.99000000001</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>13375.48</v>
+        <v>67462.41</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>6144.73</v>
+        <v>68006.92999999999</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>28990.02</v>
+        <v>82318.69</v>
       </c>
       <c r="U62" s="34" t="n">
-        <v>58527.55</v>
+        <v>293849.02</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>23774.51</v>
+        <v>74721.46000000001</v>
       </c>
       <c r="W62" s="18" t="n">
-        <v>15072.12</v>
+        <v>83099.11</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>17601.38</v>
+        <v>72766.24000000001</v>
       </c>
       <c r="Y62" s="18" t="n">
-        <v>41513.19</v>
+        <v>74138.25</v>
       </c>
       <c r="Z62" s="34" t="n">
-        <v>97961.2</v>
+        <v>304725.06</v>
       </c>
       <c r="AA62" s="18" t="n">
-        <v>20152.77</v>
+        <v>67090.32000000001</v>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>26186.91</v>
+        <v>67311.53</v>
       </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
@@ -17719,78 +17648,78 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>5562.81</v>
+        <v>-4930.13</v>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="18" t="n">
-        <v>5929.56</v>
+        <v>-1263.26</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>6069.34</v>
+        <v>18237.04</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>5843.83</v>
+        <v>10444.23</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>4596.74</v>
+        <v>19973.82</v>
       </c>
       <c r="K63" s="34" t="n">
-        <v>22439.47</v>
+        <v>47391.83</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>5208.53</v>
+        <v>-1211.28</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>5487.14</v>
+        <v>26681.42</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>6299.83</v>
+        <v>-347.92</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>6034.31</v>
+        <v>31462.31</v>
       </c>
       <c r="P63" s="34" t="n">
-        <v>23029.81</v>
+        <v>56584.53</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>5757.97</v>
+        <v>10017.32</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>5424</v>
+        <v>13375.48</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>5506.27</v>
+        <v>6144.73</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>5859.82</v>
+        <v>28990.02</v>
       </c>
       <c r="U63" s="34" t="n">
-        <v>22548.06</v>
+        <v>58527.55</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>5973.64</v>
+        <v>23774.51</v>
       </c>
       <c r="W63" s="18" t="n">
-        <v>6307.66</v>
+        <v>15072.12</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>5457.81</v>
+        <v>17601.38</v>
       </c>
       <c r="Y63" s="18" t="n">
-        <v>6833.45</v>
+        <v>41513.19</v>
       </c>
       <c r="Z63" s="34" t="n">
-        <v>24572.56</v>
+        <v>97961.2</v>
       </c>
       <c r="AA63" s="18" t="n">
-        <v>6513.94</v>
+        <v>20152.77</v>
       </c>
       <c r="AB63" s="19" t="n">
-        <v>5819.28</v>
+        <v>26186.91</v>
       </c>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
@@ -17812,78 +17741,78 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-10492.94</v>
+        <v>5562.81</v>
       </c>
       <c r="F64" s="9" t="n"/>
       <c r="G64" s="18" t="n">
-        <v>-7192.81</v>
+        <v>5929.56</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>12167.69</v>
+        <v>6069.34</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>4600.41</v>
+        <v>5843.83</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>15377.08</v>
+        <v>4596.74</v>
       </c>
       <c r="K64" s="34" t="n">
-        <v>24952.37</v>
+        <v>22439.47</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-6419.81</v>
+        <v>5208.53</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>21194.28</v>
+        <v>5487.14</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>-6647.74</v>
+        <v>6299.83</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>25428</v>
+        <v>6034.31</v>
       </c>
       <c r="P64" s="34" t="n">
-        <v>33554.73</v>
+        <v>23029.81</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>4259.35</v>
+        <v>5757.97</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>7951.48</v>
+        <v>5424</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>638.46</v>
+        <v>5506.27</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>23130.2</v>
+        <v>5859.82</v>
       </c>
       <c r="U64" s="34" t="n">
-        <v>35979.49</v>
+        <v>22548.06</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>17800.87</v>
+        <v>5973.64</v>
       </c>
       <c r="W64" s="18" t="n">
-        <v>8764.459999999999</v>
+        <v>6307.66</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>12143.57</v>
+        <v>5457.81</v>
       </c>
       <c r="Y64" s="18" t="n">
-        <v>34679.73</v>
+        <v>6833.45</v>
       </c>
       <c r="Z64" s="34" t="n">
-        <v>73388.63</v>
+        <v>24572.56</v>
       </c>
       <c r="AA64" s="18" t="n">
-        <v>13638.83</v>
+        <v>6513.94</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>20367.63</v>
+        <v>5819.28</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -17905,78 +17834,78 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
-        <v>-138.22</v>
+        <v>-10492.94</v>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="18" t="n">
-        <v>-13.94</v>
+        <v>-7192.81</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>46.41</v>
+        <v>12167.69</v>
       </c>
       <c r="I65" s="18" t="n">
-        <v>877.05</v>
+        <v>4600.41</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>-1893.11</v>
+        <v>15377.08</v>
       </c>
       <c r="K65" s="34" t="n">
-        <v>-983.59</v>
+        <v>24952.37</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>603.25</v>
+        <v>-6419.81</v>
       </c>
       <c r="M65" s="18" t="n">
-        <v>-877.5</v>
+        <v>21194.28</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>455.5</v>
+        <v>-6647.74</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>1758.04</v>
+        <v>25428</v>
       </c>
       <c r="P65" s="34" t="n">
-        <v>1939.29</v>
+        <v>33554.73</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>110.15</v>
+        <v>4259.35</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>304.78</v>
+        <v>7951.48</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>430.77</v>
+        <v>638.46</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>188.74</v>
+        <v>23130.2</v>
       </c>
       <c r="U65" s="34" t="n">
-        <v>1034.44</v>
+        <v>35979.49</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>305.6</v>
+        <v>17800.87</v>
       </c>
       <c r="W65" s="18" t="n">
-        <v>209.74</v>
+        <v>8764.459999999999</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>166.32</v>
+        <v>12143.57</v>
       </c>
       <c r="Y65" s="18" t="n">
-        <v>319.8</v>
+        <v>34679.73</v>
       </c>
       <c r="Z65" s="34" t="n">
-        <v>1001.46</v>
+        <v>73388.63</v>
       </c>
       <c r="AA65" s="18" t="n">
-        <v>113.32</v>
+        <v>13638.83</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>381.7</v>
+        <v>20367.63</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -17998,78 +17927,78 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>995.98</v>
+        <v>-138.22</v>
       </c>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="18" t="n">
-        <v>111.15</v>
+        <v>-13.94</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>263.07</v>
+        <v>46.41</v>
       </c>
       <c r="I66" s="18" t="n">
-        <v>1023.21</v>
+        <v>877.05</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>37.09</v>
+        <v>-1893.11</v>
       </c>
       <c r="K66" s="34" t="n">
-        <v>1434.52</v>
+        <v>-983.59</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>863.96</v>
+        <v>603.25</v>
       </c>
       <c r="M66" s="18" t="n">
-        <v>-268.84</v>
+        <v>-877.5</v>
       </c>
       <c r="N66" s="18" t="n">
-        <v>488.68</v>
+        <v>455.5</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>1756.02</v>
+        <v>1758.04</v>
       </c>
       <c r="P66" s="34" t="n">
-        <v>2839.82</v>
+        <v>1939.29</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>476.88</v>
+        <v>110.15</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>333.75</v>
+        <v>304.78</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>423.85</v>
+        <v>430.77</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>273.1</v>
+        <v>188.74</v>
       </c>
       <c r="U66" s="34" t="n">
-        <v>1507.58</v>
+        <v>1034.44</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>476.15</v>
+        <v>305.6</v>
       </c>
       <c r="W66" s="18" t="n">
-        <v>320.43</v>
+        <v>209.74</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>194.42</v>
+        <v>166.32</v>
       </c>
       <c r="Y66" s="18" t="n">
-        <v>253.39</v>
+        <v>319.8</v>
       </c>
       <c r="Z66" s="34" t="n">
-        <v>1244.39</v>
+        <v>1001.46</v>
       </c>
       <c r="AA66" s="18" t="n">
-        <v>261.62</v>
+        <v>113.32</v>
       </c>
       <c r="AB66" s="19" t="n">
-        <v>487.29</v>
+        <v>381.7</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -18091,78 +18020,78 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>1134.2</v>
+        <v>995.98</v>
       </c>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="18" t="n">
-        <v>125.09</v>
+        <v>111.15</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>216.66</v>
+        <v>263.07</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>146.17</v>
+        <v>1023.21</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>1930.21</v>
+        <v>37.09</v>
       </c>
       <c r="K67" s="34" t="n">
-        <v>2418.13</v>
+        <v>1434.52</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>260.71</v>
+        <v>863.96</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>608.66</v>
+        <v>-268.84</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>33.17</v>
+        <v>488.68</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-2.03</v>
+        <v>1756.02</v>
       </c>
       <c r="P67" s="34" t="n">
-        <v>900.51</v>
+        <v>2839.82</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>366.73</v>
+        <v>476.88</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>28.97</v>
+        <v>333.75</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>-6.92</v>
+        <v>423.85</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>84.37</v>
+        <v>273.1</v>
       </c>
       <c r="U67" s="34" t="n">
-        <v>473.15</v>
+        <v>1507.58</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>170.55</v>
+        <v>476.15</v>
       </c>
       <c r="W67" s="18" t="n">
-        <v>110.69</v>
+        <v>320.43</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>28.1</v>
+        <v>194.42</v>
       </c>
       <c r="Y67" s="18" t="n">
-        <v>-66.41</v>
+        <v>253.39</v>
       </c>
       <c r="Z67" s="34" t="n">
-        <v>242.93</v>
+        <v>1244.39</v>
       </c>
       <c r="AA67" s="18" t="n">
-        <v>148.3</v>
+        <v>261.62</v>
       </c>
       <c r="AB67" s="19" t="n">
-        <v>105.59</v>
+        <v>487.29</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -18184,78 +18113,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>-622.78</v>
+        <v>1134.2</v>
       </c>
       <c r="F68" s="9" t="n"/>
       <c r="G68" s="18" t="n">
-        <v>-2875.26</v>
+        <v>125.09</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>2001.45</v>
+        <v>216.66</v>
       </c>
       <c r="I68" s="18" t="n">
-        <v>455.01</v>
+        <v>146.17</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>-6405.57</v>
+        <v>1930.21</v>
       </c>
       <c r="K68" s="34" t="n">
-        <v>-6824.37</v>
+        <v>2418.13</v>
       </c>
       <c r="L68" s="18" t="n">
-        <v>-1767.94</v>
+        <v>260.71</v>
       </c>
       <c r="M68" s="18" t="n">
-        <v>-2749.08</v>
+        <v>608.66</v>
       </c>
       <c r="N68" s="18" t="n">
-        <v>-1724.77</v>
+        <v>33.17</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>-2707.67</v>
+        <v>-2.03</v>
       </c>
       <c r="P68" s="34" t="n">
-        <v>-8949.459999999999</v>
+        <v>900.51</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>-1356.24</v>
+        <v>366.73</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>-2509.73</v>
+        <v>28.97</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>-2638.48</v>
+        <v>-6.92</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>-826.9</v>
+        <v>84.37</v>
       </c>
       <c r="U68" s="34" t="n">
-        <v>-7331.35</v>
+        <v>473.15</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>-652.14</v>
+        <v>170.55</v>
       </c>
       <c r="W68" s="18" t="n">
-        <v>-2214.07</v>
+        <v>110.69</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>472.9</v>
+        <v>28.1</v>
       </c>
       <c r="Y68" s="18" t="n">
-        <v>1451.79</v>
+        <v>-66.41</v>
       </c>
       <c r="Z68" s="34" t="n">
-        <v>-941.52</v>
+        <v>242.93</v>
       </c>
       <c r="AA68" s="18" t="n">
-        <v>6732.92</v>
+        <v>148.3</v>
       </c>
       <c r="AB68" s="19" t="n">
-        <v>6121.02</v>
+        <v>105.59</v>
       </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
@@ -18277,78 +18206,78 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>881.61</v>
+        <v>-622.78</v>
       </c>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="18" t="n">
-        <v>1261.8</v>
+        <v>-2875.26</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>2260.37</v>
+        <v>2001.45</v>
       </c>
       <c r="I69" s="18" t="n">
-        <v>2673.51</v>
+        <v>455.01</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>206.25</v>
+        <v>-6405.57</v>
       </c>
       <c r="K69" s="34" t="n">
-        <v>6401.93</v>
+        <v>-6824.37</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>1665.89</v>
+        <v>-1767.94</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>626.16</v>
+        <v>-2749.08</v>
       </c>
       <c r="N69" s="18" t="n">
-        <v>1079.94</v>
+        <v>-1724.77</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>802.35</v>
+        <v>-2707.67</v>
       </c>
       <c r="P69" s="34" t="n">
-        <v>4174.34</v>
+        <v>-8949.459999999999</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>1718.62</v>
+        <v>-1356.24</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>1129.72</v>
+        <v>-2509.73</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>1101.25</v>
+        <v>-2638.48</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>2738.68</v>
+        <v>-826.9</v>
       </c>
       <c r="U69" s="34" t="n">
-        <v>6688.27</v>
+        <v>-7331.35</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>2225.28</v>
+        <v>-652.14</v>
       </c>
       <c r="W69" s="18" t="n">
-        <v>1479.28</v>
+        <v>-2214.07</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>2886.02</v>
+        <v>472.9</v>
       </c>
       <c r="Y69" s="18" t="n">
-        <v>4825.26</v>
+        <v>1451.79</v>
       </c>
       <c r="Z69" s="34" t="n">
-        <v>11415.84</v>
+        <v>-941.52</v>
       </c>
       <c r="AA69" s="18" t="n">
-        <v>10861.67</v>
+        <v>6732.92</v>
       </c>
       <c r="AB69" s="19" t="n">
-        <v>8207.5</v>
+        <v>6121.02</v>
       </c>
       <c r="AC69" s="10" t="n"/>
       <c r="AD69" s="10" t="n"/>
@@ -18370,78 +18299,78 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
-        <v>1504.4</v>
+        <v>881.61</v>
       </c>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="18" t="n">
-        <v>4137.05</v>
+        <v>1261.8</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>258.92</v>
+        <v>2260.37</v>
       </c>
       <c r="I70" s="18" t="n">
-        <v>2218.51</v>
+        <v>2673.51</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>6611.82</v>
+        <v>206.25</v>
       </c>
       <c r="K70" s="34" t="n">
-        <v>13226.3</v>
+        <v>6401.93</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>3433.83</v>
+        <v>1665.89</v>
       </c>
       <c r="M70" s="18" t="n">
-        <v>3375.24</v>
+        <v>626.16</v>
       </c>
       <c r="N70" s="18" t="n">
-        <v>2804.71</v>
+        <v>1079.94</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>3510.02</v>
+        <v>802.35</v>
       </c>
       <c r="P70" s="34" t="n">
-        <v>13123.8</v>
+        <v>4174.34</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>3074.86</v>
+        <v>1718.62</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>3639.45</v>
+        <v>1129.72</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>3739.73</v>
+        <v>1101.25</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>3565.58</v>
+        <v>2738.68</v>
       </c>
       <c r="U70" s="34" t="n">
-        <v>14019.62</v>
+        <v>6688.27</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>2877.42</v>
+        <v>2225.28</v>
       </c>
       <c r="W70" s="18" t="n">
-        <v>3693.35</v>
+        <v>1479.28</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>2413.12</v>
+        <v>2886.02</v>
       </c>
       <c r="Y70" s="18" t="n">
-        <v>3373.47</v>
+        <v>4825.26</v>
       </c>
       <c r="Z70" s="34" t="n">
-        <v>12357.36</v>
+        <v>11415.84</v>
       </c>
       <c r="AA70" s="18" t="n">
-        <v>4128.76</v>
+        <v>10861.67</v>
       </c>
       <c r="AB70" s="19" t="n">
-        <v>2086.48</v>
+        <v>8207.5</v>
       </c>
       <c r="AC70" s="10" t="n"/>
       <c r="AD70" s="10" t="n"/>
@@ -18463,78 +18392,78 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>종속기업,공동지배기업및관계기업관련손익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
-        <v>0</v>
+        <v>1504.4</v>
       </c>
       <c r="F71" s="9" t="n"/>
       <c r="G71" s="18" t="n">
-        <v>0</v>
+        <v>4137.05</v>
       </c>
       <c r="H71" s="18" t="n">
-        <v>0</v>
+        <v>258.92</v>
       </c>
       <c r="I71" s="18" t="n">
-        <v>0</v>
+        <v>2218.51</v>
       </c>
       <c r="J71" s="18" t="n">
-        <v>-574.48</v>
+        <v>6611.82</v>
       </c>
       <c r="K71" s="34" t="n">
-        <v>-574.48</v>
+        <v>13226.3</v>
       </c>
       <c r="L71" s="18" t="n">
-        <v>-17.52</v>
+        <v>3433.83</v>
       </c>
       <c r="M71" s="18" t="n">
-        <v>-240.58</v>
+        <v>3375.24</v>
       </c>
       <c r="N71" s="18" t="n">
-        <v>-135.05</v>
+        <v>2804.71</v>
       </c>
       <c r="O71" s="18" t="n">
-        <v>-325.37</v>
+        <v>3510.02</v>
       </c>
       <c r="P71" s="34" t="n">
-        <v>-718.52</v>
+        <v>13123.8</v>
       </c>
       <c r="Q71" s="18" t="n">
-        <v>-129.75</v>
+        <v>3074.86</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>-124.23</v>
+        <v>3639.45</v>
       </c>
       <c r="S71" s="18" t="n">
-        <v>-134.75</v>
+        <v>3739.73</v>
       </c>
       <c r="T71" s="18" t="n">
-        <v>-246.38</v>
+        <v>3565.58</v>
       </c>
       <c r="U71" s="34" t="n">
-        <v>-635.11</v>
+        <v>14019.62</v>
       </c>
       <c r="V71" s="18" t="n">
-        <v>-100.49</v>
+        <v>2877.42</v>
       </c>
       <c r="W71" s="18" t="n">
-        <v>96.05</v>
+        <v>3693.35</v>
       </c>
       <c r="X71" s="18" t="n">
-        <v>-7.91</v>
+        <v>2413.12</v>
       </c>
       <c r="Y71" s="18" t="n">
-        <v>0.11</v>
+        <v>3373.47</v>
       </c>
       <c r="Z71" s="34" t="n">
-        <v>-12.24</v>
+        <v>12357.36</v>
       </c>
       <c r="AA71" s="18" t="n">
-        <v>13.82</v>
+        <v>4128.76</v>
       </c>
       <c r="AB71" s="19" t="n">
-        <v>-6.39</v>
+        <v>2086.48</v>
       </c>
       <c r="AC71" s="10" t="n"/>
       <c r="AD71" s="10" t="n"/>
@@ -18556,78 +18485,78 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>종속기업,공동지배기업및관계기업관련손익</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-11253.94</v>
+        <v>0</v>
       </c>
       <c r="F72" s="9" t="n"/>
       <c r="G72" s="18" t="n">
-        <v>-10082.01</v>
+        <v>0</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>14215.55</v>
+        <v>0</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>5932.46</v>
+        <v>0</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>6503.91</v>
+        <v>-574.48</v>
       </c>
       <c r="K72" s="34" t="n">
-        <v>16569.91</v>
+        <v>-574.48</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-7602.02</v>
+        <v>-17.52</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>17327.11</v>
+        <v>-240.58</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>-8052.06</v>
+        <v>-135.05</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>24153.01</v>
+        <v>-325.37</v>
       </c>
       <c r="P72" s="34" t="n">
-        <v>25826.04</v>
+        <v>-718.52</v>
       </c>
       <c r="Q72" s="18" t="n">
-        <v>2883.5</v>
+        <v>-129.75</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>5622.3</v>
+        <v>-124.23</v>
       </c>
       <c r="S72" s="18" t="n">
-        <v>-1704</v>
+        <v>-134.75</v>
       </c>
       <c r="T72" s="18" t="n">
-        <v>22245.66</v>
+        <v>-246.38</v>
       </c>
       <c r="U72" s="34" t="n">
-        <v>29047.46</v>
+        <v>-635.11</v>
       </c>
       <c r="V72" s="18" t="n">
-        <v>17353.84</v>
+        <v>-100.49</v>
       </c>
       <c r="W72" s="18" t="n">
-        <v>6856.17</v>
+        <v>96.05</v>
       </c>
       <c r="X72" s="18" t="n">
-        <v>12774.87</v>
+        <v>-7.91</v>
       </c>
       <c r="Y72" s="18" t="n">
-        <v>36451.44</v>
+        <v>0.11</v>
       </c>
       <c r="Z72" s="34" t="n">
-        <v>73436.32000000001</v>
+        <v>-12.24</v>
       </c>
       <c r="AA72" s="18" t="n">
-        <v>20498.88</v>
+        <v>13.82</v>
       </c>
       <c r="AB72" s="19" t="n">
-        <v>26863.97</v>
+        <v>-6.39</v>
       </c>
       <c r="AC72" s="10" t="n"/>
       <c r="AD72" s="10" t="n"/>
@@ -18649,78 +18578,78 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E73" s="18" t="n">
-        <v>-1548.57</v>
+        <v>-11253.94</v>
       </c>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="18" t="n">
-        <v>-1956.87</v>
+        <v>-10082.01</v>
       </c>
       <c r="H73" s="18" t="n">
-        <v>3468.26</v>
+        <v>14215.55</v>
       </c>
       <c r="I73" s="18" t="n">
-        <v>1736.26</v>
+        <v>5932.46</v>
       </c>
       <c r="J73" s="18" t="n">
-        <v>102.19</v>
+        <v>6503.91</v>
       </c>
       <c r="K73" s="34" t="n">
-        <v>3349.84</v>
+        <v>16569.91</v>
       </c>
       <c r="L73" s="18" t="n">
-        <v>-1547.49</v>
+        <v>-7602.02</v>
       </c>
       <c r="M73" s="18" t="n">
-        <v>3858.12</v>
+        <v>17327.11</v>
       </c>
       <c r="N73" s="18" t="n">
-        <v>504</v>
+        <v>-8052.06</v>
       </c>
       <c r="O73" s="18" t="n">
-        <v>-354.56</v>
+        <v>24153.01</v>
       </c>
       <c r="P73" s="34" t="n">
-        <v>2460.07</v>
+        <v>25826.04</v>
       </c>
       <c r="Q73" s="18" t="n">
-        <v>280.17</v>
+        <v>2883.5</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>3886.87</v>
+        <v>5622.3</v>
       </c>
       <c r="S73" s="18" t="n">
-        <v>-583.59</v>
+        <v>-1704</v>
       </c>
       <c r="T73" s="18" t="n">
-        <v>3442.56</v>
+        <v>22245.66</v>
       </c>
       <c r="U73" s="34" t="n">
-        <v>7026.01</v>
+        <v>29047.46</v>
       </c>
       <c r="V73" s="18" t="n">
-        <v>4172.58</v>
+        <v>17353.84</v>
       </c>
       <c r="W73" s="18" t="n">
-        <v>2026.02</v>
+        <v>6856.17</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>2733.58</v>
+        <v>12774.87</v>
       </c>
       <c r="Y73" s="18" t="n">
-        <v>4659.68</v>
+        <v>36451.44</v>
       </c>
       <c r="Z73" s="34" t="n">
-        <v>13591.86</v>
+        <v>73436.32000000001</v>
       </c>
       <c r="AA73" s="18" t="n">
-        <v>4714.27</v>
+        <v>20498.88</v>
       </c>
       <c r="AB73" s="19" t="n">
-        <v>6240.55</v>
+        <v>26863.97</v>
       </c>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
@@ -18742,78 +18671,78 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E74" s="18" t="n">
-        <v>-9705.370000000001</v>
+        <v>-1548.57</v>
       </c>
       <c r="F74" s="9" t="n"/>
       <c r="G74" s="18" t="n">
-        <v>-8125.14</v>
+        <v>-1956.87</v>
       </c>
       <c r="H74" s="18" t="n">
-        <v>10747.3</v>
+        <v>3468.26</v>
       </c>
       <c r="I74" s="18" t="n">
-        <v>4196.2</v>
+        <v>1736.26</v>
       </c>
       <c r="J74" s="18" t="n">
-        <v>6401.72</v>
+        <v>102.19</v>
       </c>
       <c r="K74" s="34" t="n">
-        <v>13220.08</v>
+        <v>3349.84</v>
       </c>
       <c r="L74" s="18" t="n">
-        <v>-6054.53</v>
+        <v>-1547.49</v>
       </c>
       <c r="M74" s="18" t="n">
-        <v>13468.99</v>
+        <v>3858.12</v>
       </c>
       <c r="N74" s="18" t="n">
-        <v>3244.72</v>
+        <v>504</v>
       </c>
       <c r="O74" s="18" t="n">
-        <v>12071.14</v>
+        <v>-354.56</v>
       </c>
       <c r="P74" s="34" t="n">
-        <v>22730.32</v>
+        <v>2460.07</v>
       </c>
       <c r="Q74" s="18" t="n">
-        <v>2603.33</v>
+        <v>280.17</v>
       </c>
       <c r="R74" s="18" t="n">
-        <v>1735.43</v>
+        <v>3886.87</v>
       </c>
       <c r="S74" s="18" t="n">
-        <v>-1120.41</v>
+        <v>-583.59</v>
       </c>
       <c r="T74" s="18" t="n">
-        <v>18803.1</v>
+        <v>3442.56</v>
       </c>
       <c r="U74" s="34" t="n">
-        <v>22021.45</v>
+        <v>7026.01</v>
       </c>
       <c r="V74" s="18" t="n">
-        <v>13181.26</v>
+        <v>4172.58</v>
       </c>
       <c r="W74" s="18" t="n">
-        <v>4830.15</v>
+        <v>2026.02</v>
       </c>
       <c r="X74" s="18" t="n">
-        <v>10041.29</v>
+        <v>2733.58</v>
       </c>
       <c r="Y74" s="18" t="n">
-        <v>31791.76</v>
+        <v>4659.68</v>
       </c>
       <c r="Z74" s="34" t="n">
-        <v>59844.46</v>
+        <v>13591.86</v>
       </c>
       <c r="AA74" s="18" t="n">
-        <v>15784.61</v>
+        <v>4714.27</v>
       </c>
       <c r="AB74" s="19" t="n">
-        <v>20623.42</v>
+        <v>6240.55</v>
       </c>
       <c r="AC74" s="10" t="n"/>
       <c r="AD74" s="10" t="n"/>
@@ -18835,78 +18764,78 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-10998.72</v>
+        <v>-9705.370000000001</v>
       </c>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="18" t="n">
-        <v>-7956.78</v>
+        <v>-8125.14</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>10387.63</v>
+        <v>10747.3</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>3302.81</v>
+        <v>4196.2</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>5857.17</v>
+        <v>6401.72</v>
       </c>
       <c r="K75" s="34" t="n">
-        <v>11590.83</v>
+        <v>13220.08</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-6547.57</v>
+        <v>-6054.53</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>13311.95</v>
+        <v>13468.99</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>3198.49</v>
+        <v>3244.72</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>7158.84</v>
+        <v>12071.14</v>
       </c>
       <c r="P75" s="34" t="n">
-        <v>17121.71</v>
+        <v>22730.32</v>
       </c>
       <c r="Q75" s="18" t="n">
-        <v>2574.74</v>
+        <v>2603.33</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>-3529.64</v>
+        <v>1735.43</v>
       </c>
       <c r="S75" s="18" t="n">
-        <v>-2625.77</v>
+        <v>-1120.41</v>
       </c>
       <c r="T75" s="18" t="n">
-        <v>14931.38</v>
+        <v>18803.1</v>
       </c>
       <c r="U75" s="34" t="n">
-        <v>11350.71</v>
+        <v>22021.45</v>
       </c>
       <c r="V75" s="18" t="n">
-        <v>12994.64</v>
+        <v>13181.26</v>
       </c>
       <c r="W75" s="18" t="n">
-        <v>4278.63</v>
+        <v>4830.15</v>
       </c>
       <c r="X75" s="18" t="n">
-        <v>7185.88</v>
+        <v>10041.29</v>
       </c>
       <c r="Y75" s="18" t="n">
-        <v>26221.8</v>
+        <v>31791.76</v>
       </c>
       <c r="Z75" s="34" t="n">
-        <v>50680.95</v>
+        <v>59844.46</v>
       </c>
       <c r="AA75" s="18" t="n">
-        <v>14098.17</v>
+        <v>15784.61</v>
       </c>
       <c r="AB75" s="19" t="n">
-        <v>16542.49</v>
+        <v>20623.42</v>
       </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
@@ -18928,78 +18857,78 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>(비지배주주지분)당기순이익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E76" s="18" t="n">
-        <v>1293.34</v>
+        <v>-10998.72</v>
       </c>
       <c r="F76" s="9" t="n"/>
       <c r="G76" s="18" t="n">
-        <v>-168.36</v>
+        <v>-7956.78</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>359.66</v>
+        <v>10387.63</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>893.4</v>
+        <v>3302.81</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>544.55</v>
+        <v>5857.17</v>
       </c>
       <c r="K76" s="34" t="n">
-        <v>1629.25</v>
+        <v>11590.83</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>493.04</v>
+        <v>-6547.57</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>157.04</v>
+        <v>13311.95</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>46.23</v>
+        <v>3198.49</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>4912.3</v>
+        <v>7158.84</v>
       </c>
       <c r="P76" s="34" t="n">
-        <v>5608.61</v>
+        <v>17121.71</v>
       </c>
       <c r="Q76" s="18" t="n">
-        <v>28.6</v>
+        <v>2574.74</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>5265.07</v>
+        <v>-3529.64</v>
       </c>
       <c r="S76" s="18" t="n">
-        <v>1505.36</v>
+        <v>-2625.77</v>
       </c>
       <c r="T76" s="18" t="n">
-        <v>3871.72</v>
+        <v>14931.38</v>
       </c>
       <c r="U76" s="34" t="n">
-        <v>10670.75</v>
+        <v>11350.71</v>
       </c>
       <c r="V76" s="18" t="n">
-        <v>186.62</v>
+        <v>12994.64</v>
       </c>
       <c r="W76" s="18" t="n">
-        <v>551.53</v>
+        <v>4278.63</v>
       </c>
       <c r="X76" s="18" t="n">
-        <v>2855.41</v>
+        <v>7185.88</v>
       </c>
       <c r="Y76" s="18" t="n">
-        <v>5569.96</v>
+        <v>26221.8</v>
       </c>
       <c r="Z76" s="34" t="n">
-        <v>9163.52</v>
+        <v>50680.95</v>
       </c>
       <c r="AA76" s="18" t="n">
-        <v>1686.45</v>
+        <v>14098.17</v>
       </c>
       <c r="AB76" s="19" t="n">
-        <v>4080.92</v>
+        <v>16542.49</v>
       </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
@@ -19021,78 +18950,78 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>(비지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-9388.65</v>
+        <v>1293.34</v>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="18" t="n">
-        <v>-7555.73</v>
+        <v>-168.36</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>11276.06</v>
+        <v>359.66</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>4614.33</v>
+        <v>893.4</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>5354.24</v>
+        <v>544.55</v>
       </c>
       <c r="K77" s="34" t="n">
-        <v>13688.9</v>
+        <v>1629.25</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-6165.28</v>
+        <v>493.04</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>14750.38</v>
+        <v>157.04</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>3023.56</v>
+        <v>46.23</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>9891.959999999999</v>
+        <v>4912.3</v>
       </c>
       <c r="P77" s="34" t="n">
-        <v>21500.62</v>
+        <v>5608.61</v>
       </c>
       <c r="Q77" s="18" t="n">
-        <v>2599.78</v>
+        <v>28.6</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>1593.8</v>
+        <v>5265.07</v>
       </c>
       <c r="S77" s="18" t="n">
-        <v>-1480.09</v>
+        <v>1505.36</v>
       </c>
       <c r="T77" s="18" t="n">
-        <v>16459.05</v>
+        <v>3871.72</v>
       </c>
       <c r="U77" s="34" t="n">
-        <v>19172.54</v>
+        <v>10670.75</v>
       </c>
       <c r="V77" s="18" t="n">
-        <v>13353.08</v>
+        <v>186.62</v>
       </c>
       <c r="W77" s="18" t="n">
-        <v>5223.93</v>
+        <v>551.53</v>
       </c>
       <c r="X77" s="18" t="n">
-        <v>11287.64</v>
+        <v>2855.41</v>
       </c>
       <c r="Y77" s="18" t="n">
-        <v>31638.3</v>
+        <v>5569.96</v>
       </c>
       <c r="Z77" s="34" t="n">
-        <v>61502.95</v>
+        <v>9163.52</v>
       </c>
       <c r="AA77" s="18" t="n">
-        <v>14737.28</v>
+        <v>1686.45</v>
       </c>
       <c r="AB77" s="19" t="n">
-        <v>20981.81</v>
+        <v>4080.92</v>
       </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -19114,78 +19043,78 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-9705.370000000001</v>
+        <v>-9388.65</v>
       </c>
       <c r="F78" s="9" t="n"/>
       <c r="G78" s="18" t="n">
-        <v>-8125.14</v>
+        <v>-7555.73</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>10747.3</v>
+        <v>11276.06</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>4196.2</v>
+        <v>4614.33</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>6401.72</v>
+        <v>5354.24</v>
       </c>
       <c r="K78" s="34" t="n">
-        <v>13220.08</v>
+        <v>13688.9</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-6054.53</v>
+        <v>-6165.28</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>13468.99</v>
+        <v>14750.38</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-8556.049999999999</v>
+        <v>3023.56</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>24507.57</v>
+        <v>9891.959999999999</v>
       </c>
       <c r="P78" s="34" t="n">
-        <v>23365.98</v>
+        <v>21500.62</v>
       </c>
       <c r="Q78" s="18" t="n">
-        <v>2603.33</v>
+        <v>2599.78</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>1735.43</v>
+        <v>1593.8</v>
       </c>
       <c r="S78" s="18" t="n">
-        <v>-1120.41</v>
+        <v>-1480.09</v>
       </c>
       <c r="T78" s="18" t="n">
-        <v>18803.1</v>
+        <v>16459.05</v>
       </c>
       <c r="U78" s="34" t="n">
-        <v>22021.45</v>
+        <v>19172.54</v>
       </c>
       <c r="V78" s="18" t="n">
-        <v>13181.26</v>
+        <v>13353.08</v>
       </c>
       <c r="W78" s="18" t="n">
-        <v>4830.15</v>
+        <v>5223.93</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>10041.29</v>
+        <v>11287.64</v>
       </c>
       <c r="Y78" s="18" t="n">
-        <v>31791.76</v>
+        <v>31638.3</v>
       </c>
       <c r="Z78" s="34" t="n">
-        <v>59844.46</v>
+        <v>61502.95</v>
       </c>
       <c r="AA78" s="18" t="n">
-        <v>15784.61</v>
+        <v>14737.28</v>
       </c>
       <c r="AB78" s="19" t="n">
-        <v>20623.42</v>
+        <v>20981.81</v>
       </c>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
@@ -19207,27 +19136,79 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>중단사업이익</t>
-        </is>
+          <t>계속사업이익</t>
+        </is>
+      </c>
+      <c r="E79" s="18" t="n">
+        <v>-9705.370000000001</v>
       </c>
       <c r="F79" s="9" t="n"/>
-      <c r="K79" s="9" t="n"/>
+      <c r="G79" s="18" t="n">
+        <v>-8125.14</v>
+      </c>
+      <c r="H79" s="18" t="n">
+        <v>10747.3</v>
+      </c>
+      <c r="I79" s="18" t="n">
+        <v>4196.2</v>
+      </c>
+      <c r="J79" s="18" t="n">
+        <v>6401.72</v>
+      </c>
+      <c r="K79" s="34" t="n">
+        <v>13220.08</v>
+      </c>
+      <c r="L79" s="18" t="n">
+        <v>-6054.53</v>
+      </c>
+      <c r="M79" s="18" t="n">
+        <v>13468.99</v>
+      </c>
       <c r="N79" s="18" t="n">
-        <v>11800.77</v>
+        <v>-8556.049999999999</v>
       </c>
       <c r="O79" s="18" t="n">
-        <v>-12436.42</v>
-      </c>
-      <c r="P79" s="9" t="n"/>
+        <v>24507.57</v>
+      </c>
+      <c r="P79" s="34" t="n">
+        <v>23365.98</v>
+      </c>
+      <c r="Q79" s="18" t="n">
+        <v>2603.33</v>
+      </c>
+      <c r="R79" s="18" t="n">
+        <v>1735.43</v>
+      </c>
       <c r="S79" s="18" t="n">
-        <v>0</v>
+        <v>-1120.41</v>
       </c>
       <c r="T79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U79" s="9" t="n"/>
-      <c r="Z79" s="9" t="n"/>
-      <c r="AB79" s="5" t="n"/>
+        <v>18803.1</v>
+      </c>
+      <c r="U79" s="34" t="n">
+        <v>22021.45</v>
+      </c>
+      <c r="V79" s="18" t="n">
+        <v>13181.26</v>
+      </c>
+      <c r="W79" s="18" t="n">
+        <v>4830.15</v>
+      </c>
+      <c r="X79" s="18" t="n">
+        <v>10041.29</v>
+      </c>
+      <c r="Y79" s="18" t="n">
+        <v>31791.76</v>
+      </c>
+      <c r="Z79" s="34" t="n">
+        <v>59844.46</v>
+      </c>
+      <c r="AA79" s="18" t="n">
+        <v>15784.61</v>
+      </c>
+      <c r="AB79" s="19" t="n">
+        <v>20623.42</v>
+      </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
       <c r="AE79" s="11" t="n"/>
@@ -19248,79 +19229,27 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E80" s="18" t="n">
-        <v>-11105</v>
+          <t>중단사업이익</t>
+        </is>
       </c>
       <c r="F80" s="9" t="n"/>
-      <c r="G80" s="18" t="n">
-        <v>-20116.62</v>
-      </c>
-      <c r="H80" s="18" t="n">
-        <v>7511.35</v>
-      </c>
-      <c r="I80" s="18" t="n">
-        <v>4975.25</v>
-      </c>
-      <c r="J80" s="18" t="n">
-        <v>27161.72</v>
-      </c>
-      <c r="K80" s="34" t="n">
-        <v>19531.7</v>
-      </c>
-      <c r="L80" s="18" t="n">
-        <v>-10890.66</v>
-      </c>
-      <c r="M80" s="18" t="n">
-        <v>43778.46</v>
-      </c>
+      <c r="K80" s="9" t="n"/>
       <c r="N80" s="18" t="n">
-        <v>12798.55</v>
+        <v>11800.77</v>
       </c>
       <c r="O80" s="18" t="n">
-        <v>23379.42</v>
-      </c>
-      <c r="P80" s="34" t="n">
-        <v>69065.77</v>
-      </c>
-      <c r="Q80" s="18" t="n">
-        <v>13245.72</v>
-      </c>
-      <c r="R80" s="18" t="n">
-        <v>6881.57</v>
-      </c>
+        <v>-12436.42</v>
+      </c>
+      <c r="P80" s="9" t="n"/>
       <c r="S80" s="18" t="n">
-        <v>2183.77</v>
+        <v>0</v>
       </c>
       <c r="T80" s="18" t="n">
-        <v>9340.120000000001</v>
-      </c>
-      <c r="U80" s="34" t="n">
-        <v>31651.18</v>
-      </c>
-      <c r="V80" s="18" t="n">
-        <v>-711.8</v>
-      </c>
-      <c r="W80" s="18" t="n">
-        <v>32230.31</v>
-      </c>
-      <c r="X80" s="18" t="n">
-        <v>26686.46</v>
-      </c>
-      <c r="Y80" s="18" t="n">
-        <v>-647.34</v>
-      </c>
-      <c r="Z80" s="34" t="n">
-        <v>57557.63</v>
-      </c>
-      <c r="AA80" s="18" t="n">
-        <v>26339.65</v>
-      </c>
-      <c r="AB80" s="19" t="n">
-        <v>15768.09</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U80" s="9" t="n"/>
+      <c r="Z80" s="9" t="n"/>
+      <c r="AB80" s="5" t="n"/>
       <c r="AC80" s="10" t="n"/>
       <c r="AD80" s="10" t="n"/>
       <c r="AE80" s="11" t="n"/>
@@ -19341,78 +19270,16 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
-        </is>
-      </c>
-      <c r="E81" s="18" t="n">
-        <v>-109.44</v>
+          <t>이자수익</t>
+        </is>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>-5594.55</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>-6715.09</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>-245.73</v>
-      </c>
-      <c r="J81" s="18" t="n">
-        <v>-30.65</v>
-      </c>
-      <c r="K81" s="34" t="n">
-        <v>-12586.02</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>-321.14</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>295.05</v>
-      </c>
-      <c r="N81" s="18" t="n">
-        <v>-1009.87</v>
-      </c>
-      <c r="O81" s="18" t="n">
-        <v>-126.01</v>
-      </c>
-      <c r="P81" s="34" t="n">
-        <v>-1161.97</v>
-      </c>
-      <c r="Q81" s="18" t="n">
-        <v>-4239.15</v>
-      </c>
-      <c r="R81" s="18" t="n">
-        <v>-4477.44</v>
-      </c>
-      <c r="S81" s="18" t="n">
-        <v>-3440.63</v>
-      </c>
-      <c r="T81" s="18" t="n">
-        <v>-262.34</v>
-      </c>
-      <c r="U81" s="34" t="n">
-        <v>-12419.56</v>
-      </c>
-      <c r="V81" s="18" t="n">
-        <v>-3859.35</v>
-      </c>
-      <c r="W81" s="18" t="n">
-        <v>-3818.88</v>
-      </c>
-      <c r="X81" s="18" t="n">
-        <v>-1758.81</v>
-      </c>
-      <c r="Y81" s="18" t="n">
-        <v>-3544.68</v>
-      </c>
-      <c r="Z81" s="34" t="n">
-        <v>-12981.72</v>
-      </c>
-      <c r="AA81" s="18" t="n">
-        <v>-3576.28</v>
-      </c>
+      <c r="K81" s="9" t="n"/>
+      <c r="P81" s="9" t="n"/>
+      <c r="U81" s="9" t="n"/>
+      <c r="Z81" s="9" t="n"/>
       <c r="AB81" s="19" t="n">
-        <v>-4050.64</v>
+        <v>731.79</v>
       </c>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
@@ -19434,78 +19301,16 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E82" s="18" t="n">
-        <v>-2757.98</v>
+          <t>배당금수익</t>
+        </is>
       </c>
       <c r="F82" s="9" t="n"/>
-      <c r="G82" s="18" t="n">
-        <v>-17566.38</v>
-      </c>
-      <c r="H82" s="18" t="n">
-        <v>-24412.36</v>
-      </c>
-      <c r="I82" s="18" t="n">
-        <v>10213.53</v>
-      </c>
-      <c r="J82" s="18" t="n">
-        <v>-3443.48</v>
-      </c>
-      <c r="K82" s="34" t="n">
-        <v>-35208.69</v>
-      </c>
-      <c r="L82" s="18" t="n">
-        <v>-5697.75</v>
-      </c>
-      <c r="M82" s="18" t="n">
-        <v>-4816.71</v>
-      </c>
-      <c r="N82" s="18" t="n">
-        <v>-25873.48</v>
-      </c>
-      <c r="O82" s="18" t="n">
-        <v>-2913.21</v>
-      </c>
-      <c r="P82" s="34" t="n">
-        <v>-39301.15</v>
-      </c>
-      <c r="Q82" s="18" t="n">
-        <v>-4372</v>
-      </c>
-      <c r="R82" s="18" t="n">
-        <v>-15812.72</v>
-      </c>
-      <c r="S82" s="18" t="n">
-        <v>-5703.87</v>
-      </c>
-      <c r="T82" s="18" t="n">
-        <v>-14101.75</v>
-      </c>
-      <c r="U82" s="34" t="n">
-        <v>-39990.34</v>
-      </c>
-      <c r="V82" s="18" t="n">
-        <v>-2729.58</v>
-      </c>
-      <c r="W82" s="18" t="n">
-        <v>-6725.99</v>
-      </c>
-      <c r="X82" s="18" t="n">
-        <v>-19659.87</v>
-      </c>
-      <c r="Y82" s="18" t="n">
-        <v>-15083.38</v>
-      </c>
-      <c r="Z82" s="34" t="n">
-        <v>-44198.82</v>
-      </c>
-      <c r="AA82" s="18" t="n">
-        <v>-8734.1</v>
-      </c>
+      <c r="K82" s="9" t="n"/>
+      <c r="P82" s="9" t="n"/>
+      <c r="U82" s="9" t="n"/>
+      <c r="Z82" s="9" t="n"/>
       <c r="AB82" s="19" t="n">
-        <v>-26709.34</v>
+        <v>340.68</v>
       </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
@@ -19527,64 +19332,17 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
-        </is>
-      </c>
-      <c r="E83" s="18" t="n">
-        <v>600</v>
+          <t>이자비용</t>
+        </is>
       </c>
       <c r="F83" s="9" t="n"/>
-      <c r="G83" s="18" t="n">
-        <v>689.24</v>
-      </c>
-      <c r="I83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="J83" s="18" t="n">
-        <v>6.64</v>
-      </c>
       <c r="K83" s="9" t="n"/>
-      <c r="L83" s="18" t="n">
-        <v>2343.53</v>
-      </c>
-      <c r="M83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="N83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="O83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P83" s="34" t="n">
-        <v>2343.53</v>
-      </c>
-      <c r="Q83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="R83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S83" s="18" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="T83" s="18" t="n">
-        <v>4.78</v>
-      </c>
-      <c r="U83" s="34" t="n">
-        <v>8.630000000000001</v>
-      </c>
-      <c r="X83" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y83" s="18" t="n">
-        <v>0</v>
-      </c>
+      <c r="P83" s="9" t="n"/>
+      <c r="U83" s="9" t="n"/>
       <c r="Z83" s="9" t="n"/>
-      <c r="AA83" s="18" t="n">
-        <v>71.92</v>
-      </c>
-      <c r="AB83" s="5" t="n"/>
+      <c r="AB83" s="19" t="n">
+        <v>2239.9</v>
+      </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
       <c r="AE83" s="11" t="n"/>
@@ -19605,78 +19363,16 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
-        </is>
-      </c>
-      <c r="E84" s="18" t="n">
-        <v>3358.98</v>
+          <t>외환차익</t>
+        </is>
       </c>
       <c r="F84" s="9" t="n"/>
-      <c r="G84" s="18" t="n">
-        <v>20235.93</v>
-      </c>
-      <c r="H84" s="18" t="n">
-        <v>4364.11</v>
-      </c>
-      <c r="I84" s="18" t="n">
-        <v>7451.05</v>
-      </c>
-      <c r="J84" s="18" t="n">
-        <v>3313.77</v>
-      </c>
-      <c r="K84" s="34" t="n">
-        <v>35364.86</v>
-      </c>
-      <c r="L84" s="18" t="n">
-        <v>1587.33</v>
-      </c>
-      <c r="M84" s="18" t="n">
-        <v>3576.4</v>
-      </c>
-      <c r="N84" s="18" t="n">
-        <v>37664.9</v>
-      </c>
-      <c r="O84" s="18" t="n">
-        <v>309.29</v>
-      </c>
-      <c r="P84" s="34" t="n">
-        <v>43137.92</v>
-      </c>
-      <c r="Q84" s="18" t="n">
-        <v>3303.81</v>
-      </c>
-      <c r="R84" s="18" t="n">
-        <v>2728.52</v>
-      </c>
-      <c r="S84" s="18" t="n">
-        <v>4862.79</v>
-      </c>
-      <c r="T84" s="18" t="n">
-        <v>9277.129999999999</v>
-      </c>
-      <c r="U84" s="34" t="n">
-        <v>20172.25</v>
-      </c>
-      <c r="V84" s="18" t="n">
-        <v>2809.12</v>
-      </c>
-      <c r="W84" s="18" t="n">
-        <v>1146.07</v>
-      </c>
-      <c r="X84" s="18" t="n">
-        <v>1912.09</v>
-      </c>
-      <c r="Y84" s="18" t="n">
-        <v>3630.81</v>
-      </c>
-      <c r="Z84" s="34" t="n">
-        <v>9498.09</v>
-      </c>
-      <c r="AA84" s="18" t="n">
-        <v>2342.4</v>
-      </c>
+      <c r="K84" s="9" t="n"/>
+      <c r="P84" s="9" t="n"/>
+      <c r="U84" s="9" t="n"/>
+      <c r="Z84" s="9" t="n"/>
       <c r="AB84" s="19" t="n">
-        <v>6416.85</v>
+        <v>507.94</v>
       </c>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
@@ -19698,78 +19394,16 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>CAPEX</t>
-        </is>
-      </c>
-      <c r="E85" s="18" t="n">
-        <v>3408.48</v>
+          <t>외환차손</t>
+        </is>
       </c>
       <c r="F85" s="9" t="n"/>
-      <c r="G85" s="18" t="n">
-        <v>20235.93</v>
-      </c>
-      <c r="H85" s="18" t="n">
-        <v>4369.61</v>
-      </c>
-      <c r="I85" s="18" t="n">
-        <v>7863.9</v>
-      </c>
-      <c r="J85" s="18" t="n">
-        <v>3342.52</v>
-      </c>
-      <c r="K85" s="34" t="n">
-        <v>35811.96</v>
-      </c>
-      <c r="L85" s="18" t="n">
-        <v>1587.33</v>
-      </c>
-      <c r="M85" s="18" t="n">
-        <v>3970.4</v>
-      </c>
-      <c r="N85" s="18" t="n">
-        <v>37681.98</v>
-      </c>
-      <c r="O85" s="18" t="n">
-        <v>309.29</v>
-      </c>
-      <c r="P85" s="34" t="n">
-        <v>43549</v>
-      </c>
-      <c r="Q85" s="18" t="n">
-        <v>3303.81</v>
-      </c>
-      <c r="R85" s="18" t="n">
-        <v>2828.52</v>
-      </c>
-      <c r="S85" s="18" t="n">
-        <v>4869.39</v>
-      </c>
-      <c r="T85" s="18" t="n">
-        <v>9277.129999999999</v>
-      </c>
-      <c r="U85" s="34" t="n">
-        <v>20278.85</v>
-      </c>
-      <c r="V85" s="18" t="n">
-        <v>2809.12</v>
-      </c>
-      <c r="W85" s="18" t="n">
-        <v>1146.07</v>
-      </c>
-      <c r="X85" s="18" t="n">
-        <v>1912.09</v>
-      </c>
-      <c r="Y85" s="18" t="n">
-        <v>3630.81</v>
-      </c>
-      <c r="Z85" s="34" t="n">
-        <v>9498.09</v>
-      </c>
-      <c r="AA85" s="18" t="n">
-        <v>2342.96</v>
-      </c>
+      <c r="K85" s="9" t="n"/>
+      <c r="P85" s="9" t="n"/>
+      <c r="U85" s="9" t="n"/>
+      <c r="Z85" s="9" t="n"/>
       <c r="AB85" s="19" t="n">
-        <v>6416.85</v>
+        <v>16.19</v>
       </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
@@ -19791,43 +19425,16 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
-        </is>
-      </c>
-      <c r="E86" s="18" t="n">
-        <v>49.5</v>
+          <t>외화환산이익</t>
+        </is>
       </c>
       <c r="F86" s="9" t="n"/>
-      <c r="I86" s="18" t="n">
-        <v>412.85</v>
-      </c>
-      <c r="J86" s="18" t="n">
-        <v>28.75</v>
-      </c>
       <c r="K86" s="9" t="n"/>
-      <c r="N86" s="18" t="n">
-        <v>17.08</v>
-      </c>
-      <c r="O86" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="P86" s="9" t="n"/>
-      <c r="S86" s="18" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="T86" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="U86" s="9" t="n"/>
-      <c r="X86" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="Z86" s="9" t="n"/>
-      <c r="AA86" s="18" t="n">
-        <v>0.5600000000000001</v>
-      </c>
       <c r="AB86" s="19" t="n">
-        <v>0</v>
+        <v>1238.84</v>
       </c>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
@@ -19849,78 +19456,16 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
-        </is>
-      </c>
-      <c r="E87" s="18" t="n">
-        <v>19600.66</v>
+          <t>외화환산손실</t>
+        </is>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
-        <v>40002.33</v>
-      </c>
-      <c r="H87" s="18" t="n">
-        <v>-10465.85</v>
-      </c>
-      <c r="I87" s="18" t="n">
-        <v>2314.28</v>
-      </c>
-      <c r="J87" s="18" t="n">
-        <v>-4511.02</v>
-      </c>
-      <c r="K87" s="34" t="n">
-        <v>27339.74</v>
-      </c>
-      <c r="L87" s="18" t="n">
-        <v>-867.58</v>
-      </c>
-      <c r="M87" s="18" t="n">
-        <v>-31584.75</v>
-      </c>
-      <c r="N87" s="18" t="n">
-        <v>16609.06</v>
-      </c>
-      <c r="O87" s="18" t="n">
-        <v>-10151.79</v>
-      </c>
-      <c r="P87" s="34" t="n">
-        <v>-25995.06</v>
-      </c>
-      <c r="Q87" s="18" t="n">
-        <v>9557.9</v>
-      </c>
-      <c r="R87" s="18" t="n">
-        <v>-13923.18</v>
-      </c>
-      <c r="S87" s="18" t="n">
-        <v>37748.96</v>
-      </c>
-      <c r="T87" s="18" t="n">
-        <v>3914.34</v>
-      </c>
-      <c r="U87" s="34" t="n">
-        <v>37298.02</v>
-      </c>
-      <c r="V87" s="18" t="n">
-        <v>-1631.27</v>
-      </c>
-      <c r="W87" s="18" t="n">
-        <v>-11272.32</v>
-      </c>
-      <c r="X87" s="18" t="n">
-        <v>1271.83</v>
-      </c>
-      <c r="Y87" s="18" t="n">
-        <v>-25397.76</v>
-      </c>
-      <c r="Z87" s="34" t="n">
-        <v>-37029.52</v>
-      </c>
-      <c r="AA87" s="18" t="n">
-        <v>-1279.02</v>
-      </c>
+      <c r="K87" s="9" t="n"/>
+      <c r="P87" s="9" t="n"/>
+      <c r="U87" s="9" t="n"/>
+      <c r="Z87" s="9" t="n"/>
       <c r="AB87" s="19" t="n">
-        <v>-14879.09</v>
+        <v>14.61</v>
       </c>
       <c r="AC87" s="10" t="n"/>
       <c r="AD87" s="10" t="n"/>
@@ -19942,78 +19487,16 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
-        </is>
-      </c>
-      <c r="E88" s="18" t="n">
-        <v>345</v>
+          <t>이자손익</t>
+        </is>
       </c>
       <c r="F88" s="9" t="n"/>
-      <c r="G88" s="18" t="n">
-        <v>53975.2</v>
-      </c>
-      <c r="H88" s="18" t="n">
-        <v>16880</v>
-      </c>
-      <c r="I88" s="18" t="n">
-        <v>26394.06</v>
-      </c>
-      <c r="J88" s="18" t="n">
-        <v>24204</v>
-      </c>
-      <c r="K88" s="34" t="n">
-        <v>121453.26</v>
-      </c>
-      <c r="L88" s="18" t="n">
-        <v>450</v>
-      </c>
-      <c r="M88" s="18" t="n">
-        <v>57120</v>
-      </c>
-      <c r="N88" s="18" t="n">
-        <v>37120</v>
-      </c>
-      <c r="O88" s="18" t="n">
-        <v>5660</v>
-      </c>
-      <c r="P88" s="34" t="n">
-        <v>100350</v>
-      </c>
-      <c r="Q88" s="18" t="n">
-        <v>50520</v>
-      </c>
-      <c r="R88" s="18" t="n">
-        <v>43540</v>
-      </c>
-      <c r="S88" s="18" t="n">
-        <v>66880</v>
-      </c>
-      <c r="T88" s="18" t="n">
-        <v>330</v>
-      </c>
-      <c r="U88" s="34" t="n">
-        <v>161270</v>
-      </c>
-      <c r="V88" s="18" t="n">
-        <v>71577.00999999999</v>
-      </c>
-      <c r="W88" s="18" t="n">
-        <v>2072.99</v>
-      </c>
-      <c r="X88" s="18" t="n">
-        <v>51230</v>
-      </c>
-      <c r="Y88" s="18" t="n">
-        <v>1245</v>
-      </c>
-      <c r="Z88" s="34" t="n">
-        <v>126125</v>
-      </c>
-      <c r="AA88" s="18" t="n">
-        <v>45390</v>
-      </c>
+      <c r="K88" s="9" t="n"/>
+      <c r="P88" s="9" t="n"/>
+      <c r="U88" s="9" t="n"/>
+      <c r="Z88" s="9" t="n"/>
       <c r="AB88" s="19" t="n">
-        <v>29610</v>
+        <v>-1508.11</v>
       </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
@@ -20035,77 +19518,79 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>20639</v>
+        <v>-11105</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>38500</v>
+        <v>-20116.62</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>10000</v>
+        <v>7511.35</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>0</v>
+        <v>4975.25</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>28000</v>
+        <v>27161.72</v>
       </c>
       <c r="K89" s="34" t="n">
-        <v>76500</v>
+        <v>19531.7</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>0</v>
+        <v>-10890.66</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>80</v>
+        <v>43778.46</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>39920</v>
+        <v>12798.55</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>100</v>
+        <v>23379.42</v>
       </c>
       <c r="P89" s="34" t="n">
-        <v>40100</v>
+        <v>69065.77</v>
       </c>
       <c r="Q89" s="18" t="n">
-        <v>8000</v>
+        <v>13245.72</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>0</v>
+        <v>6881.57</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>37455</v>
+        <v>2183.77</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>14145</v>
+        <v>9340.120000000001</v>
       </c>
       <c r="U89" s="34" t="n">
-        <v>59600</v>
+        <v>31651.18</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>180</v>
+        <v>-711.8</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>105</v>
+        <v>32230.31</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>108180</v>
+        <v>26686.46</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>20</v>
+        <v>-647.34</v>
       </c>
       <c r="Z89" s="34" t="n">
-        <v>108485</v>
+        <v>57557.63</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>2010</v>
-      </c>
-      <c r="AB89" s="5" t="n"/>
+        <v>26339.65</v>
+      </c>
+      <c r="AB89" s="19" t="n">
+        <v>15768.09</v>
+      </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
       <c r="AE89" s="11" t="n"/>
@@ -20126,73 +19611,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>0</v>
+        <v>-109.44</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>35905.2</v>
+        <v>-5594.55</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>17550</v>
+        <v>-6715.09</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>21501.06</v>
+        <v>-245.73</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>27901</v>
+        <v>-30.65</v>
       </c>
       <c r="K90" s="34" t="n">
-        <v>102857.26</v>
+        <v>-12586.02</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>0</v>
+        <v>-321.14</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>33700</v>
+        <v>295.05</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>20390</v>
+        <v>-1009.87</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>0</v>
+        <v>-126.01</v>
       </c>
       <c r="P90" s="34" t="n">
-        <v>54090</v>
+        <v>-1161.97</v>
       </c>
       <c r="Q90" s="18" t="n">
-        <v>18000</v>
+        <v>-4239.15</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>45000</v>
+        <v>-4477.44</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>45200</v>
+        <v>-3440.63</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>1100</v>
+        <v>-262.34</v>
       </c>
       <c r="U90" s="34" t="n">
-        <v>109300</v>
+        <v>-12419.56</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>71700.33</v>
+        <v>-3859.35</v>
+      </c>
+      <c r="W90" s="18" t="n">
+        <v>-3818.88</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>116200</v>
+        <v>-1758.81</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>24985</v>
-      </c>
-      <c r="Z90" s="9" t="n"/>
+        <v>-3544.68</v>
+      </c>
+      <c r="Z90" s="34" t="n">
+        <v>-12981.72</v>
+      </c>
       <c r="AA90" s="18" t="n">
-        <v>47000</v>
+        <v>-3576.28</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>30000</v>
+        <v>-4050.64</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -20214,78 +19704,78 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
-        <v>828.14</v>
+        <v>-2757.98</v>
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="18" t="n">
-        <v>16129.05</v>
+        <v>-17566.38</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>11086.22</v>
+        <v>-24412.36</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>2100</v>
+        <v>10213.53</v>
       </c>
       <c r="J91" s="18" t="n">
-        <v>15600.35</v>
+        <v>-3443.48</v>
       </c>
       <c r="K91" s="34" t="n">
-        <v>44915.62</v>
+        <v>-35208.69</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>600</v>
+        <v>-5697.75</v>
       </c>
       <c r="M91" s="18" t="n">
-        <v>32200</v>
+        <v>-4816.71</v>
       </c>
       <c r="N91" s="18" t="n">
-        <v>26812</v>
+        <v>-25873.48</v>
       </c>
       <c r="O91" s="18" t="n">
-        <v>15600</v>
+        <v>-2913.21</v>
       </c>
       <c r="P91" s="34" t="n">
-        <v>75212</v>
+        <v>-39301.15</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>40600</v>
+        <v>-4372</v>
       </c>
       <c r="R91" s="18" t="n">
-        <v>600</v>
+        <v>-15812.72</v>
       </c>
       <c r="S91" s="18" t="n">
-        <v>15600</v>
+        <v>-5703.87</v>
       </c>
       <c r="T91" s="18" t="n">
-        <v>2496.04</v>
+        <v>-14101.75</v>
       </c>
       <c r="U91" s="34" t="n">
-        <v>59296.04</v>
+        <v>-39990.34</v>
       </c>
       <c r="V91" s="18" t="n">
-        <v>1350</v>
+        <v>-2729.58</v>
       </c>
       <c r="W91" s="18" t="n">
-        <v>1350</v>
+        <v>-6725.99</v>
       </c>
       <c r="X91" s="18" t="n">
-        <v>41350</v>
+        <v>-19659.87</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>1050</v>
+        <v>-15083.38</v>
       </c>
       <c r="Z91" s="34" t="n">
-        <v>45100</v>
+        <v>-44198.82</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>1050</v>
+        <v>-8734.1</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>1050</v>
+        <v>-26709.34</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -20307,79 +19797,64 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E92" s="18" t="n">
-        <v>520.01</v>
+        <v>600</v>
       </c>
       <c r="F92" s="9" t="n"/>
       <c r="G92" s="18" t="n">
-        <v>538.26</v>
-      </c>
-      <c r="H92" s="18" t="n">
-        <v>486.52</v>
+        <v>689.24</v>
       </c>
       <c r="I92" s="18" t="n">
-        <v>478.72</v>
+        <v>0</v>
       </c>
       <c r="J92" s="18" t="n">
-        <v>174.02</v>
-      </c>
-      <c r="K92" s="34" t="n">
-        <v>1677.52</v>
-      </c>
+        <v>6.64</v>
+      </c>
+      <c r="K92" s="9" t="n"/>
       <c r="L92" s="18" t="n">
-        <v>177.58</v>
+        <v>2343.53</v>
       </c>
       <c r="M92" s="18" t="n">
-        <v>190.08</v>
+        <v>0</v>
       </c>
       <c r="N92" s="18" t="n">
-        <v>228.95</v>
+        <v>0</v>
       </c>
       <c r="O92" s="18" t="n">
-        <v>311.78</v>
+        <v>0</v>
       </c>
       <c r="P92" s="34" t="n">
-        <v>908.39</v>
+        <v>2343.53</v>
       </c>
       <c r="Q92" s="18" t="n">
-        <v>313.27</v>
+        <v>0</v>
       </c>
       <c r="R92" s="18" t="n">
-        <v>320.97</v>
+        <v>0</v>
       </c>
       <c r="S92" s="18" t="n">
-        <v>317</v>
+        <v>3.85</v>
       </c>
       <c r="T92" s="18" t="n">
-        <v>319.13</v>
+        <v>4.78</v>
       </c>
       <c r="U92" s="34" t="n">
-        <v>1270.37</v>
-      </c>
-      <c r="V92" s="18" t="n">
-        <v>337.95</v>
-      </c>
-      <c r="W92" s="18" t="n">
-        <v>915.74</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="X92" s="18" t="n">
-        <v>588.1799999999999</v>
+        <v>0</v>
       </c>
       <c r="Y92" s="18" t="n">
-        <v>627.76</v>
-      </c>
-      <c r="Z92" s="34" t="n">
-        <v>2469.63</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z92" s="9" t="n"/>
       <c r="AA92" s="18" t="n">
-        <v>629.02</v>
-      </c>
-      <c r="AB92" s="19" t="n">
-        <v>637.96</v>
-      </c>
+        <v>71.92</v>
+      </c>
+      <c r="AB92" s="5" t="n"/>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
       <c r="AE92" s="11" t="n"/>
@@ -20400,69 +19875,79 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E93" s="18" t="n">
-        <v>0</v>
+        <v>3358.98</v>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="G93" s="18" t="n">
-        <v>0.36</v>
+        <v>20235.93</v>
       </c>
       <c r="H93" s="18" t="n">
-        <v>0</v>
+        <v>4364.11</v>
       </c>
       <c r="I93" s="18" t="n">
-        <v>0</v>
+        <v>7451.05</v>
       </c>
       <c r="J93" s="18" t="n">
-        <v>12999.64</v>
+        <v>3313.77</v>
       </c>
       <c r="K93" s="34" t="n">
-        <v>13000</v>
+        <v>35364.86</v>
       </c>
       <c r="L93" s="18" t="n">
-        <v>0</v>
+        <v>1587.33</v>
       </c>
       <c r="M93" s="18" t="n">
-        <v>0</v>
+        <v>3576.4</v>
       </c>
       <c r="N93" s="18" t="n">
-        <v>13000</v>
+        <v>37664.9</v>
       </c>
       <c r="O93" s="18" t="n">
-        <v>0</v>
+        <v>309.29</v>
       </c>
       <c r="P93" s="34" t="n">
-        <v>13000</v>
+        <v>43137.92</v>
       </c>
       <c r="Q93" s="18" t="n">
-        <v>208.41</v>
+        <v>3303.81</v>
       </c>
       <c r="R93" s="18" t="n">
-        <v>562.65</v>
+        <v>2728.52</v>
       </c>
       <c r="S93" s="18" t="n">
-        <v>5187.42</v>
+        <v>4862.79</v>
       </c>
       <c r="T93" s="18" t="n">
-        <v>6645.48</v>
+        <v>9277.129999999999</v>
       </c>
       <c r="U93" s="34" t="n">
-        <v>12603.96</v>
+        <v>20172.25</v>
       </c>
       <c r="V93" s="18" t="n">
-        <v>0</v>
+        <v>2809.12</v>
       </c>
       <c r="W93" s="18" t="n">
-        <v>0</v>
+        <v>1146.07</v>
       </c>
       <c r="X93" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z93" s="9" t="n"/>
-      <c r="AB93" s="5" t="n"/>
+        <v>1912.09</v>
+      </c>
+      <c r="Y93" s="18" t="n">
+        <v>3630.81</v>
+      </c>
+      <c r="Z93" s="34" t="n">
+        <v>9498.09</v>
+      </c>
+      <c r="AA93" s="18" t="n">
+        <v>2342.4</v>
+      </c>
+      <c r="AB93" s="19" t="n">
+        <v>6416.85</v>
+      </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
       <c r="AE93" s="11" t="n"/>
@@ -20483,50 +19968,79 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E94" s="18" t="n">
-        <v>0</v>
+        <v>3408.48</v>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="G94" s="18" t="n">
-        <v>0</v>
+        <v>20235.93</v>
       </c>
       <c r="H94" s="18" t="n">
-        <v>8223.120000000001</v>
+        <v>4369.61</v>
       </c>
       <c r="I94" s="18" t="n">
-        <v>0</v>
+        <v>7863.9</v>
       </c>
       <c r="J94" s="18" t="n">
-        <v>0</v>
+        <v>3342.52</v>
       </c>
       <c r="K94" s="34" t="n">
-        <v>8223.120000000001</v>
+        <v>35811.96</v>
+      </c>
+      <c r="L94" s="18" t="n">
+        <v>1587.33</v>
+      </c>
+      <c r="M94" s="18" t="n">
+        <v>3970.4</v>
       </c>
       <c r="N94" s="18" t="n">
-        <v>0</v>
+        <v>37681.98</v>
       </c>
       <c r="O94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" s="9" t="n"/>
+        <v>309.29</v>
+      </c>
+      <c r="P94" s="34" t="n">
+        <v>43549</v>
+      </c>
+      <c r="Q94" s="18" t="n">
+        <v>3303.81</v>
+      </c>
+      <c r="R94" s="18" t="n">
+        <v>2828.52</v>
+      </c>
       <c r="S94" s="18" t="n">
-        <v>0</v>
+        <v>4869.39</v>
       </c>
       <c r="T94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U94" s="9" t="n"/>
+        <v>9277.129999999999</v>
+      </c>
+      <c r="U94" s="34" t="n">
+        <v>20278.85</v>
+      </c>
+      <c r="V94" s="18" t="n">
+        <v>2809.12</v>
+      </c>
+      <c r="W94" s="18" t="n">
+        <v>1146.07</v>
+      </c>
       <c r="X94" s="18" t="n">
-        <v>0</v>
+        <v>1912.09</v>
       </c>
       <c r="Y94" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z94" s="9" t="n"/>
-      <c r="AB94" s="5" t="n"/>
+        <v>3630.81</v>
+      </c>
+      <c r="Z94" s="34" t="n">
+        <v>9498.09</v>
+      </c>
+      <c r="AA94" s="18" t="n">
+        <v>2342.96</v>
+      </c>
+      <c r="AB94" s="19" t="n">
+        <v>6416.85</v>
+      </c>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -20547,24 +20061,44 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E95" s="18" t="n">
+        <v>49.5</v>
+      </c>
+      <c r="F95" s="9" t="n"/>
+      <c r="I95" s="18" t="n">
+        <v>412.85</v>
+      </c>
+      <c r="J95" s="18" t="n">
+        <v>28.75</v>
+      </c>
+      <c r="K95" s="9" t="n"/>
+      <c r="N95" s="18" t="n">
+        <v>17.08</v>
+      </c>
+      <c r="O95" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="F95" s="9" t="n"/>
-      <c r="G95" s="18" t="n">
+      <c r="P95" s="9" t="n"/>
+      <c r="S95" s="18" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="T95" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J95" s="18" t="n">
+      <c r="U95" s="9" t="n"/>
+      <c r="X95" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="K95" s="9" t="n"/>
-      <c r="P95" s="9" t="n"/>
-      <c r="U95" s="9" t="n"/>
       <c r="Z95" s="9" t="n"/>
-      <c r="AB95" s="5" t="n"/>
+      <c r="AA95" s="18" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AB95" s="19" t="n">
+        <v>0</v>
+      </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
       <c r="AE95" s="11" t="n"/>
@@ -20585,78 +20119,78 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E96" s="18" t="n">
-        <v>5662.39</v>
+        <v>19600.66</v>
       </c>
       <c r="F96" s="9" t="n"/>
       <c r="G96" s="18" t="n">
-        <v>2720.95</v>
+        <v>40002.33</v>
       </c>
       <c r="H96" s="18" t="n">
-        <v>-27623.26</v>
+        <v>-10465.85</v>
       </c>
       <c r="I96" s="18" t="n">
-        <v>18377.33</v>
+        <v>2314.28</v>
       </c>
       <c r="J96" s="18" t="n">
-        <v>15993.43</v>
+        <v>-4511.02</v>
       </c>
       <c r="K96" s="34" t="n">
-        <v>9468.450000000001</v>
+        <v>27339.74</v>
       </c>
       <c r="L96" s="18" t="n">
-        <v>-17003.88</v>
+        <v>-867.58</v>
       </c>
       <c r="M96" s="18" t="n">
-        <v>7033.05</v>
+        <v>-31584.75</v>
       </c>
       <c r="N96" s="18" t="n">
-        <v>3879.46</v>
+        <v>16609.06</v>
       </c>
       <c r="O96" s="18" t="n">
-        <v>9752.02</v>
+        <v>-10151.79</v>
       </c>
       <c r="P96" s="34" t="n">
-        <v>3660.65</v>
+        <v>-25995.06</v>
       </c>
       <c r="Q96" s="18" t="n">
-        <v>19094.45</v>
+        <v>9557.9</v>
       </c>
       <c r="R96" s="18" t="n">
-        <v>-23560.38</v>
+        <v>-13923.18</v>
       </c>
       <c r="S96" s="18" t="n">
-        <v>33662.45</v>
+        <v>37748.96</v>
       </c>
       <c r="T96" s="18" t="n">
-        <v>-405.76</v>
+        <v>3914.34</v>
       </c>
       <c r="U96" s="34" t="n">
-        <v>28790.76</v>
+        <v>37298.02</v>
       </c>
       <c r="V96" s="18" t="n">
-        <v>-4952.72</v>
+        <v>-1631.27</v>
       </c>
       <c r="W96" s="18" t="n">
-        <v>14969.52</v>
+        <v>-11272.32</v>
       </c>
       <c r="X96" s="18" t="n">
-        <v>8382.809999999999</v>
+        <v>1271.83</v>
       </c>
       <c r="Y96" s="18" t="n">
-        <v>-42888.22</v>
+        <v>-25397.76</v>
       </c>
       <c r="Z96" s="34" t="n">
-        <v>-24488.61</v>
+        <v>-37029.52</v>
       </c>
       <c r="AA96" s="18" t="n">
-        <v>14494.38</v>
+        <v>-1279.02</v>
       </c>
       <c r="AB96" s="19" t="n">
-        <v>-26079.27</v>
+        <v>-14879.09</v>
       </c>
       <c r="AC96" s="10" t="n"/>
       <c r="AD96" s="10" t="n"/>
@@ -20678,78 +20212,78 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
+          <t>단기차입금의증가</t>
         </is>
       </c>
       <c r="E97" s="18" t="n">
-        <v>5662.38</v>
+        <v>345</v>
       </c>
       <c r="F97" s="9" t="n"/>
       <c r="G97" s="18" t="n">
-        <v>40389.7</v>
+        <v>53975.2</v>
       </c>
       <c r="H97" s="18" t="n">
-        <v>-27623.26</v>
+        <v>16880</v>
       </c>
       <c r="I97" s="18" t="n">
-        <v>18377.33</v>
+        <v>26394.06</v>
       </c>
       <c r="J97" s="18" t="n">
-        <v>15993.42</v>
+        <v>24204</v>
       </c>
       <c r="K97" s="34" t="n">
-        <v>47137.19</v>
+        <v>121453.26</v>
       </c>
       <c r="L97" s="18" t="n">
-        <v>30087.12</v>
+        <v>450</v>
       </c>
       <c r="M97" s="18" t="n">
-        <v>7033.05</v>
+        <v>57120</v>
       </c>
       <c r="N97" s="18" t="n">
-        <v>3448.19</v>
+        <v>37120</v>
       </c>
       <c r="O97" s="18" t="n">
-        <v>10183.3</v>
+        <v>5660</v>
       </c>
       <c r="P97" s="34" t="n">
-        <v>50751.66</v>
+        <v>100350</v>
       </c>
       <c r="Q97" s="18" t="n">
-        <v>69793.88</v>
+        <v>50520</v>
       </c>
       <c r="R97" s="18" t="n">
-        <v>-23508.15</v>
+        <v>43540</v>
       </c>
       <c r="S97" s="18" t="n">
-        <v>33662.44</v>
+        <v>66880</v>
       </c>
       <c r="T97" s="18" t="n">
-        <v>-405.75</v>
+        <v>330</v>
       </c>
       <c r="U97" s="34" t="n">
-        <v>79542.42</v>
+        <v>161270</v>
       </c>
       <c r="V97" s="18" t="n">
-        <v>74589.69</v>
+        <v>71577.00999999999</v>
       </c>
       <c r="W97" s="18" t="n">
-        <v>14969.53</v>
+        <v>2072.99</v>
       </c>
       <c r="X97" s="18" t="n">
-        <v>8382.809999999999</v>
+        <v>51230</v>
       </c>
       <c r="Y97" s="18" t="n">
-        <v>-42888.23</v>
+        <v>1245</v>
       </c>
       <c r="Z97" s="34" t="n">
-        <v>55053.8</v>
+        <v>126125</v>
       </c>
       <c r="AA97" s="18" t="n">
-        <v>69548.17999999999</v>
+        <v>45390</v>
       </c>
       <c r="AB97" s="19" t="n">
-        <v>-26079.27</v>
+        <v>29610</v>
       </c>
       <c r="AC97" s="10" t="n"/>
       <c r="AD97" s="10" t="n"/>
@@ -20771,40 +20305,76 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
-        </is>
+          <t>장기차입금의증가</t>
+        </is>
+      </c>
+      <c r="E98" s="18" t="n">
+        <v>20639</v>
       </c>
       <c r="F98" s="9" t="n"/>
+      <c r="G98" s="18" t="n">
+        <v>38500</v>
+      </c>
+      <c r="H98" s="18" t="n">
+        <v>10000</v>
+      </c>
       <c r="I98" s="18" t="n">
-        <v>31.36</v>
+        <v>0</v>
       </c>
       <c r="J98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K98" s="9" t="n"/>
+        <v>28000</v>
+      </c>
+      <c r="K98" s="34" t="n">
+        <v>76500</v>
+      </c>
       <c r="L98" s="18" t="n">
         <v>0</v>
       </c>
       <c r="M98" s="18" t="n">
-        <v>96.40000000000001</v>
+        <v>80</v>
       </c>
       <c r="N98" s="18" t="n">
+        <v>39920</v>
+      </c>
+      <c r="O98" s="18" t="n">
+        <v>100</v>
+      </c>
+      <c r="P98" s="34" t="n">
+        <v>40100</v>
+      </c>
+      <c r="Q98" s="18" t="n">
+        <v>8000</v>
+      </c>
+      <c r="R98" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="O98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P98" s="34" t="n">
-        <v>96.40000000000001</v>
-      </c>
       <c r="S98" s="18" t="n">
-        <v>0</v>
+        <v>37455</v>
       </c>
       <c r="T98" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U98" s="9" t="n"/>
-      <c r="Z98" s="9" t="n"/>
+        <v>14145</v>
+      </c>
+      <c r="U98" s="34" t="n">
+        <v>59600</v>
+      </c>
+      <c r="V98" s="18" t="n">
+        <v>180</v>
+      </c>
+      <c r="W98" s="18" t="n">
+        <v>105</v>
+      </c>
+      <c r="X98" s="18" t="n">
+        <v>108180</v>
+      </c>
+      <c r="Y98" s="18" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z98" s="34" t="n">
+        <v>108485</v>
+      </c>
+      <c r="AA98" s="18" t="n">
+        <v>2010</v>
+      </c>
       <c r="AB98" s="5" t="n"/>
       <c r="AC98" s="10" t="n"/>
       <c r="AD98" s="10" t="n"/>
@@ -20826,50 +20396,73 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
-        </is>
+          <t>단기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E99" s="18" t="n">
+        <v>0</v>
       </c>
       <c r="F99" s="9" t="n"/>
-      <c r="K99" s="9" t="n"/>
+      <c r="G99" s="18" t="n">
+        <v>35905.2</v>
+      </c>
+      <c r="H99" s="18" t="n">
+        <v>17550</v>
+      </c>
+      <c r="I99" s="18" t="n">
+        <v>21501.06</v>
+      </c>
+      <c r="J99" s="18" t="n">
+        <v>27901</v>
+      </c>
+      <c r="K99" s="34" t="n">
+        <v>102857.26</v>
+      </c>
+      <c r="L99" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M99" s="18" t="n">
+        <v>33700</v>
+      </c>
+      <c r="N99" s="18" t="n">
+        <v>20390</v>
+      </c>
       <c r="O99" s="18" t="n">
-        <v>188.75</v>
-      </c>
-      <c r="P99" s="9" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="P99" s="34" t="n">
+        <v>54090</v>
+      </c>
       <c r="Q99" s="18" t="n">
-        <v>493.48</v>
+        <v>18000</v>
       </c>
       <c r="R99" s="18" t="n">
-        <v>431.27</v>
+        <v>45000</v>
       </c>
       <c r="S99" s="18" t="n">
-        <v>866.21</v>
+        <v>45200</v>
       </c>
       <c r="T99" s="18" t="n">
-        <v>587.95</v>
+        <v>1100</v>
       </c>
       <c r="U99" s="34" t="n">
-        <v>2378.91</v>
+        <v>109300</v>
       </c>
       <c r="V99" s="18" t="n">
-        <v>621.75</v>
-      </c>
-      <c r="W99" s="18" t="n">
-        <v>301.18</v>
+        <v>71700.33</v>
       </c>
       <c r="X99" s="18" t="n">
-        <v>561.72</v>
+        <v>116200</v>
       </c>
       <c r="Y99" s="18" t="n">
-        <v>1749.29</v>
-      </c>
-      <c r="Z99" s="34" t="n">
-        <v>3233.94</v>
-      </c>
+        <v>24985</v>
+      </c>
+      <c r="Z99" s="9" t="n"/>
       <c r="AA99" s="18" t="n">
-        <v>1701.06</v>
+        <v>47000</v>
       </c>
       <c r="AB99" s="19" t="n">
-        <v>109.26</v>
+        <v>30000</v>
       </c>
       <c r="AC99" s="10" t="n"/>
       <c r="AD99" s="10" t="n"/>
@@ -20891,33 +20484,78 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>이자지급(CF)</t>
-        </is>
+          <t>유동성장기부채의감소</t>
+        </is>
+      </c>
+      <c r="E100" s="18" t="n">
+        <v>828.14</v>
       </c>
       <c r="F100" s="9" t="n"/>
-      <c r="K100" s="9" t="n"/>
-      <c r="P100" s="9" t="n"/>
-      <c r="U100" s="9" t="n"/>
+      <c r="G100" s="18" t="n">
+        <v>16129.05</v>
+      </c>
+      <c r="H100" s="18" t="n">
+        <v>11086.22</v>
+      </c>
+      <c r="I100" s="18" t="n">
+        <v>2100</v>
+      </c>
+      <c r="J100" s="18" t="n">
+        <v>15600.35</v>
+      </c>
+      <c r="K100" s="34" t="n">
+        <v>44915.62</v>
+      </c>
+      <c r="L100" s="18" t="n">
+        <v>600</v>
+      </c>
+      <c r="M100" s="18" t="n">
+        <v>32200</v>
+      </c>
+      <c r="N100" s="18" t="n">
+        <v>26812</v>
+      </c>
+      <c r="O100" s="18" t="n">
+        <v>15600</v>
+      </c>
+      <c r="P100" s="34" t="n">
+        <v>75212</v>
+      </c>
+      <c r="Q100" s="18" t="n">
+        <v>40600</v>
+      </c>
+      <c r="R100" s="18" t="n">
+        <v>600</v>
+      </c>
+      <c r="S100" s="18" t="n">
+        <v>15600</v>
+      </c>
+      <c r="T100" s="18" t="n">
+        <v>2496.04</v>
+      </c>
+      <c r="U100" s="34" t="n">
+        <v>59296.04</v>
+      </c>
       <c r="V100" s="18" t="n">
-        <v>-3362.94</v>
+        <v>1350</v>
       </c>
       <c r="W100" s="18" t="n">
-        <v>-2665.68</v>
+        <v>1350</v>
       </c>
       <c r="X100" s="18" t="n">
-        <v>-102.44</v>
+        <v>41350</v>
       </c>
       <c r="Y100" s="18" t="n">
-        <v>-2674.74</v>
+        <v>1050</v>
       </c>
       <c r="Z100" s="34" t="n">
-        <v>-8805.799999999999</v>
+        <v>45100</v>
       </c>
       <c r="AA100" s="18" t="n">
-        <v>-2347.47</v>
+        <v>1050</v>
       </c>
       <c r="AB100" s="19" t="n">
-        <v>-2365.97</v>
+        <v>1050</v>
       </c>
       <c r="AC100" s="10" t="n"/>
       <c r="AD100" s="10" t="n"/>
@@ -20932,6 +20570,638 @@
       <c r="AM100" s="10" t="n"/>
       <c r="AN100" s="10" t="n"/>
       <c r="AO100" s="11" t="n"/>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>리스부채의상환</t>
+        </is>
+      </c>
+      <c r="E101" s="18" t="n">
+        <v>520.01</v>
+      </c>
+      <c r="F101" s="9" t="n"/>
+      <c r="G101" s="18" t="n">
+        <v>538.26</v>
+      </c>
+      <c r="H101" s="18" t="n">
+        <v>486.52</v>
+      </c>
+      <c r="I101" s="18" t="n">
+        <v>478.72</v>
+      </c>
+      <c r="J101" s="18" t="n">
+        <v>174.02</v>
+      </c>
+      <c r="K101" s="34" t="n">
+        <v>1677.52</v>
+      </c>
+      <c r="L101" s="18" t="n">
+        <v>177.58</v>
+      </c>
+      <c r="M101" s="18" t="n">
+        <v>190.08</v>
+      </c>
+      <c r="N101" s="18" t="n">
+        <v>228.95</v>
+      </c>
+      <c r="O101" s="18" t="n">
+        <v>311.78</v>
+      </c>
+      <c r="P101" s="34" t="n">
+        <v>908.39</v>
+      </c>
+      <c r="Q101" s="18" t="n">
+        <v>313.27</v>
+      </c>
+      <c r="R101" s="18" t="n">
+        <v>320.97</v>
+      </c>
+      <c r="S101" s="18" t="n">
+        <v>317</v>
+      </c>
+      <c r="T101" s="18" t="n">
+        <v>319.13</v>
+      </c>
+      <c r="U101" s="34" t="n">
+        <v>1270.37</v>
+      </c>
+      <c r="V101" s="18" t="n">
+        <v>337.95</v>
+      </c>
+      <c r="W101" s="18" t="n">
+        <v>915.74</v>
+      </c>
+      <c r="X101" s="18" t="n">
+        <v>588.1799999999999</v>
+      </c>
+      <c r="Y101" s="18" t="n">
+        <v>627.76</v>
+      </c>
+      <c r="Z101" s="34" t="n">
+        <v>2469.63</v>
+      </c>
+      <c r="AA101" s="18" t="n">
+        <v>629.02</v>
+      </c>
+      <c r="AB101" s="19" t="n">
+        <v>637.96</v>
+      </c>
+      <c r="AC101" s="10" t="n"/>
+      <c r="AD101" s="10" t="n"/>
+      <c r="AE101" s="11" t="n"/>
+      <c r="AF101" s="10" t="n"/>
+      <c r="AG101" s="10" t="n"/>
+      <c r="AH101" s="10" t="n"/>
+      <c r="AI101" s="10" t="n"/>
+      <c r="AJ101" s="11" t="n"/>
+      <c r="AK101" s="10" t="n"/>
+      <c r="AL101" s="10" t="n"/>
+      <c r="AM101" s="10" t="n"/>
+      <c r="AN101" s="10" t="n"/>
+      <c r="AO101" s="11" t="n"/>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>1</v>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>장기차입금의감소</t>
+        </is>
+      </c>
+      <c r="E102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F102" s="9" t="n"/>
+      <c r="G102" s="18" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="H102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J102" s="18" t="n">
+        <v>12999.64</v>
+      </c>
+      <c r="K102" s="34" t="n">
+        <v>13000</v>
+      </c>
+      <c r="L102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="N102" s="18" t="n">
+        <v>13000</v>
+      </c>
+      <c r="O102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P102" s="34" t="n">
+        <v>13000</v>
+      </c>
+      <c r="Q102" s="18" t="n">
+        <v>208.41</v>
+      </c>
+      <c r="R102" s="18" t="n">
+        <v>562.65</v>
+      </c>
+      <c r="S102" s="18" t="n">
+        <v>5187.42</v>
+      </c>
+      <c r="T102" s="18" t="n">
+        <v>6645.48</v>
+      </c>
+      <c r="U102" s="34" t="n">
+        <v>12603.96</v>
+      </c>
+      <c r="V102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="W102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="X102" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z102" s="9" t="n"/>
+      <c r="AB102" s="5" t="n"/>
+      <c r="AC102" s="10" t="n"/>
+      <c r="AD102" s="10" t="n"/>
+      <c r="AE102" s="11" t="n"/>
+      <c r="AF102" s="10" t="n"/>
+      <c r="AG102" s="10" t="n"/>
+      <c r="AH102" s="10" t="n"/>
+      <c r="AI102" s="10" t="n"/>
+      <c r="AJ102" s="11" t="n"/>
+      <c r="AK102" s="10" t="n"/>
+      <c r="AL102" s="10" t="n"/>
+      <c r="AM102" s="10" t="n"/>
+      <c r="AN102" s="10" t="n"/>
+      <c r="AO102" s="11" t="n"/>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>1</v>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>배당금지급</t>
+        </is>
+      </c>
+      <c r="E103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F103" s="9" t="n"/>
+      <c r="G103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="18" t="n">
+        <v>8223.120000000001</v>
+      </c>
+      <c r="I103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="34" t="n">
+        <v>8223.120000000001</v>
+      </c>
+      <c r="N103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P103" s="9" t="n"/>
+      <c r="S103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U103" s="9" t="n"/>
+      <c r="X103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z103" s="9" t="n"/>
+      <c r="AB103" s="5" t="n"/>
+      <c r="AC103" s="10" t="n"/>
+      <c r="AD103" s="10" t="n"/>
+      <c r="AE103" s="11" t="n"/>
+      <c r="AF103" s="10" t="n"/>
+      <c r="AG103" s="10" t="n"/>
+      <c r="AH103" s="10" t="n"/>
+      <c r="AI103" s="10" t="n"/>
+      <c r="AJ103" s="11" t="n"/>
+      <c r="AK103" s="10" t="n"/>
+      <c r="AL103" s="10" t="n"/>
+      <c r="AM103" s="10" t="n"/>
+      <c r="AN103" s="10" t="n"/>
+      <c r="AO103" s="11" t="n"/>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>1</v>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>자기주식의취득</t>
+        </is>
+      </c>
+      <c r="E104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="F104" s="9" t="n"/>
+      <c r="G104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J104" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="9" t="n"/>
+      <c r="P104" s="9" t="n"/>
+      <c r="U104" s="9" t="n"/>
+      <c r="Z104" s="9" t="n"/>
+      <c r="AB104" s="5" t="n"/>
+      <c r="AC104" s="10" t="n"/>
+      <c r="AD104" s="10" t="n"/>
+      <c r="AE104" s="11" t="n"/>
+      <c r="AF104" s="10" t="n"/>
+      <c r="AG104" s="10" t="n"/>
+      <c r="AH104" s="10" t="n"/>
+      <c r="AI104" s="10" t="n"/>
+      <c r="AJ104" s="11" t="n"/>
+      <c r="AK104" s="10" t="n"/>
+      <c r="AL104" s="10" t="n"/>
+      <c r="AM104" s="10" t="n"/>
+      <c r="AN104" s="10" t="n"/>
+      <c r="AO104" s="11" t="n"/>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>1</v>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>현금및현금성자산의증감</t>
+        </is>
+      </c>
+      <c r="E105" s="18" t="n">
+        <v>5662.39</v>
+      </c>
+      <c r="F105" s="9" t="n"/>
+      <c r="G105" s="18" t="n">
+        <v>2720.95</v>
+      </c>
+      <c r="H105" s="18" t="n">
+        <v>-27623.26</v>
+      </c>
+      <c r="I105" s="18" t="n">
+        <v>18377.33</v>
+      </c>
+      <c r="J105" s="18" t="n">
+        <v>15993.43</v>
+      </c>
+      <c r="K105" s="34" t="n">
+        <v>9468.450000000001</v>
+      </c>
+      <c r="L105" s="18" t="n">
+        <v>-17003.88</v>
+      </c>
+      <c r="M105" s="18" t="n">
+        <v>7033.05</v>
+      </c>
+      <c r="N105" s="18" t="n">
+        <v>3879.46</v>
+      </c>
+      <c r="O105" s="18" t="n">
+        <v>9752.02</v>
+      </c>
+      <c r="P105" s="34" t="n">
+        <v>3660.65</v>
+      </c>
+      <c r="Q105" s="18" t="n">
+        <v>19094.45</v>
+      </c>
+      <c r="R105" s="18" t="n">
+        <v>-23560.38</v>
+      </c>
+      <c r="S105" s="18" t="n">
+        <v>33662.45</v>
+      </c>
+      <c r="T105" s="18" t="n">
+        <v>-405.76</v>
+      </c>
+      <c r="U105" s="34" t="n">
+        <v>28790.76</v>
+      </c>
+      <c r="V105" s="18" t="n">
+        <v>-4952.72</v>
+      </c>
+      <c r="W105" s="18" t="n">
+        <v>14969.52</v>
+      </c>
+      <c r="X105" s="18" t="n">
+        <v>8382.809999999999</v>
+      </c>
+      <c r="Y105" s="18" t="n">
+        <v>-42888.22</v>
+      </c>
+      <c r="Z105" s="34" t="n">
+        <v>-24488.61</v>
+      </c>
+      <c r="AA105" s="18" t="n">
+        <v>14494.38</v>
+      </c>
+      <c r="AB105" s="19" t="n">
+        <v>-26079.27</v>
+      </c>
+      <c r="AC105" s="10" t="n"/>
+      <c r="AD105" s="10" t="n"/>
+      <c r="AE105" s="11" t="n"/>
+      <c r="AF105" s="10" t="n"/>
+      <c r="AG105" s="10" t="n"/>
+      <c r="AH105" s="10" t="n"/>
+      <c r="AI105" s="10" t="n"/>
+      <c r="AJ105" s="11" t="n"/>
+      <c r="AK105" s="10" t="n"/>
+      <c r="AL105" s="10" t="n"/>
+      <c r="AM105" s="10" t="n"/>
+      <c r="AN105" s="10" t="n"/>
+      <c r="AO105" s="11" t="n"/>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>1</v>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>기말현금및현금성자산</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="n">
+        <v>5662.38</v>
+      </c>
+      <c r="F106" s="9" t="n"/>
+      <c r="G106" s="18" t="n">
+        <v>40389.7</v>
+      </c>
+      <c r="H106" s="18" t="n">
+        <v>-27623.26</v>
+      </c>
+      <c r="I106" s="18" t="n">
+        <v>18377.33</v>
+      </c>
+      <c r="J106" s="18" t="n">
+        <v>15993.42</v>
+      </c>
+      <c r="K106" s="34" t="n">
+        <v>47137.19</v>
+      </c>
+      <c r="L106" s="18" t="n">
+        <v>30087.12</v>
+      </c>
+      <c r="M106" s="18" t="n">
+        <v>7033.05</v>
+      </c>
+      <c r="N106" s="18" t="n">
+        <v>3448.19</v>
+      </c>
+      <c r="O106" s="18" t="n">
+        <v>10183.3</v>
+      </c>
+      <c r="P106" s="34" t="n">
+        <v>50751.66</v>
+      </c>
+      <c r="Q106" s="18" t="n">
+        <v>69793.88</v>
+      </c>
+      <c r="R106" s="18" t="n">
+        <v>-23508.15</v>
+      </c>
+      <c r="S106" s="18" t="n">
+        <v>33662.44</v>
+      </c>
+      <c r="T106" s="18" t="n">
+        <v>-405.75</v>
+      </c>
+      <c r="U106" s="34" t="n">
+        <v>79542.42</v>
+      </c>
+      <c r="V106" s="18" t="n">
+        <v>74589.69</v>
+      </c>
+      <c r="W106" s="18" t="n">
+        <v>14969.53</v>
+      </c>
+      <c r="X106" s="18" t="n">
+        <v>8382.809999999999</v>
+      </c>
+      <c r="Y106" s="18" t="n">
+        <v>-42888.23</v>
+      </c>
+      <c r="Z106" s="34" t="n">
+        <v>55053.8</v>
+      </c>
+      <c r="AA106" s="18" t="n">
+        <v>69548.17999999999</v>
+      </c>
+      <c r="AB106" s="19" t="n">
+        <v>-26079.27</v>
+      </c>
+      <c r="AC106" s="10" t="n"/>
+      <c r="AD106" s="10" t="n"/>
+      <c r="AE106" s="11" t="n"/>
+      <c r="AF106" s="10" t="n"/>
+      <c r="AG106" s="10" t="n"/>
+      <c r="AH106" s="10" t="n"/>
+      <c r="AI106" s="10" t="n"/>
+      <c r="AJ106" s="11" t="n"/>
+      <c r="AK106" s="10" t="n"/>
+      <c r="AL106" s="10" t="n"/>
+      <c r="AM106" s="10" t="n"/>
+      <c r="AN106" s="10" t="n"/>
+      <c r="AO106" s="11" t="n"/>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>1</v>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>배당금수취(CF)</t>
+        </is>
+      </c>
+      <c r="F107" s="9" t="n"/>
+      <c r="I107" s="18" t="n">
+        <v>31.36</v>
+      </c>
+      <c r="J107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="9" t="n"/>
+      <c r="L107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M107" s="18" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="N107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="P107" s="34" t="n">
+        <v>96.40000000000001</v>
+      </c>
+      <c r="S107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T107" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="U107" s="9" t="n"/>
+      <c r="Z107" s="9" t="n"/>
+      <c r="AB107" s="5" t="n"/>
+      <c r="AC107" s="10" t="n"/>
+      <c r="AD107" s="10" t="n"/>
+      <c r="AE107" s="11" t="n"/>
+      <c r="AF107" s="10" t="n"/>
+      <c r="AG107" s="10" t="n"/>
+      <c r="AH107" s="10" t="n"/>
+      <c r="AI107" s="10" t="n"/>
+      <c r="AJ107" s="11" t="n"/>
+      <c r="AK107" s="10" t="n"/>
+      <c r="AL107" s="10" t="n"/>
+      <c r="AM107" s="10" t="n"/>
+      <c r="AN107" s="10" t="n"/>
+      <c r="AO107" s="11" t="n"/>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>1</v>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>이자수취(CF)</t>
+        </is>
+      </c>
+      <c r="F108" s="9" t="n"/>
+      <c r="K108" s="9" t="n"/>
+      <c r="O108" s="18" t="n">
+        <v>188.75</v>
+      </c>
+      <c r="P108" s="9" t="n"/>
+      <c r="Q108" s="18" t="n">
+        <v>493.48</v>
+      </c>
+      <c r="R108" s="18" t="n">
+        <v>431.27</v>
+      </c>
+      <c r="S108" s="18" t="n">
+        <v>866.21</v>
+      </c>
+      <c r="T108" s="18" t="n">
+        <v>587.95</v>
+      </c>
+      <c r="U108" s="34" t="n">
+        <v>2378.91</v>
+      </c>
+      <c r="V108" s="18" t="n">
+        <v>621.75</v>
+      </c>
+      <c r="W108" s="18" t="n">
+        <v>301.18</v>
+      </c>
+      <c r="X108" s="18" t="n">
+        <v>561.72</v>
+      </c>
+      <c r="Y108" s="18" t="n">
+        <v>1749.29</v>
+      </c>
+      <c r="Z108" s="34" t="n">
+        <v>3233.94</v>
+      </c>
+      <c r="AA108" s="18" t="n">
+        <v>1701.06</v>
+      </c>
+      <c r="AB108" s="19" t="n">
+        <v>109.26</v>
+      </c>
+      <c r="AC108" s="10" t="n"/>
+      <c r="AD108" s="10" t="n"/>
+      <c r="AE108" s="11" t="n"/>
+      <c r="AF108" s="10" t="n"/>
+      <c r="AG108" s="10" t="n"/>
+      <c r="AH108" s="10" t="n"/>
+      <c r="AI108" s="10" t="n"/>
+      <c r="AJ108" s="11" t="n"/>
+      <c r="AK108" s="10" t="n"/>
+      <c r="AL108" s="10" t="n"/>
+      <c r="AM108" s="10" t="n"/>
+      <c r="AN108" s="10" t="n"/>
+      <c r="AO108" s="11" t="n"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>1</v>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>이자지급(CF)</t>
+        </is>
+      </c>
+      <c r="F109" s="9" t="n"/>
+      <c r="K109" s="9" t="n"/>
+      <c r="P109" s="9" t="n"/>
+      <c r="U109" s="9" t="n"/>
+      <c r="V109" s="18" t="n">
+        <v>-3362.94</v>
+      </c>
+      <c r="W109" s="18" t="n">
+        <v>-2665.68</v>
+      </c>
+      <c r="X109" s="18" t="n">
+        <v>-102.44</v>
+      </c>
+      <c r="Y109" s="18" t="n">
+        <v>-2674.74</v>
+      </c>
+      <c r="Z109" s="34" t="n">
+        <v>-8805.799999999999</v>
+      </c>
+      <c r="AA109" s="18" t="n">
+        <v>-2347.47</v>
+      </c>
+      <c r="AB109" s="19" t="n">
+        <v>-2365.97</v>
+      </c>
+      <c r="AC109" s="10" t="n"/>
+      <c r="AD109" s="10" t="n"/>
+      <c r="AE109" s="11" t="n"/>
+      <c r="AF109" s="10" t="n"/>
+      <c r="AG109" s="10" t="n"/>
+      <c r="AH109" s="10" t="n"/>
+      <c r="AI109" s="10" t="n"/>
+      <c r="AJ109" s="11" t="n"/>
+      <c r="AK109" s="10" t="n"/>
+      <c r="AL109" s="10" t="n"/>
+      <c r="AM109" s="10" t="n"/>
+      <c r="AN109" s="10" t="n"/>
+      <c r="AO109" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -21192,7 +21462,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-09-30</t>
+          <t>UPDATE: 26-10-02</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -44233,7 +44503,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>884</v>
+        <v>892.5</v>
       </c>
     </row>
     <row r="30">
@@ -44253,7 +44523,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>10.97</v>
+        <v>10.87</v>
       </c>
     </row>
     <row r="32">
@@ -44273,7 +44543,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.2046</v>
+        <v>0.2065</v>
       </c>
     </row>
     <row r="34">
@@ -44283,7 +44553,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
     </row>
     <row r="35">
@@ -44293,7 +44563,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>9800</v>
+        <v>9900</v>
       </c>
     </row>
     <row r="36">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -1773,7 +1773,7 @@
     <comment ref="AG43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 276억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 275억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AH43" authorId="0" shapeId="0">
@@ -1785,7 +1785,7 @@
     <comment ref="AI43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 413억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 412억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AK43" authorId="0" shapeId="0">
@@ -1797,13 +1797,13 @@
     <comment ref="AL43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 341억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 340억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AM43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 371억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 370억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AN43" authorId="0" shapeId="0">
@@ -1902,7 +1902,7 @@
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 855 + 종속사 276 + 연결조정 -172
+        <t>추정: 별도(조선기자재) 855 + 종속사 275 + 연결조정 -172
 [identity]</t>
       </text>
     </comment>
@@ -1914,7 +1914,7 @@
     </comment>
     <comment ref="AI5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1116 + 종속사 413 + 연결조정 -258
+        <t>추정: 별도(조선기자재) 1116 + 종속사 412 + 연결조정 -258
 [identity]</t>
       </text>
     </comment>
@@ -1926,13 +1926,13 @@
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 867 + 종속사 341 + 연결조정 -213
+        <t>추정: 별도(조선기자재) 867 + 종속사 340 + 연결조정 -213
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 843 + 종속사 371 + 연결조정 -232
+        <t>추정: 별도(조선기자재) 843 + 종속사 370 + 연결조정 -232
 [identity]</t>
       </text>
     </comment>
@@ -4485,7 +4485,7 @@
     </comment>
     <comment ref="AG41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 276억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 275억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
@@ -4497,7 +4497,7 @@
     </comment>
     <comment ref="AI41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 413억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 412억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
@@ -4509,13 +4509,13 @@
     </comment>
     <comment ref="AL41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 341억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 340억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 371억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 370억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
@@ -4989,7 +4989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-05</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -5860,35 +5860,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1354.78</v>
+        <v>1351.18</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1460.21</v>
+        <v>1459.61</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5979,35 +5979,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1348.28</v>
+        <v>1343.98</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6098,35 +6098,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>858.4</v>
+        <v>855.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>921.0599999999999</v>
+        <v>920.6900000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6217,35 +6217,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>855.13</v>
+        <v>849.38</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6336,35 +6336,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1525.7</v>
+        <v>1519.07</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1694.79</v>
+        <v>1693.81</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6455,35 +6455,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1513.44</v>
+        <v>1505.79</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6574,35 +6574,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>202.07</v>
+        <v>201.53</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.1</v>
+        <v>214.03</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6693,35 +6693,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>201.1</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6919,7 +6919,7 @@
         <v>14570</v>
       </c>
       <c r="AD16" s="20" t="n">
-        <v>10060</v>
+        <v>10080</v>
       </c>
       <c r="AE16" s="11" t="n"/>
       <c r="AF16" s="10" t="n"/>
@@ -7101,7 +7101,7 @@
         <v>10929</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>9985</v>
+        <v>9993.299999999999</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8485,36 +8485,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>0.001876573</v>
+        <v>0.002033772</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.005330017</v>
+        <v>0.005593081</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.005569049</v>
+        <v>0.005797321</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>127.90824296</v>
+        <v>127.910429851</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.004226872</v>
+        <v>0.004425839</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.000877996</v>
+        <v>0.003098323</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>0.005052881</v>
+        <v>-0.002834464</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>127.905531714</v>
+        <v>127.915783462</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.005927288</v>
+        <v>0.006104253</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.004046252</v>
+        <v>-0.003754116</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -8613,36 +8613,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>0.00610542</v>
+        <v>0.005232613</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.001608106</v>
+        <v>-0.002769128</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.007068734</v>
+        <v>0.006267861</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>127.918276704</v>
+        <v>127.910784746</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.001624802</v>
+        <v>0.000729353</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.002473432</v>
+        <v>0.004634267</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.005088667</v>
+        <v>-0.002441023</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>127.912305252</v>
+        <v>127.921373151</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.00314206</v>
+        <v>0.002162586</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.000876413</v>
+        <v>0.007837136</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -8879,26 +8879,26 @@
         <v>-0.094459125</v>
       </c>
       <c r="AG32" s="32" t="n">
-        <v>0.003565534</v>
+        <v>0.003574653</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>-0.11135645</v>
+        <v>-0.111355438</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>-0.171129994</v>
+        <v>-0.171118019</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>-0.149640394</v>
+        <v>-0.149636702</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>-0.005657832</v>
+        <v>-0.005657668</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>-0.189944705</v>
+        <v>-0.189924573</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>-0.318198192</v>
+        <v>-0.318181</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -9007,26 +9007,26 @@
         <v>0.06884949899999999</v>
       </c>
       <c r="AG33" s="32" t="n">
-        <v>-0.002201775</v>
+        <v>-0.002207406</v>
       </c>
       <c r="AH33" s="32" t="n">
-        <v>0.069161874</v>
+        <v>0.069162265</v>
       </c>
       <c r="AI33" s="32" t="n">
-        <v>0.08834086400000001</v>
+        <v>0.088336052</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="32" t="n">
-        <v>0.058830947</v>
+        <v>0.058831518</v>
       </c>
       <c r="AL33" s="32" t="n">
-        <v>0.001790998</v>
+        <v>0.001786434</v>
       </c>
       <c r="AM33" s="32" t="n">
-        <v>0.059523102</v>
+        <v>0.059523918</v>
       </c>
       <c r="AN33" s="32" t="n">
-        <v>0.07624189200000001</v>
+        <v>0.076242879</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9988,33 +9988,33 @@
         <v>-0.012566686</v>
       </c>
       <c r="AD41" s="32" t="n">
-        <v>0.240289804</v>
+        <v>0.24021912</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="32" t="n">
-        <v>0.15750141</v>
+        <v>0.157313405</v>
       </c>
       <c r="AG41" s="32" t="n">
-        <v>-0.012083617</v>
+        <v>-0.012262899</v>
       </c>
       <c r="AH41" s="32" t="n">
-        <v>0.180974107</v>
+        <v>0.180613919</v>
       </c>
       <c r="AI41" s="32" t="n">
-        <v>0.17558557</v>
+        <v>0.175367605</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="32" t="n">
-        <v>0.203760101</v>
+        <v>0.203711977</v>
       </c>
       <c r="AL41" s="32" t="n">
-        <v>0.235990128</v>
+        <v>0.235960359</v>
       </c>
       <c r="AM41" s="32" t="n">
-        <v>0.255684706</v>
+        <v>0.255830508</v>
       </c>
       <c r="AN41" s="32" t="n">
-        <v>0.248424472</v>
+        <v>0.248533191</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -10134,39 +10134,39 @@
         <v>0.188177852</v>
       </c>
       <c r="AD42" s="32" t="n">
-        <v>0.188237306</v>
+        <v>0.188191041</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="32" t="n">
-        <v>0.18873594</v>
+        <v>0.188725988</v>
       </c>
       <c r="AG42" s="32" t="n">
-        <v>0.188552555</v>
+        <v>0.188586779</v>
       </c>
       <c r="AH42" s="32" t="n">
-        <v>0.188179877</v>
+        <v>0.188169492</v>
       </c>
       <c r="AI42" s="32" t="n">
-        <v>0.188215048</v>
+        <v>0.18821219</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="32" t="n">
-        <v>0.188733345</v>
+        <v>0.188704072</v>
       </c>
       <c r="AL42" s="32" t="n">
-        <v>0.188582839</v>
+        <v>0.188562869</v>
       </c>
       <c r="AM42" s="32" t="n">
-        <v>0.188157824</v>
+        <v>0.188166383</v>
       </c>
       <c r="AN42" s="32" t="n">
-        <v>0.188195321</v>
+        <v>0.188205138</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO39,"")</f>
@@ -10289,39 +10289,39 @@
         <v>-0.625165086</v>
       </c>
       <c r="AD43" s="32" t="n">
-        <v>-0.625149598</v>
+        <v>-0.625156731</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF43" s="32" t="n">
-        <v>-0.625167499</v>
+        <v>-0.62514722</v>
       </c>
       <c r="AG43" s="32" t="n">
-        <v>-0.62514518</v>
+        <v>-0.625149744</v>
       </c>
       <c r="AH43" s="32" t="n">
-        <v>-0.625165204</v>
+        <v>-0.625152542</v>
       </c>
       <c r="AI43" s="32" t="n">
-        <v>-0.625145433</v>
+        <v>-0.62515153</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK43" s="32" t="n">
-        <v>-0.625164446</v>
+        <v>-0.625156044</v>
       </c>
       <c r="AL43" s="32" t="n">
-        <v>-0.625154167</v>
+        <v>-0.6251652130000001</v>
       </c>
       <c r="AM43" s="32" t="n">
-        <v>-0.625168673</v>
+        <v>-0.625151834</v>
       </c>
       <c r="AN43" s="32" t="n">
-        <v>-0.625162606</v>
+        <v>-0.625162631</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -10444,39 +10444,39 @@
         <v>0.140323923</v>
       </c>
       <c r="AD44" s="32" t="n">
-        <v>0.143534345</v>
+        <v>0.143449722</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE42/subQ!AE41,"")</f>
         <v/>
       </c>
       <c r="AF44" s="32" t="n">
-        <v>0.142179787</v>
+        <v>0.142142532</v>
       </c>
       <c r="AG44" s="32" t="n">
-        <v>0.144623781</v>
+        <v>0.144707044</v>
       </c>
       <c r="AH44" s="32" t="n">
-        <v>0.148850824</v>
+        <v>0.148790804</v>
       </c>
       <c r="AI44" s="32" t="n">
-        <v>0.151293087</v>
+        <v>0.151289509</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ42/subQ!AJ41,"")</f>
         <v/>
       </c>
       <c r="AK44" s="32" t="n">
-        <v>0.151459559</v>
+        <v>0.151438286</v>
       </c>
       <c r="AL44" s="32" t="n">
-        <v>0.154774766</v>
+        <v>0.15470989</v>
       </c>
       <c r="AM44" s="32" t="n">
-        <v>0.158946687</v>
+        <v>0.158937824</v>
       </c>
       <c r="AN44" s="32" t="n">
-        <v>0.160719277</v>
+        <v>0.160713176</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO42/subQ!AO41,"")</f>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.1911523951882696</v>
+        <v>0.191150998908556</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.06131715422666392</v>
+        <v>0.06131748845681975</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.8217719402459683</v>
+        <v>0.8217632995497146</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.03608861683548219</v>
+        <v>0.03608993984517214</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03869439312458308</v>
+        <v>0.03869520913211543</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-05</t>
+          <t>UPDATE: 26-10-06</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36428,7 +36428,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42073,7 +42073,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261002</t>
+          <t>20261006</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -44369,7 +44369,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>742.6</v>
+        <v>742.5</v>
       </c>
     </row>
     <row r="30">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -4989,7 +4989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-06</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -5860,35 +5860,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1351.18</v>
+        <v>1348.08</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1459.61</v>
+        <v>1458.99</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5979,35 +5979,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.98</v>
+        <v>1338.78</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6098,35 +6098,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>855.39</v>
+        <v>853.26</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.6900000000001</v>
+        <v>920.3099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6217,35 +6217,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>849.38</v>
+        <v>846.85</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6336,35 +6336,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1519.07</v>
+        <v>1516.47</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1693.81</v>
+        <v>1692.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6455,35 +6455,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1505.79</v>
+        <v>1508.67</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6574,35 +6574,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.53</v>
+        <v>201.07</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>214.03</v>
+        <v>213.96</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6693,35 +6693,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.68</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6828,7 +6828,7 @@
         <v>9770</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>10010</v>
+        <v>9820</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -7101,7 +7101,7 @@
         <v>10929</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>9993.299999999999</v>
+        <v>9955</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8485,36 +8485,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>0.002033772</v>
+        <v>0.001339457</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.005593081</v>
+        <v>0.004677872</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.005797321</v>
+        <v>-0.002922923</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>127.910429851</v>
+        <v>127.90976647</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.004425839</v>
+        <v>0.005681342</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.003098323</v>
+        <v>-0.005873596</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.002834464</v>
+        <v>0.006500226</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>127.915783462</v>
+        <v>127.906921261</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.006104253</v>
+        <v>-0.002747917</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.003754116</v>
+        <v>0.007158055</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -8613,36 +8613,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>0.005232613</v>
+        <v>0.002658042</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>-0.002769128</v>
+        <v>0.003724336</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.006267861</v>
+        <v>-0.002874927</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>127.910784746</v>
+        <v>127.908096842</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.000729353</v>
+        <v>-0.008574362</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.004634267</v>
+        <v>0.004369471</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.002441023</v>
+        <v>-0.005083969</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>127.921373151</v>
+        <v>127.911812662</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.002162586</v>
+        <v>0.002638505</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.007837136</v>
+        <v>-0.012683857</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -8882,23 +8882,23 @@
         <v>0.003574653</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>-0.111355438</v>
+        <v>-0.111346351</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>-0.171118019</v>
+        <v>-0.171116269</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>-0.149636702</v>
+        <v>-0.14962252</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>-0.005657668</v>
+        <v>-0.005657503</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>-0.189924573</v>
+        <v>-0.189904442</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>-0.318181</v>
+        <v>-0.3181458</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -9013,20 +9013,20 @@
         <v>0.069162265</v>
       </c>
       <c r="AI33" s="32" t="n">
-        <v>0.088336052</v>
+        <v>0.088330773</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="32" t="n">
-        <v>0.058831518</v>
+        <v>0.058826953</v>
       </c>
       <c r="AL33" s="32" t="n">
-        <v>0.001786434</v>
+        <v>0.00178645</v>
       </c>
       <c r="AM33" s="32" t="n">
-        <v>0.059523918</v>
+        <v>0.059524463</v>
       </c>
       <c r="AN33" s="32" t="n">
-        <v>0.076242879</v>
+        <v>0.076239222</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9988,33 +9988,33 @@
         <v>-0.012566686</v>
       </c>
       <c r="AD41" s="32" t="n">
-        <v>0.24021912</v>
+        <v>0.240148436</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="32" t="n">
-        <v>0.157313405</v>
+        <v>0.157172401</v>
       </c>
       <c r="AG41" s="32" t="n">
-        <v>-0.012262899</v>
+        <v>-0.012478038</v>
       </c>
       <c r="AH41" s="32" t="n">
-        <v>0.180613919</v>
+        <v>0.180333774</v>
       </c>
       <c r="AI41" s="32" t="n">
-        <v>0.175367605</v>
+        <v>0.175092619</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="32" t="n">
-        <v>0.203711977</v>
+        <v>0.203533712</v>
       </c>
       <c r="AL41" s="32" t="n">
-        <v>0.235960359</v>
+        <v>0.235939145</v>
       </c>
       <c r="AM41" s="32" t="n">
-        <v>0.255830508</v>
+        <v>0.255857322</v>
       </c>
       <c r="AN41" s="32" t="n">
-        <v>0.248533191</v>
+        <v>0.248654023</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -10134,39 +10134,39 @@
         <v>0.188177852</v>
       </c>
       <c r="AD42" s="32" t="n">
-        <v>0.188191041</v>
+        <v>0.188201767</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="32" t="n">
-        <v>0.188725988</v>
+        <v>0.188748985</v>
       </c>
       <c r="AG42" s="32" t="n">
-        <v>0.188586779</v>
+        <v>0.188591554</v>
       </c>
       <c r="AH42" s="32" t="n">
-        <v>0.188169492</v>
+        <v>0.18814634</v>
       </c>
       <c r="AI42" s="32" t="n">
-        <v>0.18821219</v>
+        <v>0.18821846</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="32" t="n">
-        <v>0.188704072</v>
+        <v>0.188721272</v>
       </c>
       <c r="AL42" s="32" t="n">
-        <v>0.188562869</v>
+        <v>0.188577808</v>
       </c>
       <c r="AM42" s="32" t="n">
-        <v>0.188166383</v>
+        <v>0.188153028</v>
       </c>
       <c r="AN42" s="32" t="n">
-        <v>0.188205138</v>
+        <v>0.188202847</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO39,"")</f>
@@ -10289,39 +10289,39 @@
         <v>-0.625165086</v>
       </c>
       <c r="AD43" s="32" t="n">
-        <v>-0.625156731</v>
+        <v>-0.625163864</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF43" s="32" t="n">
-        <v>-0.62514722</v>
+        <v>-0.625142161</v>
       </c>
       <c r="AG43" s="32" t="n">
-        <v>-0.625149744</v>
+        <v>-0.625140699</v>
       </c>
       <c r="AH43" s="32" t="n">
-        <v>-0.625152542</v>
+        <v>-0.625165293</v>
       </c>
       <c r="AI43" s="32" t="n">
-        <v>-0.62515153</v>
+        <v>-0.6251637</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK43" s="32" t="n">
-        <v>-0.625156044</v>
+        <v>-0.625156087</v>
       </c>
       <c r="AL43" s="32" t="n">
-        <v>-0.6251652130000001</v>
+        <v>-0.6251652519999999</v>
       </c>
       <c r="AM43" s="32" t="n">
-        <v>-0.625151834</v>
+        <v>-0.625151867</v>
       </c>
       <c r="AN43" s="32" t="n">
-        <v>-0.625162631</v>
+        <v>-0.625148096</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -10444,39 +10444,39 @@
         <v>0.140323923</v>
       </c>
       <c r="AD44" s="32" t="n">
-        <v>0.143449722</v>
+        <v>0.143456261</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE42/subQ!AE41,"")</f>
         <v/>
       </c>
       <c r="AF44" s="32" t="n">
-        <v>0.142142532</v>
+        <v>0.142225976</v>
       </c>
       <c r="AG44" s="32" t="n">
-        <v>0.144707044</v>
+        <v>0.144682581</v>
       </c>
       <c r="AH44" s="32" t="n">
-        <v>0.148790804</v>
+        <v>0.148768847</v>
       </c>
       <c r="AI44" s="32" t="n">
-        <v>0.151289509</v>
+        <v>0.151291799</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ42/subQ!AJ41,"")</f>
         <v/>
       </c>
       <c r="AK44" s="32" t="n">
-        <v>0.151438286</v>
+        <v>0.151425178</v>
       </c>
       <c r="AL44" s="32" t="n">
-        <v>0.15470989</v>
+        <v>0.154746241</v>
       </c>
       <c r="AM44" s="32" t="n">
-        <v>0.158937824</v>
+        <v>0.158928957</v>
       </c>
       <c r="AN44" s="32" t="n">
-        <v>0.160713176</v>
+        <v>0.16071706</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO42/subQ!AO41,"")</f>
@@ -10547,11 +10547,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>10010</v>
+        <v>9820</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 9,970원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,020원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.191150998908556</v>
+        <v>0.1911555344643492</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.06131748845681975</v>
+        <v>0.06131794015701576</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.8217632995497146</v>
+        <v>0.8217460177769955</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.03608993984517214</v>
+        <v>0.03609090415933141</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03869520913211543</v>
+        <v>0.03869582903030195</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-06</t>
+          <t>UPDATE: 26-10-07</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36428,7 +36428,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42073,7 +42073,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261006</t>
+          <t>20261007</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.48</v>
+        <v>13.23</v>
       </c>
     </row>
     <row r="32">
@@ -44399,7 +44399,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -4989,7 +4989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-07</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20937,7 +20937,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-07</t>
+          <t>UPDATE: 26-10-08</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -5860,35 +5860,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1348.08</v>
+        <v>1346.2</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.99</v>
+        <v>1458.38</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5979,35 +5979,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.78</v>
+        <v>1338.69</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6098,35 +6098,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>853.26</v>
+        <v>851.8099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>920.3099999999999</v>
+        <v>919.9299999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6217,35 +6217,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.85</v>
+        <v>846.04</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6336,35 +6336,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1516.47</v>
+        <v>1512.43</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1692.86</v>
+        <v>1691.86</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6455,35 +6455,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1508.67</v>
+        <v>1496.26</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6574,35 +6574,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>201.07</v>
+        <v>200.79</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.96</v>
+        <v>213.89</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6693,35 +6693,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.68</v>
+        <v>199.67</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6828,7 +6828,7 @@
         <v>9770</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>9820</v>
+        <v>9310</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -7010,7 +7010,7 @@
         <v>8500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>9610</v>
+        <v>9290</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -7101,7 +7101,7 @@
         <v>10929</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>9955</v>
+        <v>9826</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8485,36 +8485,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>0.001339457</v>
+        <v>0.001335022</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.004677872</v>
+        <v>0.004677742</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>-0.002922923</v>
+        <v>-0.00291662</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>127.90976647</v>
+        <v>127.909777243</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.005681342</v>
+        <v>0.005691791</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>-0.005873596</v>
+        <v>-0.00593104</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>0.006500226</v>
+        <v>0.006522139</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>127.906921261</v>
+        <v>127.906947917</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>-0.002747917</v>
+        <v>0.007278873</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>0.007158055</v>
+        <v>-0.002883059</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -8613,36 +8613,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>0.002658042</v>
+        <v>0.002654398</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.003724336</v>
+        <v>0.003724228</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.002874927</v>
+        <v>-0.002869747</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>127.908096842</v>
+        <v>127.908105695</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.008574362</v>
+        <v>-0.008565776000000001</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.004369471</v>
+        <v>0.004322267</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.005083969</v>
+        <v>-0.005065962</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>127.911812662</v>
+        <v>127.911834566</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.002638505</v>
+        <v>0.002660519</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>-0.012683857</v>
+        <v>-0.002717642</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -8876,26 +8876,26 @@
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="32" t="n">
-        <v>-0.094459125</v>
+        <v>-0.09445086699999999</v>
       </c>
       <c r="AG32" s="32" t="n">
-        <v>0.003574653</v>
+        <v>0.003565501</v>
       </c>
       <c r="AH32" s="32" t="n">
         <v>-0.111346351</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>-0.171116269</v>
+        <v>-0.171106044</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>-0.14962252</v>
+        <v>-0.149633011</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>-0.005657503</v>
+        <v>-0.005642997</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>-0.189904442</v>
+        <v>-0.189916261</v>
       </c>
       <c r="AN32" s="32" t="n">
         <v>-0.3181458</v>
@@ -9010,10 +9010,10 @@
         <v>-0.002207406</v>
       </c>
       <c r="AH33" s="32" t="n">
-        <v>0.069162265</v>
+        <v>0.069156621</v>
       </c>
       <c r="AI33" s="32" t="n">
-        <v>0.088330773</v>
+        <v>0.088336518</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="32" t="n">
@@ -9023,10 +9023,10 @@
         <v>0.00178645</v>
       </c>
       <c r="AM33" s="32" t="n">
-        <v>0.059524463</v>
+        <v>0.05951989</v>
       </c>
       <c r="AN33" s="32" t="n">
-        <v>0.076239222</v>
+        <v>0.076239551</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9988,33 +9988,33 @@
         <v>-0.012566686</v>
       </c>
       <c r="AD41" s="32" t="n">
-        <v>0.240148436</v>
+        <v>0.240113094</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="32" t="n">
         <v>0.157172401</v>
       </c>
       <c r="AG41" s="32" t="n">
-        <v>-0.012478038</v>
+        <v>-0.012513894</v>
       </c>
       <c r="AH41" s="32" t="n">
-        <v>0.180333774</v>
+        <v>0.180253732</v>
       </c>
       <c r="AI41" s="32" t="n">
-        <v>0.175092619</v>
+        <v>0.175097609</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="32" t="n">
         <v>0.203533712</v>
       </c>
       <c r="AL41" s="32" t="n">
-        <v>0.235939145</v>
+        <v>0.235984023</v>
       </c>
       <c r="AM41" s="32" t="n">
-        <v>0.255857322</v>
+        <v>0.255942491</v>
       </c>
       <c r="AN41" s="32" t="n">
-        <v>0.248654023</v>
+        <v>0.248684306</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -10134,7 +10134,7 @@
         <v>0.188177852</v>
       </c>
       <c r="AD42" s="32" t="n">
-        <v>0.188201767</v>
+        <v>0.18820713</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE39,"")</f>
@@ -10144,13 +10144,13 @@
         <v>0.188748985</v>
       </c>
       <c r="AG42" s="32" t="n">
-        <v>0.188591554</v>
+        <v>0.188598402</v>
       </c>
       <c r="AH42" s="32" t="n">
-        <v>0.18814634</v>
+        <v>0.188159099</v>
       </c>
       <c r="AI42" s="32" t="n">
-        <v>0.18821846</v>
+        <v>0.188223025</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
@@ -10289,7 +10289,7 @@
         <v>-0.625165086</v>
       </c>
       <c r="AD43" s="32" t="n">
-        <v>-0.625163864</v>
+        <v>-0.625153182</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
@@ -10299,13 +10299,13 @@
         <v>-0.625142161</v>
       </c>
       <c r="AG43" s="32" t="n">
-        <v>-0.625140699</v>
+        <v>-0.625163399</v>
       </c>
       <c r="AH43" s="32" t="n">
-        <v>-0.625165293</v>
+        <v>-0.625139873</v>
       </c>
       <c r="AI43" s="32" t="n">
-        <v>-0.6251637</v>
+        <v>-0.625154609</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
@@ -10444,7 +10444,7 @@
         <v>0.140323923</v>
       </c>
       <c r="AD44" s="32" t="n">
-        <v>0.143456261</v>
+        <v>0.143462801</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE42/subQ!AE41,"")</f>
@@ -10457,10 +10457,10 @@
         <v>0.144682581</v>
       </c>
       <c r="AH44" s="32" t="n">
-        <v>0.148768847</v>
+        <v>0.148784986</v>
       </c>
       <c r="AI44" s="32" t="n">
-        <v>0.151291799</v>
+        <v>0.151297668</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ42/subQ!AJ41,"")</f>
@@ -10547,11 +10547,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>9820</v>
+        <v>9310</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,020원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,010원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.06131794015701576</v>
+        <v>0.06131805761342098</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.03609090415933141</v>
+        <v>0.03609109701823326</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03869582903030195</v>
+        <v>0.03869594437146839</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -36428,7 +36428,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42073,7 +42073,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261007</t>
+          <t>20261008</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -44389,7 +44389,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.23</v>
+        <v>12.54</v>
       </c>
     </row>
     <row r="32">
@@ -44399,7 +44399,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.27</v>
+        <v>2.15</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="README" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="변수" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="subQ" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="분기" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TP" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="외화" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="README" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="변수" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="BS연결" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="BS별도" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="subQ" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="분기" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="연간예상" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="TP" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="외화" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="변수H">변수!$C$1:$AO$1</definedName>
@@ -23,7 +23,7 @@
     <definedName name="BS연결H">BS연결!$C$1:$AO$1</definedName>
     <definedName name="BS연결">BS연결!$C$5:$AO$110</definedName>
     <definedName name="BS별도H">BS별도!$C$1:$AO$1</definedName>
-    <definedName name="BS별도">BS별도!$C$5:$AO$96</definedName>
+    <definedName name="BS별도">BS별도!$C$5:$AO$95</definedName>
     <definedName name="SUBQH">subQ!$A$1:$AO$1</definedName>
     <definedName name="subQ">subQ!$A$5:$AO$46</definedName>
   </definedNames>
@@ -5860,35 +5860,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1346.2</v>
+        <v>1345.74</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1458.38</v>
+        <v>1457.79</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5979,35 +5979,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1338.69</v>
+        <v>1343.46</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6098,35 +6098,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.8099999999999</v>
+        <v>851.3099999999999</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.9299999999999</v>
+        <v>919.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6217,35 +6217,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>846.04</v>
+        <v>848.79</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6336,35 +6336,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1512.43</v>
+        <v>1510.82</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1691.86</v>
+        <v>1690.9</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6455,35 +6455,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1496.26</v>
+        <v>1502.8</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6574,35 +6574,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.79</v>
+        <v>200.73</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.89</v>
+        <v>213.82</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6693,35 +6693,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.67</v>
+        <v>200.45</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8485,36 +8485,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.003385375</v>
+        <v>-0.004572831</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.005055082</v>
+        <v>0.00339074</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.002119117</v>
+        <v>0.0008957700000000001</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>127.915474948</v>
+        <v>127.904129595</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.003364192</v>
+        <v>0.002107971</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.003167593</v>
+        <v>0.009509101000000001</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>0.001032483</v>
+        <v>-0.002175437</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>127.908680938</v>
+        <v>127.915413511</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>5.1639e-05</v>
+        <v>0.006800535</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>0.003028113</v>
+        <v>-0.000733468</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -8613,36 +8613,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.00471141</v>
+        <v>-0.007632917</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.010549925</v>
+        <v>0.006506994</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.000626901</v>
+        <v>-0.002298533</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>127.912300379</v>
+        <v>127.909113587</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.006140369</v>
+        <v>-0.006948149</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.003039445</v>
+        <v>-0.000634592</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.006627857</v>
+        <v>0.000175846</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>127.906761845</v>
+        <v>127.910085166</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.000198454</v>
+        <v>0.003562679</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.001709757</v>
+        <v>0.003875063</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -8882,23 +8882,23 @@
         <v>0.003511428</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>-0.111399929</v>
+        <v>-0.111409018</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>-0.171095428</v>
+        <v>-0.171097178</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>-0.149564423</v>
+        <v>-0.149578608</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>-0.00548454</v>
+        <v>-0.005484699</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>-0.189734911</v>
+        <v>-0.189740447</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>-0.317818431</v>
+        <v>-0.317847882</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -9007,26 +9007,26 @@
         <v>0.068886655</v>
       </c>
       <c r="AG33" s="32" t="n">
-        <v>-0.002167756</v>
+        <v>-0.002162126</v>
       </c>
       <c r="AH33" s="32" t="n">
-        <v>0.069163403</v>
+        <v>0.069163013</v>
       </c>
       <c r="AI33" s="32" t="n">
-        <v>0.088286054</v>
+        <v>0.088285588</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="32" t="n">
-        <v>0.05878188</v>
+        <v>0.058786444</v>
       </c>
       <c r="AL33" s="32" t="n">
-        <v>0.001731372</v>
+        <v>0.001731356</v>
       </c>
       <c r="AM33" s="32" t="n">
-        <v>0.059464477</v>
+        <v>0.059463933</v>
       </c>
       <c r="AN33" s="32" t="n">
-        <v>0.076178104</v>
+        <v>0.076181762</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9992,29 +9992,29 @@
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="32" t="n">
-        <v>0.163799586</v>
+        <v>0.163893589</v>
       </c>
       <c r="AG41" s="32" t="n">
-        <v>-0.00752985</v>
+        <v>-0.007422281</v>
       </c>
       <c r="AH41" s="32" t="n">
-        <v>0.179197445</v>
+        <v>0.179437013</v>
       </c>
       <c r="AI41" s="32" t="n">
-        <v>0.165593898</v>
+        <v>0.165934159</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="32" t="n">
-        <v>0.189855014</v>
+        <v>0.190041594</v>
       </c>
       <c r="AL41" s="32" t="n">
-        <v>0.221323025</v>
+        <v>0.221479662</v>
       </c>
       <c r="AM41" s="32" t="n">
-        <v>0.245691261</v>
+        <v>0.245742916</v>
       </c>
       <c r="AN41" s="32" t="n">
-        <v>0.245554285</v>
+        <v>0.245433984</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -10141,32 +10141,32 @@
         <v/>
       </c>
       <c r="AF42" s="32" t="n">
-        <v>0.188724203</v>
+        <v>0.188708961</v>
       </c>
       <c r="AG42" s="32" t="n">
-        <v>0.188590628</v>
+        <v>0.18857019</v>
       </c>
       <c r="AH42" s="32" t="n">
-        <v>0.188162395</v>
+        <v>0.188158028</v>
       </c>
       <c r="AI42" s="32" t="n">
-        <v>0.188216119</v>
+        <v>0.18820983</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="32" t="n">
-        <v>0.188751612</v>
+        <v>0.188706777</v>
       </c>
       <c r="AL42" s="32" t="n">
-        <v>0.188581571</v>
+        <v>0.188566528</v>
       </c>
       <c r="AM42" s="32" t="n">
-        <v>0.188154068</v>
+        <v>0.188135225</v>
       </c>
       <c r="AN42" s="32" t="n">
-        <v>0.188199449</v>
+        <v>0.188201754</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO39,"")</f>
@@ -10296,32 +10296,32 @@
         <v/>
       </c>
       <c r="AF43" s="32" t="n">
-        <v>-0.625136303</v>
+        <v>-0.6251665789999999</v>
       </c>
       <c r="AG43" s="32" t="n">
-        <v>-0.625167094</v>
+        <v>-0.6251715920000001</v>
       </c>
       <c r="AH43" s="32" t="n">
-        <v>-0.62516507</v>
+        <v>-0.625139646</v>
       </c>
       <c r="AI43" s="32" t="n">
-        <v>-0.625149001</v>
+        <v>-0.625161118</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK43" s="32" t="n">
-        <v>-0.625144254</v>
+        <v>-0.625165428</v>
       </c>
       <c r="AL43" s="32" t="n">
-        <v>-0.625144209</v>
+        <v>-0.625144175</v>
       </c>
       <c r="AM43" s="32" t="n">
-        <v>-0.625159694</v>
+        <v>-0.625142671</v>
       </c>
       <c r="AN43" s="32" t="n">
-        <v>-0.625163571</v>
+        <v>-0.625158657</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -10451,32 +10451,32 @@
         <v/>
       </c>
       <c r="AF44" s="32" t="n">
-        <v>0.142515666</v>
+        <v>0.142497255</v>
       </c>
       <c r="AG44" s="32" t="n">
-        <v>0.144937587</v>
+        <v>0.144920837</v>
       </c>
       <c r="AH44" s="32" t="n">
-        <v>0.148838217</v>
+        <v>0.14886819</v>
       </c>
       <c r="AI44" s="32" t="n">
-        <v>0.151140167</v>
+        <v>0.151132031</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ42/subQ!AJ41,"")</f>
         <v/>
       </c>
       <c r="AK44" s="32" t="n">
-        <v>0.151210772</v>
+        <v>0.151115454</v>
       </c>
       <c r="AL44" s="32" t="n">
-        <v>0.154450386</v>
+        <v>0.154413852</v>
       </c>
       <c r="AM44" s="32" t="n">
-        <v>0.158659072</v>
+        <v>0.158624587</v>
       </c>
       <c r="AN44" s="32" t="n">
-        <v>0.160486113</v>
+        <v>0.160487272</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO42/subQ!AO41,"")</f>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 10,010원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 9,810원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.1911550943642502</v>
+        <v>0.1911635578337843</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.06131586560475753</v>
+        <v>0.06131744718026529</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.8217620608968011</v>
+        <v>0.8217452854407958</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.03609739549956988</v>
+        <v>0.03609646464754426</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03869755028888258</v>
+        <v>0.03869698415983145</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -20715,7 +20715,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AO96"/>
+  <dimension ref="A1:AO95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -24172,19 +24172,16 @@
         </is>
       </c>
       <c r="E37" s="18" t="n">
-        <v>92300</v>
+        <v>107300</v>
       </c>
       <c r="F37" s="37" t="n">
-        <v>92300</v>
+        <v>107300</v>
       </c>
       <c r="G37" s="18" t="n">
-        <v>121700</v>
+        <v>136700</v>
       </c>
       <c r="H37" s="18" t="n">
         <v>101100</v>
-      </c>
-      <c r="I37" s="18" t="n">
-        <v>61300</v>
       </c>
       <c r="J37" s="18" t="n">
         <v>73700</v>
@@ -24263,80 +24260,77 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>비유동리스부채</t>
+          <t>장기금융부채(face)</t>
         </is>
       </c>
       <c r="E38" s="18" t="n">
-        <v>2666.33</v>
+        <v>107300</v>
       </c>
       <c r="F38" s="37" t="n">
-        <v>2666.33</v>
+        <v>107300</v>
       </c>
       <c r="G38" s="18" t="n">
-        <v>2556.18</v>
+        <v>136700</v>
       </c>
       <c r="H38" s="18" t="n">
-        <v>2711.63</v>
-      </c>
-      <c r="I38" s="18" t="n">
-        <v>2532.91</v>
+        <v>101100</v>
       </c>
       <c r="J38" s="18" t="n">
-        <v>2353.03</v>
+        <v>73700</v>
       </c>
       <c r="K38" s="37" t="n">
-        <v>2353.03</v>
+        <v>73700</v>
       </c>
       <c r="L38" s="18" t="n">
-        <v>2188.72</v>
+        <v>28700</v>
       </c>
       <c r="M38" s="18" t="n">
-        <v>2149.27</v>
+        <v>17500</v>
       </c>
       <c r="N38" s="18" t="n">
-        <v>2016.76</v>
+        <v>43900</v>
       </c>
       <c r="O38" s="18" t="n">
-        <v>1800.41</v>
+        <v>43300</v>
       </c>
       <c r="P38" s="37" t="n">
-        <v>1800.41</v>
+        <v>43300</v>
       </c>
       <c r="Q38" s="18" t="n">
-        <v>1215.87</v>
+        <v>42700</v>
       </c>
       <c r="R38" s="18" t="n">
-        <v>1155.66</v>
+        <v>42100</v>
       </c>
       <c r="S38" s="18" t="n">
-        <v>1120.13</v>
+        <v>25900</v>
       </c>
       <c r="T38" s="18" t="n">
-        <v>1104.89</v>
+        <v>30650</v>
       </c>
       <c r="U38" s="37" t="n">
-        <v>1104.89</v>
+        <v>30650</v>
       </c>
       <c r="V38" s="18" t="n">
-        <v>5447.33</v>
+        <v>29600</v>
       </c>
       <c r="W38" s="18" t="n">
-        <v>5020.72</v>
+        <v>28550</v>
       </c>
       <c r="X38" s="18" t="n">
-        <v>4593.82</v>
+        <v>106500</v>
       </c>
       <c r="Y38" s="18" t="n">
-        <v>4332.65</v>
+        <v>106200</v>
       </c>
       <c r="Z38" s="37" t="n">
-        <v>4332.65</v>
+        <v>106200</v>
       </c>
       <c r="AA38" s="18" t="n">
-        <v>3721.81</v>
+        <v>106200</v>
       </c>
       <c r="AB38" s="19" t="n">
-        <v>3107.73</v>
+        <v>106200</v>
       </c>
       <c r="AC38" s="10" t="n"/>
       <c r="AD38" s="10" t="n"/>
@@ -24358,7 +24352,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>장기금융부채</t>
+          <t>비유동리스부채</t>
         </is>
       </c>
       <c r="E39" s="18" t="n">
@@ -24453,80 +24447,80 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>기타비유동부채</t>
+          <t>장기금융부채</t>
         </is>
       </c>
       <c r="E40" s="18" t="n">
-        <v>576.55</v>
+        <v>2666.33</v>
       </c>
       <c r="F40" s="37" t="n">
-        <v>576.55</v>
+        <v>2666.33</v>
       </c>
       <c r="G40" s="18" t="n">
-        <v>541.6799999999999</v>
+        <v>2556.18</v>
       </c>
       <c r="H40" s="18" t="n">
-        <v>472.69</v>
+        <v>2711.63</v>
       </c>
       <c r="I40" s="18" t="n">
-        <v>423.04</v>
+        <v>2532.91</v>
       </c>
       <c r="J40" s="18" t="n">
-        <v>306.58</v>
+        <v>2353.03</v>
       </c>
       <c r="K40" s="37" t="n">
-        <v>306.58</v>
+        <v>2353.03</v>
       </c>
       <c r="L40" s="18" t="n">
-        <v>300.9</v>
+        <v>2188.72</v>
       </c>
       <c r="M40" s="18" t="n">
-        <v>295.36</v>
+        <v>2149.27</v>
       </c>
       <c r="N40" s="18" t="n">
-        <v>294.05</v>
+        <v>2016.76</v>
       </c>
       <c r="O40" s="18" t="n">
-        <v>253.15</v>
+        <v>1800.41</v>
       </c>
       <c r="P40" s="37" t="n">
-        <v>253.15</v>
+        <v>1800.41</v>
       </c>
       <c r="Q40" s="18" t="n">
-        <v>249.44</v>
+        <v>1215.87</v>
       </c>
       <c r="R40" s="18" t="n">
-        <v>336.21</v>
+        <v>1155.66</v>
       </c>
       <c r="S40" s="18" t="n">
-        <v>347.1</v>
+        <v>1120.13</v>
       </c>
       <c r="T40" s="18" t="n">
-        <v>470.38</v>
+        <v>1104.89</v>
       </c>
       <c r="U40" s="37" t="n">
-        <v>470.38</v>
+        <v>1104.89</v>
       </c>
       <c r="V40" s="18" t="n">
-        <v>489.33</v>
+        <v>5447.33</v>
       </c>
       <c r="W40" s="18" t="n">
-        <v>490.52</v>
+        <v>5020.72</v>
       </c>
       <c r="X40" s="18" t="n">
-        <v>499.5</v>
+        <v>4593.82</v>
       </c>
       <c r="Y40" s="18" t="n">
-        <v>393.95</v>
+        <v>4332.65</v>
       </c>
       <c r="Z40" s="37" t="n">
-        <v>393.95</v>
+        <v>4332.65</v>
       </c>
       <c r="AA40" s="18" t="n">
-        <v>381.05</v>
+        <v>3721.81</v>
       </c>
       <c r="AB40" s="19" t="n">
-        <v>378.11</v>
+        <v>3107.73</v>
       </c>
       <c r="AC40" s="10" t="n"/>
       <c r="AD40" s="10" t="n"/>
@@ -24548,80 +24542,80 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>확정급여부채</t>
+          <t>기타비유동부채</t>
         </is>
       </c>
       <c r="E41" s="18" t="n">
-        <v>2490.97</v>
+        <v>576.55</v>
       </c>
       <c r="F41" s="37" t="n">
-        <v>2490.97</v>
+        <v>576.55</v>
       </c>
       <c r="G41" s="18" t="n">
-        <v>2743.24</v>
+        <v>541.6799999999999</v>
       </c>
       <c r="H41" s="18" t="n">
-        <v>2711.17</v>
+        <v>472.69</v>
       </c>
       <c r="I41" s="18" t="n">
-        <v>3186.96</v>
+        <v>423.04</v>
       </c>
       <c r="J41" s="18" t="n">
-        <v>1726.49</v>
+        <v>306.58</v>
       </c>
       <c r="K41" s="37" t="n">
-        <v>1726.49</v>
+        <v>306.58</v>
       </c>
       <c r="L41" s="18" t="n">
-        <v>2744</v>
+        <v>300.9</v>
       </c>
       <c r="M41" s="18" t="n">
-        <v>2928.49</v>
+        <v>295.36</v>
       </c>
       <c r="N41" s="18" t="n">
-        <v>2994.37</v>
+        <v>294.05</v>
       </c>
       <c r="O41" s="18" t="n">
-        <v>5145.29</v>
+        <v>253.15</v>
       </c>
       <c r="P41" s="37" t="n">
-        <v>5145.29</v>
+        <v>253.15</v>
       </c>
       <c r="Q41" s="18" t="n">
-        <v>5268.77</v>
+        <v>249.44</v>
       </c>
       <c r="R41" s="18" t="n">
-        <v>5833.58</v>
+        <v>336.21</v>
       </c>
       <c r="S41" s="18" t="n">
-        <v>6261.26</v>
+        <v>347.1</v>
       </c>
       <c r="T41" s="18" t="n">
-        <v>3728.08</v>
+        <v>470.38</v>
       </c>
       <c r="U41" s="37" t="n">
-        <v>3728.08</v>
+        <v>470.38</v>
       </c>
       <c r="V41" s="18" t="n">
-        <v>4572.68</v>
+        <v>489.33</v>
       </c>
       <c r="W41" s="18" t="n">
-        <v>4846.95</v>
+        <v>490.52</v>
       </c>
       <c r="X41" s="18" t="n">
-        <v>4902.68</v>
+        <v>499.5</v>
       </c>
       <c r="Y41" s="18" t="n">
-        <v>5105.12</v>
+        <v>393.95</v>
       </c>
       <c r="Z41" s="37" t="n">
-        <v>5105.12</v>
+        <v>393.95</v>
       </c>
       <c r="AA41" s="18" t="n">
-        <v>5716.04</v>
+        <v>381.05</v>
       </c>
       <c r="AB41" s="19" t="n">
-        <v>6074.78</v>
+        <v>378.11</v>
       </c>
       <c r="AC41" s="10" t="n"/>
       <c r="AD41" s="10" t="n"/>
@@ -24643,80 +24637,80 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>부채총계</t>
+          <t>확정급여부채</t>
         </is>
       </c>
       <c r="E42" s="18" t="n">
-        <v>284138.67</v>
+        <v>2490.97</v>
       </c>
       <c r="F42" s="37" t="n">
-        <v>284138.67</v>
+        <v>2490.97</v>
       </c>
       <c r="G42" s="18" t="n">
-        <v>281201.52</v>
+        <v>2743.24</v>
       </c>
       <c r="H42" s="18" t="n">
-        <v>256220.04</v>
+        <v>2711.17</v>
       </c>
       <c r="I42" s="18" t="n">
-        <v>253900.45</v>
+        <v>3186.96</v>
       </c>
       <c r="J42" s="18" t="n">
-        <v>246366.02</v>
+        <v>1726.49</v>
       </c>
       <c r="K42" s="37" t="n">
-        <v>246366.02</v>
+        <v>1726.49</v>
       </c>
       <c r="L42" s="18" t="n">
-        <v>261270.02</v>
+        <v>2744</v>
       </c>
       <c r="M42" s="18" t="n">
-        <v>230547.37</v>
+        <v>2928.49</v>
       </c>
       <c r="N42" s="18" t="n">
-        <v>255094.06</v>
+        <v>2994.37</v>
       </c>
       <c r="O42" s="18" t="n">
-        <v>242199.22</v>
+        <v>5145.29</v>
       </c>
       <c r="P42" s="37" t="n">
-        <v>242199.22</v>
+        <v>5145.29</v>
       </c>
       <c r="Q42" s="18" t="n">
-        <v>276054.89</v>
+        <v>5268.77</v>
       </c>
       <c r="R42" s="18" t="n">
-        <v>247215.63</v>
+        <v>5833.58</v>
       </c>
       <c r="S42" s="18" t="n">
-        <v>283176.88</v>
+        <v>6261.26</v>
       </c>
       <c r="T42" s="18" t="n">
-        <v>292617.62</v>
+        <v>3728.08</v>
       </c>
       <c r="U42" s="37" t="n">
-        <v>292617.62</v>
+        <v>3728.08</v>
       </c>
       <c r="V42" s="18" t="n">
-        <v>300107.52</v>
+        <v>4572.68</v>
       </c>
       <c r="W42" s="18" t="n">
-        <v>291133.08</v>
+        <v>4846.95</v>
       </c>
       <c r="X42" s="18" t="n">
-        <v>294969.17</v>
+        <v>4902.68</v>
       </c>
       <c r="Y42" s="18" t="n">
-        <v>261292.72</v>
+        <v>5105.12</v>
       </c>
       <c r="Z42" s="37" t="n">
-        <v>261292.72</v>
+        <v>5105.12</v>
       </c>
       <c r="AA42" s="18" t="n">
-        <v>271244.07</v>
+        <v>5716.04</v>
       </c>
       <c r="AB42" s="19" t="n">
-        <v>258069.67</v>
+        <v>6074.78</v>
       </c>
       <c r="AC42" s="10" t="n"/>
       <c r="AD42" s="10" t="n"/>
@@ -24738,80 +24732,80 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>자본금</t>
+          <t>부채총계</t>
         </is>
       </c>
       <c r="E43" s="18" t="n">
-        <v>31224.73</v>
+        <v>284138.67</v>
       </c>
       <c r="F43" s="37" t="n">
-        <v>31224.73</v>
+        <v>284138.67</v>
       </c>
       <c r="G43" s="18" t="n">
-        <v>31224.73</v>
+        <v>281201.52</v>
       </c>
       <c r="H43" s="18" t="n">
-        <v>31224.73</v>
+        <v>256220.04</v>
       </c>
       <c r="I43" s="18" t="n">
-        <v>31224.73</v>
+        <v>253900.45</v>
       </c>
       <c r="J43" s="18" t="n">
-        <v>31224.73</v>
+        <v>246366.02</v>
       </c>
       <c r="K43" s="37" t="n">
-        <v>31224.73</v>
+        <v>246366.02</v>
       </c>
       <c r="L43" s="18" t="n">
-        <v>31224.73</v>
+        <v>261270.02</v>
       </c>
       <c r="M43" s="18" t="n">
-        <v>31224.73</v>
+        <v>230547.37</v>
       </c>
       <c r="N43" s="18" t="n">
-        <v>31224.73</v>
+        <v>255094.06</v>
       </c>
       <c r="O43" s="18" t="n">
-        <v>31224.73</v>
+        <v>242199.22</v>
       </c>
       <c r="P43" s="37" t="n">
-        <v>31224.73</v>
+        <v>242199.22</v>
       </c>
       <c r="Q43" s="18" t="n">
-        <v>31224.73</v>
+        <v>276054.89</v>
       </c>
       <c r="R43" s="18" t="n">
-        <v>31224.73</v>
+        <v>247215.63</v>
       </c>
       <c r="S43" s="18" t="n">
-        <v>31224.73</v>
+        <v>283176.88</v>
       </c>
       <c r="T43" s="18" t="n">
-        <v>31224.73</v>
+        <v>292617.62</v>
       </c>
       <c r="U43" s="37" t="n">
-        <v>31224.73</v>
+        <v>292617.62</v>
       </c>
       <c r="V43" s="18" t="n">
-        <v>31224.73</v>
+        <v>300107.52</v>
       </c>
       <c r="W43" s="18" t="n">
-        <v>31224.73</v>
+        <v>291133.08</v>
       </c>
       <c r="X43" s="18" t="n">
-        <v>31224.73</v>
+        <v>294969.17</v>
       </c>
       <c r="Y43" s="18" t="n">
-        <v>31224.73</v>
+        <v>261292.72</v>
       </c>
       <c r="Z43" s="37" t="n">
-        <v>31224.73</v>
+        <v>261292.72</v>
       </c>
       <c r="AA43" s="18" t="n">
-        <v>31224.73</v>
+        <v>271244.07</v>
       </c>
       <c r="AB43" s="19" t="n">
-        <v>31224.73</v>
+        <v>258069.67</v>
       </c>
       <c r="AC43" s="10" t="n"/>
       <c r="AD43" s="10" t="n"/>
@@ -24833,80 +24827,80 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>자본잉여금</t>
+          <t>자본금</t>
         </is>
       </c>
       <c r="E44" s="18" t="n">
-        <v>369.53</v>
+        <v>31224.73</v>
       </c>
       <c r="F44" s="37" t="n">
-        <v>369.53</v>
+        <v>31224.73</v>
       </c>
       <c r="G44" s="18" t="n">
-        <v>552.77</v>
+        <v>31224.73</v>
       </c>
       <c r="H44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="I44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="J44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="K44" s="37" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="L44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="M44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="N44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="O44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="P44" s="37" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="Q44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="R44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="S44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="T44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="U44" s="37" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="V44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="W44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="X44" s="18" t="n">
-        <v>143.83</v>
+        <v>31224.73</v>
       </c>
       <c r="Y44" s="18" t="n">
-        <v>1769.68</v>
+        <v>31224.73</v>
       </c>
       <c r="Z44" s="37" t="n">
-        <v>1769.68</v>
+        <v>31224.73</v>
       </c>
       <c r="AA44" s="18" t="n">
-        <v>1769.68</v>
+        <v>31224.73</v>
       </c>
       <c r="AB44" s="19" t="n">
-        <v>1769.68</v>
+        <v>31224.73</v>
       </c>
       <c r="AC44" s="10" t="n"/>
       <c r="AD44" s="10" t="n"/>
@@ -24928,71 +24922,81 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>기타자본</t>
+          <t>자본잉여금</t>
         </is>
       </c>
       <c r="E45" s="18" t="n">
-        <v>-8011.63</v>
+        <v>369.53</v>
       </c>
       <c r="F45" s="37" t="n">
-        <v>-8011.63</v>
+        <v>369.53</v>
       </c>
       <c r="G45" s="18" t="n">
-        <v>-7707.55</v>
+        <v>552.77</v>
       </c>
       <c r="H45" s="18" t="n">
-        <v>-7298.61</v>
+        <v>143.83</v>
       </c>
       <c r="I45" s="18" t="n">
-        <v>-7298.61</v>
+        <v>143.83</v>
       </c>
       <c r="J45" s="18" t="n">
-        <v>-7298.61</v>
+        <v>143.83</v>
       </c>
       <c r="K45" s="37" t="n">
-        <v>-7298.61</v>
+        <v>143.83</v>
       </c>
       <c r="L45" s="18" t="n">
-        <v>-7298.61</v>
+        <v>143.83</v>
       </c>
       <c r="M45" s="18" t="n">
-        <v>-7298.61</v>
+        <v>143.83</v>
       </c>
       <c r="N45" s="18" t="n">
-        <v>-7298.61</v>
+        <v>143.83</v>
       </c>
       <c r="O45" s="18" t="n">
-        <v>-7298.61</v>
+        <v>143.83</v>
       </c>
       <c r="P45" s="37" t="n">
-        <v>-7298.61</v>
+        <v>143.83</v>
       </c>
       <c r="Q45" s="18" t="n">
-        <v>1625.85</v>
+        <v>143.83</v>
       </c>
       <c r="R45" s="18" t="n">
-        <v>1625.85</v>
+        <v>143.83</v>
       </c>
       <c r="S45" s="18" t="n">
-        <v>1625.85</v>
+        <v>143.83</v>
       </c>
       <c r="T45" s="18" t="n">
-        <v>1625.85</v>
+        <v>143.83</v>
       </c>
       <c r="U45" s="37" t="n">
-        <v>1625.85</v>
+        <v>143.83</v>
       </c>
       <c r="V45" s="18" t="n">
-        <v>1625.85</v>
+        <v>143.83</v>
       </c>
       <c r="W45" s="18" t="n">
-        <v>1625.85</v>
+        <v>143.83</v>
       </c>
       <c r="X45" s="18" t="n">
-        <v>1625.85</v>
-      </c>
-      <c r="Z45" s="9" t="n"/>
-      <c r="AB45" s="5" t="n"/>
+        <v>143.83</v>
+      </c>
+      <c r="Y45" s="18" t="n">
+        <v>1769.68</v>
+      </c>
+      <c r="Z45" s="37" t="n">
+        <v>1769.68</v>
+      </c>
+      <c r="AA45" s="18" t="n">
+        <v>1769.68</v>
+      </c>
+      <c r="AB45" s="19" t="n">
+        <v>1769.68</v>
+      </c>
       <c r="AC45" s="10" t="n"/>
       <c r="AD45" s="10" t="n"/>
       <c r="AE45" s="11" t="n"/>
@@ -25013,81 +25017,71 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>기타포괄이익누계액</t>
+          <t>기타자본</t>
         </is>
       </c>
       <c r="E46" s="18" t="n">
-        <v>-33.42</v>
+        <v>-8011.63</v>
       </c>
       <c r="F46" s="37" t="n">
-        <v>-33.42</v>
+        <v>-8011.63</v>
       </c>
       <c r="G46" s="18" t="n">
-        <v>-33.42</v>
+        <v>-7707.55</v>
       </c>
       <c r="H46" s="18" t="n">
-        <v>-67.27</v>
+        <v>-7298.61</v>
       </c>
       <c r="I46" s="18" t="n">
-        <v>-33.42</v>
+        <v>-7298.61</v>
       </c>
       <c r="J46" s="18" t="n">
-        <v>-202.27</v>
+        <v>-7298.61</v>
       </c>
       <c r="K46" s="37" t="n">
-        <v>-202.27</v>
+        <v>-7298.61</v>
       </c>
       <c r="L46" s="18" t="n">
-        <v>-202.27</v>
+        <v>-7298.61</v>
       </c>
       <c r="M46" s="18" t="n">
-        <v>-202.27</v>
+        <v>-7298.61</v>
       </c>
       <c r="N46" s="18" t="n">
-        <v>-202.27</v>
+        <v>-7298.61</v>
       </c>
       <c r="O46" s="18" t="n">
-        <v>-202.27</v>
+        <v>-7298.61</v>
       </c>
       <c r="P46" s="37" t="n">
-        <v>-202.27</v>
+        <v>-7298.61</v>
       </c>
       <c r="Q46" s="18" t="n">
-        <v>-202.27</v>
+        <v>1625.85</v>
       </c>
       <c r="R46" s="18" t="n">
-        <v>-326.02</v>
+        <v>1625.85</v>
       </c>
       <c r="S46" s="18" t="n">
-        <v>-482.17</v>
+        <v>1625.85</v>
       </c>
       <c r="T46" s="18" t="n">
-        <v>-1850.85</v>
+        <v>1625.85</v>
       </c>
       <c r="U46" s="37" t="n">
-        <v>-1850.85</v>
+        <v>1625.85</v>
       </c>
       <c r="V46" s="18" t="n">
-        <v>-1374.51</v>
+        <v>1625.85</v>
       </c>
       <c r="W46" s="18" t="n">
-        <v>-1280.27</v>
+        <v>1625.85</v>
       </c>
       <c r="X46" s="18" t="n">
-        <v>-412.31</v>
-      </c>
-      <c r="Y46" s="18" t="n">
-        <v>-1001.23</v>
-      </c>
-      <c r="Z46" s="37" t="n">
-        <v>-1001.23</v>
-      </c>
-      <c r="AA46" s="18" t="n">
-        <v>-1864.07</v>
-      </c>
-      <c r="AB46" s="19" t="n">
-        <v>-1635.96</v>
-      </c>
+        <v>1625.85</v>
+      </c>
+      <c r="Z46" s="9" t="n"/>
+      <c r="AB46" s="5" t="n"/>
       <c r="AC46" s="10" t="n"/>
       <c r="AD46" s="10" t="n"/>
       <c r="AE46" s="11" t="n"/>
@@ -25108,80 +25102,80 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>이익잉여금</t>
+          <t>기타포괄이익누계액</t>
         </is>
       </c>
       <c r="E47" s="18" t="n">
-        <v>136709.68</v>
+        <v>-33.42</v>
       </c>
       <c r="F47" s="37" t="n">
-        <v>136709.68</v>
+        <v>-33.42</v>
       </c>
       <c r="G47" s="18" t="n">
-        <v>121321.35</v>
+        <v>-33.42</v>
       </c>
       <c r="H47" s="18" t="n">
-        <v>132497.31</v>
+        <v>-67.27</v>
       </c>
       <c r="I47" s="18" t="n">
-        <v>135356.26</v>
+        <v>-33.42</v>
       </c>
       <c r="J47" s="18" t="n">
-        <v>141643.04</v>
+        <v>-202.27</v>
       </c>
       <c r="K47" s="37" t="n">
-        <v>141643.04</v>
+        <v>-202.27</v>
       </c>
       <c r="L47" s="18" t="n">
-        <v>127829.98</v>
+        <v>-202.27</v>
       </c>
       <c r="M47" s="18" t="n">
-        <v>141736.46</v>
+        <v>-202.27</v>
       </c>
       <c r="N47" s="18" t="n">
-        <v>144299.56</v>
+        <v>-202.27</v>
       </c>
       <c r="O47" s="18" t="n">
-        <v>158193.89</v>
+        <v>-202.27</v>
       </c>
       <c r="P47" s="37" t="n">
-        <v>158193.89</v>
+        <v>-202.27</v>
       </c>
       <c r="Q47" s="18" t="n">
-        <v>150119.64</v>
+        <v>-202.27</v>
       </c>
       <c r="R47" s="18" t="n">
-        <v>154244.53</v>
+        <v>-326.02</v>
       </c>
       <c r="S47" s="18" t="n">
-        <v>151114.17</v>
+        <v>-482.17</v>
       </c>
       <c r="T47" s="18" t="n">
-        <v>165918.64</v>
+        <v>-1850.85</v>
       </c>
       <c r="U47" s="37" t="n">
-        <v>165918.64</v>
+        <v>-1850.85</v>
       </c>
       <c r="V47" s="18" t="n">
-        <v>167279.02</v>
+        <v>-1374.51</v>
       </c>
       <c r="W47" s="18" t="n">
-        <v>172186.35</v>
+        <v>-1280.27</v>
       </c>
       <c r="X47" s="18" t="n">
-        <v>179094.49</v>
+        <v>-412.31</v>
       </c>
       <c r="Y47" s="18" t="n">
-        <v>198491.16</v>
+        <v>-1001.23</v>
       </c>
       <c r="Z47" s="37" t="n">
-        <v>198491.16</v>
+        <v>-1001.23</v>
       </c>
       <c r="AA47" s="18" t="n">
-        <v>197398.39</v>
+        <v>-1864.07</v>
       </c>
       <c r="AB47" s="19" t="n">
-        <v>211121.71</v>
+        <v>-1635.96</v>
       </c>
       <c r="AC47" s="10" t="n"/>
       <c r="AD47" s="10" t="n"/>
@@ -25203,80 +25197,80 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>자본총계</t>
+          <t>이익잉여금</t>
         </is>
       </c>
       <c r="E48" s="18" t="n">
-        <v>160258.89</v>
+        <v>136709.68</v>
       </c>
       <c r="F48" s="37" t="n">
-        <v>160258.89</v>
+        <v>136709.68</v>
       </c>
       <c r="G48" s="18" t="n">
-        <v>145357.87</v>
+        <v>121321.35</v>
       </c>
       <c r="H48" s="18" t="n">
-        <v>156499.99</v>
+        <v>132497.31</v>
       </c>
       <c r="I48" s="18" t="n">
-        <v>159392.79</v>
+        <v>135356.26</v>
       </c>
       <c r="J48" s="18" t="n">
-        <v>165510.73</v>
+        <v>141643.04</v>
       </c>
       <c r="K48" s="37" t="n">
-        <v>165510.73</v>
+        <v>141643.04</v>
       </c>
       <c r="L48" s="18" t="n">
-        <v>151697.66</v>
+        <v>127829.98</v>
       </c>
       <c r="M48" s="18" t="n">
-        <v>165604.14</v>
+        <v>141736.46</v>
       </c>
       <c r="N48" s="18" t="n">
-        <v>168167.24</v>
+        <v>144299.56</v>
       </c>
       <c r="O48" s="18" t="n">
-        <v>182061.57</v>
+        <v>158193.89</v>
       </c>
       <c r="P48" s="37" t="n">
-        <v>182061.57</v>
+        <v>158193.89</v>
       </c>
       <c r="Q48" s="18" t="n">
-        <v>182911.78</v>
+        <v>150119.64</v>
       </c>
       <c r="R48" s="18" t="n">
-        <v>186912.92</v>
+        <v>154244.53</v>
       </c>
       <c r="S48" s="18" t="n">
-        <v>183626.41</v>
+        <v>151114.17</v>
       </c>
       <c r="T48" s="18" t="n">
-        <v>197062.19</v>
+        <v>165918.64</v>
       </c>
       <c r="U48" s="37" t="n">
-        <v>197062.19</v>
+        <v>165918.64</v>
       </c>
       <c r="V48" s="18" t="n">
-        <v>198898.92</v>
+        <v>167279.02</v>
       </c>
       <c r="W48" s="18" t="n">
-        <v>203900.48</v>
+        <v>172186.35</v>
       </c>
       <c r="X48" s="18" t="n">
-        <v>211676.58</v>
+        <v>179094.49</v>
       </c>
       <c r="Y48" s="18" t="n">
-        <v>230484.34</v>
+        <v>198491.16</v>
       </c>
       <c r="Z48" s="37" t="n">
-        <v>230484.34</v>
+        <v>198491.16</v>
       </c>
       <c r="AA48" s="18" t="n">
-        <v>228528.73</v>
+        <v>197398.39</v>
       </c>
       <c r="AB48" s="19" t="n">
-        <v>242480.15</v>
+        <v>211121.71</v>
       </c>
       <c r="AC48" s="10" t="n"/>
       <c r="AD48" s="10" t="n"/>
@@ -25298,80 +25292,80 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>부채와자본총계</t>
+          <t>자본총계</t>
         </is>
       </c>
       <c r="E49" s="18" t="n">
-        <v>444397.56</v>
+        <v>160258.89</v>
       </c>
       <c r="F49" s="37" t="n">
-        <v>444397.56</v>
+        <v>160258.89</v>
       </c>
       <c r="G49" s="18" t="n">
-        <v>426559.39</v>
+        <v>145357.87</v>
       </c>
       <c r="H49" s="18" t="n">
-        <v>412720.03</v>
+        <v>156499.99</v>
       </c>
       <c r="I49" s="18" t="n">
-        <v>413293.23</v>
+        <v>159392.79</v>
       </c>
       <c r="J49" s="18" t="n">
-        <v>411876.75</v>
+        <v>165510.73</v>
       </c>
       <c r="K49" s="37" t="n">
-        <v>411876.75</v>
+        <v>165510.73</v>
       </c>
       <c r="L49" s="18" t="n">
-        <v>412967.68</v>
+        <v>151697.66</v>
       </c>
       <c r="M49" s="18" t="n">
-        <v>396151.51</v>
+        <v>165604.14</v>
       </c>
       <c r="N49" s="18" t="n">
-        <v>423261.31</v>
+        <v>168167.24</v>
       </c>
       <c r="O49" s="18" t="n">
-        <v>424260.79</v>
+        <v>182061.57</v>
       </c>
       <c r="P49" s="37" t="n">
-        <v>424260.79</v>
+        <v>182061.57</v>
       </c>
       <c r="Q49" s="18" t="n">
-        <v>458966.67</v>
+        <v>182911.78</v>
       </c>
       <c r="R49" s="18" t="n">
-        <v>434128.55</v>
+        <v>186912.92</v>
       </c>
       <c r="S49" s="18" t="n">
-        <v>466803.3</v>
+        <v>183626.41</v>
       </c>
       <c r="T49" s="18" t="n">
-        <v>489679.81</v>
+        <v>197062.19</v>
       </c>
       <c r="U49" s="37" t="n">
-        <v>489679.81</v>
+        <v>197062.19</v>
       </c>
       <c r="V49" s="18" t="n">
-        <v>499006.44</v>
+        <v>198898.92</v>
       </c>
       <c r="W49" s="18" t="n">
-        <v>495033.56</v>
+        <v>203900.48</v>
       </c>
       <c r="X49" s="18" t="n">
-        <v>506645.75</v>
+        <v>211676.58</v>
       </c>
       <c r="Y49" s="18" t="n">
-        <v>491777.06</v>
+        <v>230484.34</v>
       </c>
       <c r="Z49" s="37" t="n">
-        <v>491777.06</v>
+        <v>230484.34</v>
       </c>
       <c r="AA49" s="18" t="n">
-        <v>499772.8</v>
+        <v>228528.73</v>
       </c>
       <c r="AB49" s="19" t="n">
-        <v>500549.83</v>
+        <v>242480.15</v>
       </c>
       <c r="AC49" s="10" t="n"/>
       <c r="AD49" s="10" t="n"/>
@@ -25393,80 +25387,80 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>지배주주지분</t>
+          <t>부채와자본총계</t>
         </is>
       </c>
       <c r="E50" s="18" t="n">
-        <v>160258.89</v>
+        <v>444397.56</v>
       </c>
       <c r="F50" s="37" t="n">
-        <v>160258.89</v>
+        <v>444397.56</v>
       </c>
       <c r="G50" s="18" t="n">
-        <v>145357.87</v>
+        <v>426559.39</v>
       </c>
       <c r="H50" s="18" t="n">
-        <v>156499.99</v>
+        <v>412720.03</v>
       </c>
       <c r="I50" s="18" t="n">
-        <v>159392.79</v>
+        <v>413293.23</v>
       </c>
       <c r="J50" s="18" t="n">
-        <v>165510.73</v>
+        <v>411876.75</v>
       </c>
       <c r="K50" s="37" t="n">
-        <v>165510.73</v>
+        <v>411876.75</v>
       </c>
       <c r="L50" s="18" t="n">
-        <v>151697.66</v>
+        <v>412967.68</v>
       </c>
       <c r="M50" s="18" t="n">
-        <v>165604.14</v>
+        <v>396151.51</v>
       </c>
       <c r="N50" s="18" t="n">
-        <v>168167.24</v>
+        <v>423261.31</v>
       </c>
       <c r="O50" s="18" t="n">
-        <v>182061.57</v>
+        <v>424260.79</v>
       </c>
       <c r="P50" s="37" t="n">
-        <v>182061.57</v>
+        <v>424260.79</v>
       </c>
       <c r="Q50" s="18" t="n">
-        <v>182911.78</v>
+        <v>458966.67</v>
       </c>
       <c r="R50" s="18" t="n">
-        <v>186912.92</v>
+        <v>434128.55</v>
       </c>
       <c r="S50" s="18" t="n">
-        <v>183626.41</v>
+        <v>466803.3</v>
       </c>
       <c r="T50" s="18" t="n">
-        <v>197062.19</v>
+        <v>489679.81</v>
       </c>
       <c r="U50" s="37" t="n">
-        <v>197062.19</v>
+        <v>489679.81</v>
       </c>
       <c r="V50" s="18" t="n">
-        <v>198898.92</v>
+        <v>499006.44</v>
       </c>
       <c r="W50" s="18" t="n">
-        <v>203900.48</v>
+        <v>495033.56</v>
       </c>
       <c r="X50" s="18" t="n">
-        <v>211676.58</v>
+        <v>506645.75</v>
       </c>
       <c r="Y50" s="18" t="n">
-        <v>230484.34</v>
+        <v>491777.06</v>
       </c>
       <c r="Z50" s="37" t="n">
-        <v>230484.34</v>
+        <v>491777.06</v>
       </c>
       <c r="AA50" s="18" t="n">
-        <v>228528.73</v>
+        <v>499772.8</v>
       </c>
       <c r="AB50" s="19" t="n">
-        <v>242480.15</v>
+        <v>500549.83</v>
       </c>
       <c r="AC50" s="10" t="n"/>
       <c r="AD50" s="10" t="n"/>
@@ -25488,80 +25482,80 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>총차입금</t>
+          <t>지배주주지분</t>
         </is>
       </c>
       <c r="E51" s="18" t="n">
-        <v>177000</v>
+        <v>160258.89</v>
       </c>
       <c r="F51" s="37" t="n">
-        <v>177000</v>
+        <v>160258.89</v>
       </c>
       <c r="G51" s="18" t="n">
-        <v>201000</v>
+        <v>145357.87</v>
       </c>
       <c r="H51" s="18" t="n">
-        <v>198000</v>
+        <v>156499.99</v>
       </c>
       <c r="I51" s="18" t="n">
-        <v>199313</v>
+        <v>159392.79</v>
       </c>
       <c r="J51" s="18" t="n">
-        <v>195300</v>
+        <v>165510.73</v>
       </c>
       <c r="K51" s="37" t="n">
-        <v>195300</v>
+        <v>165510.73</v>
       </c>
       <c r="L51" s="18" t="n">
-        <v>194700</v>
+        <v>151697.66</v>
       </c>
       <c r="M51" s="18" t="n">
-        <v>171100</v>
+        <v>165604.14</v>
       </c>
       <c r="N51" s="18" t="n">
-        <v>187500</v>
+        <v>168167.24</v>
       </c>
       <c r="O51" s="18" t="n">
-        <v>176900</v>
+        <v>182061.57</v>
       </c>
       <c r="P51" s="37" t="n">
-        <v>176900</v>
+        <v>182061.57</v>
       </c>
       <c r="Q51" s="18" t="n">
-        <v>176300</v>
+        <v>182911.78</v>
       </c>
       <c r="R51" s="18" t="n">
-        <v>170700</v>
+        <v>186912.92</v>
       </c>
       <c r="S51" s="18" t="n">
-        <v>207500</v>
+        <v>183626.41</v>
       </c>
       <c r="T51" s="18" t="n">
-        <v>211950</v>
+        <v>197062.19</v>
       </c>
       <c r="U51" s="37" t="n">
-        <v>211950</v>
+        <v>197062.19</v>
       </c>
       <c r="V51" s="18" t="n">
-        <v>210600</v>
+        <v>198898.92</v>
       </c>
       <c r="W51" s="18" t="n">
-        <v>209250</v>
+        <v>203900.48</v>
       </c>
       <c r="X51" s="18" t="n">
-        <v>207900</v>
+        <v>211676.58</v>
       </c>
       <c r="Y51" s="18" t="n">
-        <v>182370</v>
+        <v>230484.34</v>
       </c>
       <c r="Z51" s="37" t="n">
-        <v>182370</v>
+        <v>230484.34</v>
       </c>
       <c r="AA51" s="18" t="n">
-        <v>181320</v>
+        <v>228528.73</v>
       </c>
       <c r="AB51" s="19" t="n">
-        <v>180270</v>
+        <v>242480.15</v>
       </c>
       <c r="AC51" s="10" t="n"/>
       <c r="AD51" s="10" t="n"/>
@@ -25583,80 +25577,80 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>순차입금</t>
+          <t>총차입금</t>
         </is>
       </c>
       <c r="E52" s="18" t="n">
-        <v>150387.9</v>
+        <v>177000</v>
       </c>
       <c r="F52" s="37" t="n">
-        <v>150387.9</v>
+        <v>177000</v>
       </c>
       <c r="G52" s="18" t="n">
-        <v>171641.71</v>
+        <v>201000</v>
       </c>
       <c r="H52" s="18" t="n">
-        <v>189772.76</v>
+        <v>198000</v>
       </c>
       <c r="I52" s="18" t="n">
-        <v>174834.09</v>
+        <v>138013</v>
       </c>
       <c r="J52" s="18" t="n">
-        <v>155182.38</v>
+        <v>195300</v>
       </c>
       <c r="K52" s="37" t="n">
-        <v>155182.38</v>
+        <v>195300</v>
       </c>
       <c r="L52" s="18" t="n">
-        <v>176424.64</v>
+        <v>194700</v>
       </c>
       <c r="M52" s="18" t="n">
-        <v>148451.94</v>
+        <v>171100</v>
       </c>
       <c r="N52" s="18" t="n">
-        <v>164824.84</v>
+        <v>187500</v>
       </c>
       <c r="O52" s="18" t="n">
-        <v>144380.75</v>
+        <v>176900</v>
       </c>
       <c r="P52" s="37" t="n">
-        <v>144380.75</v>
+        <v>176900</v>
       </c>
       <c r="Q52" s="18" t="n">
-        <v>129587.01</v>
+        <v>176300</v>
       </c>
       <c r="R52" s="18" t="n">
-        <v>149550.63</v>
+        <v>170700</v>
       </c>
       <c r="S52" s="18" t="n">
-        <v>154945.62</v>
+        <v>207500</v>
       </c>
       <c r="T52" s="18" t="n">
-        <v>167081.14</v>
+        <v>211950</v>
       </c>
       <c r="U52" s="37" t="n">
-        <v>167081.14</v>
+        <v>211950</v>
       </c>
       <c r="V52" s="18" t="n">
-        <v>167568.2</v>
+        <v>210600</v>
       </c>
       <c r="W52" s="18" t="n">
-        <v>148093.14</v>
+        <v>209250</v>
       </c>
       <c r="X52" s="18" t="n">
-        <v>131271.33</v>
+        <v>207900</v>
       </c>
       <c r="Y52" s="18" t="n">
-        <v>144439.39</v>
+        <v>182370</v>
       </c>
       <c r="Z52" s="37" t="n">
-        <v>144439.39</v>
+        <v>182370</v>
       </c>
       <c r="AA52" s="18" t="n">
-        <v>124090.35</v>
+        <v>181320</v>
       </c>
       <c r="AB52" s="19" t="n">
-        <v>132549.46</v>
+        <v>180270</v>
       </c>
       <c r="AC52" s="10" t="n"/>
       <c r="AD52" s="10" t="n"/>
@@ -25678,80 +25672,80 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>이자발생자산</t>
+          <t>순차입금</t>
         </is>
       </c>
       <c r="E53" s="18" t="n">
-        <v>75930.03</v>
+        <v>150387.9</v>
       </c>
       <c r="F53" s="37" t="n">
-        <v>75930.03</v>
+        <v>150387.9</v>
       </c>
       <c r="G53" s="18" t="n">
-        <v>30550.56</v>
+        <v>171641.71</v>
       </c>
       <c r="H53" s="18" t="n">
-        <v>27011.68</v>
+        <v>189772.76</v>
       </c>
       <c r="I53" s="18" t="n">
-        <v>25761.18</v>
+        <v>113534.09</v>
       </c>
       <c r="J53" s="18" t="n">
-        <v>41225.33</v>
+        <v>155182.38</v>
       </c>
       <c r="K53" s="37" t="n">
-        <v>41225.33</v>
+        <v>155182.38</v>
       </c>
       <c r="L53" s="18" t="n">
-        <v>24428.07</v>
+        <v>176424.64</v>
       </c>
       <c r="M53" s="18" t="n">
-        <v>28845.77</v>
+        <v>148451.94</v>
       </c>
       <c r="N53" s="18" t="n">
-        <v>28917.87</v>
+        <v>164824.84</v>
       </c>
       <c r="O53" s="18" t="n">
-        <v>38806.96</v>
+        <v>144380.75</v>
       </c>
       <c r="P53" s="37" t="n">
-        <v>38806.96</v>
+        <v>144380.75</v>
       </c>
       <c r="Q53" s="18" t="n">
-        <v>53045.7</v>
+        <v>129587.01</v>
       </c>
       <c r="R53" s="18" t="n">
-        <v>34072.11</v>
+        <v>149550.63</v>
       </c>
       <c r="S53" s="18" t="n">
-        <v>65061.21</v>
+        <v>154945.62</v>
       </c>
       <c r="T53" s="18" t="n">
-        <v>57568.23</v>
+        <v>167081.14</v>
       </c>
       <c r="U53" s="37" t="n">
-        <v>57568.23</v>
+        <v>167081.14</v>
       </c>
       <c r="V53" s="18" t="n">
-        <v>56965.39</v>
+        <v>167568.2</v>
       </c>
       <c r="W53" s="18" t="n">
-        <v>75792.5</v>
+        <v>148093.14</v>
       </c>
       <c r="X53" s="18" t="n">
-        <v>98200.57000000001</v>
+        <v>131271.33</v>
       </c>
       <c r="Y53" s="18" t="n">
-        <v>60210.58</v>
+        <v>144439.39</v>
       </c>
       <c r="Z53" s="37" t="n">
-        <v>60210.58</v>
+        <v>144439.39</v>
       </c>
       <c r="AA53" s="18" t="n">
-        <v>80555.39</v>
+        <v>124090.35</v>
       </c>
       <c r="AB53" s="19" t="n">
-        <v>73937.92999999999</v>
+        <v>132549.46</v>
       </c>
       <c r="AC53" s="10" t="n"/>
       <c r="AD53" s="10" t="n"/>
@@ -25773,23 +25767,81 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>사채</t>
+          <t>이자발생자산</t>
         </is>
       </c>
       <c r="E54" s="18" t="n">
-        <v>15000</v>
+        <v>75930.03</v>
       </c>
       <c r="F54" s="37" t="n">
-        <v>15000</v>
+        <v>75930.03</v>
       </c>
       <c r="G54" s="18" t="n">
-        <v>15000</v>
-      </c>
-      <c r="K54" s="9" t="n"/>
-      <c r="P54" s="9" t="n"/>
-      <c r="U54" s="9" t="n"/>
-      <c r="Z54" s="9" t="n"/>
-      <c r="AB54" s="5" t="n"/>
+        <v>30550.56</v>
+      </c>
+      <c r="H54" s="18" t="n">
+        <v>27011.68</v>
+      </c>
+      <c r="I54" s="18" t="n">
+        <v>25761.18</v>
+      </c>
+      <c r="J54" s="18" t="n">
+        <v>41225.33</v>
+      </c>
+      <c r="K54" s="37" t="n">
+        <v>41225.33</v>
+      </c>
+      <c r="L54" s="18" t="n">
+        <v>24428.07</v>
+      </c>
+      <c r="M54" s="18" t="n">
+        <v>28845.77</v>
+      </c>
+      <c r="N54" s="18" t="n">
+        <v>28917.87</v>
+      </c>
+      <c r="O54" s="18" t="n">
+        <v>38806.96</v>
+      </c>
+      <c r="P54" s="37" t="n">
+        <v>38806.96</v>
+      </c>
+      <c r="Q54" s="18" t="n">
+        <v>53045.7</v>
+      </c>
+      <c r="R54" s="18" t="n">
+        <v>34072.11</v>
+      </c>
+      <c r="S54" s="18" t="n">
+        <v>65061.21</v>
+      </c>
+      <c r="T54" s="18" t="n">
+        <v>57568.23</v>
+      </c>
+      <c r="U54" s="37" t="n">
+        <v>57568.23</v>
+      </c>
+      <c r="V54" s="18" t="n">
+        <v>56965.39</v>
+      </c>
+      <c r="W54" s="18" t="n">
+        <v>75792.5</v>
+      </c>
+      <c r="X54" s="18" t="n">
+        <v>98200.57000000001</v>
+      </c>
+      <c r="Y54" s="18" t="n">
+        <v>60210.58</v>
+      </c>
+      <c r="Z54" s="37" t="n">
+        <v>60210.58</v>
+      </c>
+      <c r="AA54" s="18" t="n">
+        <v>80555.39</v>
+      </c>
+      <c r="AB54" s="19" t="n">
+        <v>73937.92999999999</v>
+      </c>
       <c r="AC54" s="10" t="n"/>
       <c r="AD54" s="10" t="n"/>
       <c r="AE54" s="11" t="n"/>
@@ -25984,52 +26036,78 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>장기금융부채(face)</t>
-        </is>
+          <t>매출액(수익)</t>
+        </is>
+      </c>
+      <c r="E58" s="18" t="n">
+        <v>64557.81</v>
       </c>
       <c r="F58" s="9" t="n"/>
-      <c r="K58" s="9" t="n"/>
+      <c r="G58" s="18" t="n">
+        <v>128719.92</v>
+      </c>
+      <c r="H58" s="18" t="n">
+        <v>80273.87</v>
+      </c>
+      <c r="I58" s="18" t="n">
+        <v>68805.25999999999</v>
+      </c>
+      <c r="J58" s="18" t="n">
+        <v>85266.78999999999</v>
+      </c>
+      <c r="K58" s="37" t="n">
+        <v>363065.84</v>
+      </c>
+      <c r="L58" s="18" t="n">
+        <v>60148.33</v>
+      </c>
+      <c r="M58" s="18" t="n">
+        <v>110127.93</v>
+      </c>
+      <c r="N58" s="18" t="n">
+        <v>75583.02</v>
+      </c>
       <c r="O58" s="18" t="n">
-        <v>43300</v>
+        <v>101980.32</v>
       </c>
       <c r="P58" s="37" t="n">
-        <v>43300</v>
+        <v>347839.6</v>
       </c>
       <c r="Q58" s="18" t="n">
-        <v>42700</v>
+        <v>78440.09</v>
       </c>
       <c r="R58" s="18" t="n">
-        <v>42100</v>
+        <v>70848.27</v>
       </c>
       <c r="S58" s="18" t="n">
-        <v>25900</v>
+        <v>65466.35</v>
       </c>
       <c r="T58" s="18" t="n">
-        <v>30650</v>
+        <v>96902.03</v>
       </c>
       <c r="U58" s="37" t="n">
-        <v>30650</v>
+        <v>311656.74</v>
       </c>
       <c r="V58" s="18" t="n">
-        <v>29600</v>
+        <v>90047.77</v>
       </c>
       <c r="W58" s="18" t="n">
-        <v>28550</v>
+        <v>88154.49000000001</v>
       </c>
       <c r="X58" s="18" t="n">
-        <v>106500</v>
+        <v>80589.05</v>
       </c>
       <c r="Y58" s="18" t="n">
-        <v>106200</v>
+        <v>107338.84</v>
       </c>
       <c r="Z58" s="37" t="n">
-        <v>106200</v>
+        <v>366130.15</v>
       </c>
       <c r="AA58" s="18" t="n">
-        <v>106200</v>
+        <v>78164.42999999999</v>
       </c>
       <c r="AB58" s="19" t="n">
-        <v>106200</v>
+        <v>83367.47</v>
       </c>
       <c r="AC58" s="10" t="n"/>
       <c r="AD58" s="10" t="n"/>
@@ -26051,78 +26129,78 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>매출액(수익)</t>
+          <t>매출원가</t>
         </is>
       </c>
       <c r="E59" s="18" t="n">
-        <v>64557.81</v>
+        <v>73165.17999999999</v>
       </c>
       <c r="F59" s="9" t="n"/>
       <c r="G59" s="18" t="n">
-        <v>128719.92</v>
+        <v>131290.28</v>
       </c>
       <c r="H59" s="18" t="n">
-        <v>80273.87</v>
+        <v>64379.4</v>
       </c>
       <c r="I59" s="18" t="n">
-        <v>68805.25999999999</v>
+        <v>63132.01</v>
       </c>
       <c r="J59" s="18" t="n">
-        <v>85266.78999999999</v>
+        <v>68208.09</v>
       </c>
       <c r="K59" s="37" t="n">
-        <v>363065.84</v>
+        <v>327009.78</v>
       </c>
       <c r="L59" s="18" t="n">
-        <v>60148.33</v>
+        <v>62569.39</v>
       </c>
       <c r="M59" s="18" t="n">
-        <v>110127.93</v>
+        <v>87367.14</v>
       </c>
       <c r="N59" s="18" t="n">
-        <v>75583.02</v>
+        <v>77529.17999999999</v>
       </c>
       <c r="O59" s="18" t="n">
-        <v>101980.32</v>
+        <v>77164.84</v>
       </c>
       <c r="P59" s="37" t="n">
-        <v>347839.6</v>
+        <v>304630.55</v>
       </c>
       <c r="Q59" s="18" t="n">
-        <v>78440.09</v>
+        <v>70833.09</v>
       </c>
       <c r="R59" s="18" t="n">
-        <v>70848.27</v>
+        <v>60445.65</v>
       </c>
       <c r="S59" s="18" t="n">
-        <v>65466.35</v>
+        <v>64259.24</v>
       </c>
       <c r="T59" s="18" t="n">
-        <v>96902.03</v>
+        <v>73053.14</v>
       </c>
       <c r="U59" s="37" t="n">
-        <v>311656.74</v>
+        <v>268591.12</v>
       </c>
       <c r="V59" s="18" t="n">
-        <v>90047.77</v>
+        <v>68889.17999999999</v>
       </c>
       <c r="W59" s="18" t="n">
-        <v>88154.49000000001</v>
+        <v>75779.87</v>
       </c>
       <c r="X59" s="18" t="n">
-        <v>80589.05</v>
+        <v>68334.02</v>
       </c>
       <c r="Y59" s="18" t="n">
-        <v>107338.84</v>
+        <v>72436.69</v>
       </c>
       <c r="Z59" s="37" t="n">
-        <v>366130.15</v>
+        <v>285439.76</v>
       </c>
       <c r="AA59" s="18" t="n">
-        <v>78164.42999999999</v>
+        <v>62848.29</v>
       </c>
       <c r="AB59" s="19" t="n">
-        <v>83367.47</v>
+        <v>64286.28</v>
       </c>
       <c r="AC59" s="10" t="n"/>
       <c r="AD59" s="10" t="n"/>
@@ -26144,78 +26222,78 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>매출원가</t>
+          <t>매출총이익</t>
         </is>
       </c>
       <c r="E60" s="18" t="n">
-        <v>73165.17999999999</v>
+        <v>-8607.379999999999</v>
       </c>
       <c r="F60" s="9" t="n"/>
       <c r="G60" s="18" t="n">
-        <v>131290.28</v>
+        <v>-2570.36</v>
       </c>
       <c r="H60" s="18" t="n">
-        <v>64379.4</v>
+        <v>15894.47</v>
       </c>
       <c r="I60" s="18" t="n">
-        <v>63132.01</v>
+        <v>5673.25</v>
       </c>
       <c r="J60" s="18" t="n">
-        <v>68208.09</v>
+        <v>17058.7</v>
       </c>
       <c r="K60" s="37" t="n">
-        <v>327009.78</v>
+        <v>36056.06</v>
       </c>
       <c r="L60" s="18" t="n">
-        <v>62569.39</v>
+        <v>-2421.06</v>
       </c>
       <c r="M60" s="18" t="n">
-        <v>87367.14</v>
+        <v>22760.79</v>
       </c>
       <c r="N60" s="18" t="n">
-        <v>77529.17999999999</v>
+        <v>-1946.16</v>
       </c>
       <c r="O60" s="18" t="n">
-        <v>77164.84</v>
+        <v>24815.48</v>
       </c>
       <c r="P60" s="37" t="n">
-        <v>304630.55</v>
+        <v>43209.05</v>
       </c>
       <c r="Q60" s="18" t="n">
-        <v>70833.09</v>
+        <v>7607.01</v>
       </c>
       <c r="R60" s="18" t="n">
-        <v>60445.65</v>
+        <v>10402.63</v>
       </c>
       <c r="S60" s="18" t="n">
-        <v>64259.24</v>
+        <v>1207.11</v>
       </c>
       <c r="T60" s="18" t="n">
-        <v>73053.14</v>
+        <v>23848.89</v>
       </c>
       <c r="U60" s="37" t="n">
-        <v>268591.12</v>
+        <v>43065.64</v>
       </c>
       <c r="V60" s="18" t="n">
-        <v>68889.17999999999</v>
+        <v>21158.59</v>
       </c>
       <c r="W60" s="18" t="n">
-        <v>75779.87</v>
+        <v>12374.62</v>
       </c>
       <c r="X60" s="18" t="n">
-        <v>68334.02</v>
+        <v>12255.03</v>
       </c>
       <c r="Y60" s="18" t="n">
-        <v>72436.69</v>
+        <v>34902.14</v>
       </c>
       <c r="Z60" s="37" t="n">
-        <v>285439.76</v>
+        <v>80690.38</v>
       </c>
       <c r="AA60" s="18" t="n">
-        <v>62848.29</v>
+        <v>15316.14</v>
       </c>
       <c r="AB60" s="19" t="n">
-        <v>64286.28</v>
+        <v>19081.19</v>
       </c>
       <c r="AC60" s="10" t="n"/>
       <c r="AD60" s="10" t="n"/>
@@ -26237,78 +26315,78 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>매출총이익</t>
+          <t>판관비</t>
         </is>
       </c>
       <c r="E61" s="18" t="n">
-        <v>-8607.379999999999</v>
+        <v>3602.63</v>
       </c>
       <c r="F61" s="9" t="n"/>
       <c r="G61" s="18" t="n">
-        <v>-2570.36</v>
+        <v>3876.34</v>
       </c>
       <c r="H61" s="18" t="n">
-        <v>15894.47</v>
+        <v>4326.19</v>
       </c>
       <c r="I61" s="18" t="n">
-        <v>5673.25</v>
+        <v>3241.07</v>
       </c>
       <c r="J61" s="18" t="n">
-        <v>17058.7</v>
+        <v>2356.98</v>
       </c>
       <c r="K61" s="37" t="n">
-        <v>36056.06</v>
+        <v>13800.58</v>
       </c>
       <c r="L61" s="18" t="n">
-        <v>-2421.06</v>
+        <v>3120.14</v>
       </c>
       <c r="M61" s="18" t="n">
-        <v>22760.79</v>
+        <v>3840.27</v>
       </c>
       <c r="N61" s="18" t="n">
-        <v>-1946.16</v>
+        <v>3876.97</v>
       </c>
       <c r="O61" s="18" t="n">
-        <v>24815.48</v>
+        <v>3891.74</v>
       </c>
       <c r="P61" s="37" t="n">
-        <v>43209.05</v>
+        <v>14729.12</v>
       </c>
       <c r="Q61" s="18" t="n">
-        <v>7607.01</v>
+        <v>3613.4</v>
       </c>
       <c r="R61" s="18" t="n">
-        <v>10402.63</v>
+        <v>3416.56</v>
       </c>
       <c r="S61" s="18" t="n">
-        <v>1207.11</v>
+        <v>3389.26</v>
       </c>
       <c r="T61" s="18" t="n">
-        <v>23848.89</v>
+        <v>3423.88</v>
       </c>
       <c r="U61" s="37" t="n">
-        <v>43065.64</v>
+        <v>13843.1</v>
       </c>
       <c r="V61" s="18" t="n">
-        <v>21158.59</v>
+        <v>4064.28</v>
       </c>
       <c r="W61" s="18" t="n">
-        <v>12374.62</v>
+        <v>4495.99</v>
       </c>
       <c r="X61" s="18" t="n">
-        <v>12255.03</v>
+        <v>3560.52</v>
       </c>
       <c r="Y61" s="18" t="n">
-        <v>34902.14</v>
+        <v>4778.43</v>
       </c>
       <c r="Z61" s="37" t="n">
-        <v>80690.38</v>
+        <v>16899.22</v>
       </c>
       <c r="AA61" s="18" t="n">
-        <v>15316.14</v>
+        <v>4677.16</v>
       </c>
       <c r="AB61" s="19" t="n">
-        <v>19081.19</v>
+        <v>4206.11</v>
       </c>
       <c r="AC61" s="10" t="n"/>
       <c r="AD61" s="10" t="n"/>
@@ -26330,78 +26408,78 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>판관비</t>
+          <t>영업이익</t>
         </is>
       </c>
       <c r="E62" s="18" t="n">
-        <v>3602.63</v>
+        <v>-12210.01</v>
       </c>
       <c r="F62" s="9" t="n"/>
       <c r="G62" s="18" t="n">
-        <v>3876.34</v>
+        <v>-6446.7</v>
       </c>
       <c r="H62" s="18" t="n">
-        <v>4326.19</v>
+        <v>11568.28</v>
       </c>
       <c r="I62" s="18" t="n">
-        <v>3241.07</v>
+        <v>2432.18</v>
       </c>
       <c r="J62" s="18" t="n">
-        <v>2356.98</v>
+        <v>14701.71</v>
       </c>
       <c r="K62" s="37" t="n">
-        <v>13800.58</v>
+        <v>22255.47</v>
       </c>
       <c r="L62" s="18" t="n">
-        <v>3120.14</v>
+        <v>-5541.2</v>
       </c>
       <c r="M62" s="18" t="n">
-        <v>3840.27</v>
+        <v>18920.52</v>
       </c>
       <c r="N62" s="18" t="n">
-        <v>3876.97</v>
+        <v>-5823.13</v>
       </c>
       <c r="O62" s="18" t="n">
-        <v>3891.74</v>
+        <v>20923.74</v>
       </c>
       <c r="P62" s="37" t="n">
-        <v>14729.12</v>
+        <v>28479.93</v>
       </c>
       <c r="Q62" s="18" t="n">
-        <v>3613.4</v>
+        <v>3993.61</v>
       </c>
       <c r="R62" s="18" t="n">
-        <v>3416.56</v>
+        <v>6986.06</v>
       </c>
       <c r="S62" s="18" t="n">
-        <v>3389.26</v>
+        <v>-2182.16</v>
       </c>
       <c r="T62" s="18" t="n">
-        <v>3423.88</v>
+        <v>20425.01</v>
       </c>
       <c r="U62" s="37" t="n">
-        <v>13843.1</v>
+        <v>29222.52</v>
       </c>
       <c r="V62" s="18" t="n">
-        <v>4064.28</v>
+        <v>17094.31</v>
       </c>
       <c r="W62" s="18" t="n">
-        <v>4495.99</v>
+        <v>7878.63</v>
       </c>
       <c r="X62" s="18" t="n">
-        <v>3560.52</v>
+        <v>8694.5</v>
       </c>
       <c r="Y62" s="18" t="n">
-        <v>4778.43</v>
+        <v>30123.71</v>
       </c>
       <c r="Z62" s="37" t="n">
-        <v>16899.22</v>
+        <v>63791.15</v>
       </c>
       <c r="AA62" s="18" t="n">
-        <v>4677.16</v>
+        <v>10638.98</v>
       </c>
       <c r="AB62" s="19" t="n">
-        <v>4206.11</v>
+        <v>14875.09</v>
       </c>
       <c r="AC62" s="10" t="n"/>
       <c r="AD62" s="10" t="n"/>
@@ -26423,78 +26501,78 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>영업이익</t>
+          <t>기타영업외손익</t>
         </is>
       </c>
       <c r="E63" s="18" t="n">
-        <v>-12210.01</v>
+        <v>-127.43</v>
       </c>
       <c r="F63" s="9" t="n"/>
       <c r="G63" s="18" t="n">
-        <v>-6446.7</v>
+        <v>-68.64</v>
       </c>
       <c r="H63" s="18" t="n">
-        <v>11568.28</v>
+        <v>37.94</v>
       </c>
       <c r="I63" s="18" t="n">
-        <v>2432.18</v>
+        <v>910.62</v>
       </c>
       <c r="J63" s="18" t="n">
-        <v>14701.71</v>
+        <v>-2610.46</v>
       </c>
       <c r="K63" s="37" t="n">
-        <v>22255.47</v>
+        <v>-1730.54</v>
       </c>
       <c r="L63" s="18" t="n">
-        <v>-5541.2</v>
+        <v>-179.93</v>
       </c>
       <c r="M63" s="18" t="n">
-        <v>18920.52</v>
+        <v>254.75</v>
       </c>
       <c r="N63" s="18" t="n">
-        <v>-5823.13</v>
+        <v>10304.35</v>
       </c>
       <c r="O63" s="18" t="n">
-        <v>20923.74</v>
+        <v>1574.53</v>
       </c>
       <c r="P63" s="37" t="n">
-        <v>28479.93</v>
+        <v>11953.7</v>
       </c>
       <c r="Q63" s="18" t="n">
-        <v>3993.61</v>
+        <v>-47.75</v>
       </c>
       <c r="R63" s="18" t="n">
-        <v>6986.06</v>
+        <v>206.24</v>
       </c>
       <c r="S63" s="18" t="n">
-        <v>-2182.16</v>
+        <v>90.59</v>
       </c>
       <c r="T63" s="18" t="n">
-        <v>20425.01</v>
+        <v>109.99</v>
       </c>
       <c r="U63" s="37" t="n">
-        <v>29222.52</v>
+        <v>359.07</v>
       </c>
       <c r="V63" s="18" t="n">
-        <v>17094.31</v>
+        <v>195.81</v>
       </c>
       <c r="W63" s="18" t="n">
-        <v>7878.63</v>
+        <v>61.92</v>
       </c>
       <c r="X63" s="18" t="n">
-        <v>8694.5</v>
+        <v>57.59</v>
       </c>
       <c r="Y63" s="18" t="n">
-        <v>30123.71</v>
+        <v>-5813.95</v>
       </c>
       <c r="Z63" s="37" t="n">
-        <v>63791.15</v>
+        <v>-5498.63</v>
       </c>
       <c r="AA63" s="18" t="n">
-        <v>10638.98</v>
+        <v>-37.85</v>
       </c>
       <c r="AB63" s="19" t="n">
-        <v>14875.09</v>
+        <v>-1216.33</v>
       </c>
       <c r="AC63" s="10" t="n"/>
       <c r="AD63" s="10" t="n"/>
@@ -26516,78 +26594,78 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>기타영업외손익</t>
+          <t>기타영업외수익</t>
         </is>
       </c>
       <c r="E64" s="18" t="n">
-        <v>-127.43</v>
+        <v>945.77</v>
       </c>
       <c r="F64" s="9" t="n"/>
       <c r="G64" s="18" t="n">
-        <v>-68.64</v>
+        <v>56.01</v>
       </c>
       <c r="H64" s="18" t="n">
-        <v>37.94</v>
+        <v>153.92</v>
       </c>
       <c r="I64" s="18" t="n">
-        <v>910.62</v>
+        <v>979.62</v>
       </c>
       <c r="J64" s="18" t="n">
-        <v>-2610.46</v>
+        <v>-685.39</v>
       </c>
       <c r="K64" s="37" t="n">
-        <v>-1730.54</v>
+        <v>504.16</v>
       </c>
       <c r="L64" s="18" t="n">
-        <v>-179.93</v>
+        <v>76.53</v>
       </c>
       <c r="M64" s="18" t="n">
-        <v>254.75</v>
+        <v>248.25</v>
       </c>
       <c r="N64" s="18" t="n">
-        <v>10304.35</v>
+        <v>10340.31</v>
       </c>
       <c r="O64" s="18" t="n">
-        <v>1574.53</v>
+        <v>1570.96</v>
       </c>
       <c r="P64" s="37" t="n">
-        <v>11953.7</v>
+        <v>12236.05</v>
       </c>
       <c r="Q64" s="18" t="n">
-        <v>-47.75</v>
+        <v>317.14</v>
       </c>
       <c r="R64" s="18" t="n">
-        <v>206.24</v>
+        <v>207.98</v>
       </c>
       <c r="S64" s="18" t="n">
-        <v>90.59</v>
+        <v>93.92</v>
       </c>
       <c r="T64" s="18" t="n">
-        <v>109.99</v>
+        <v>113.62</v>
       </c>
       <c r="U64" s="37" t="n">
-        <v>359.07</v>
+        <v>732.66</v>
       </c>
       <c r="V64" s="18" t="n">
-        <v>195.81</v>
+        <v>349.18</v>
       </c>
       <c r="W64" s="18" t="n">
-        <v>61.92</v>
+        <v>167.04</v>
       </c>
       <c r="X64" s="18" t="n">
-        <v>57.59</v>
+        <v>74.13</v>
       </c>
       <c r="Y64" s="18" t="n">
-        <v>-5813.95</v>
+        <v>42.58</v>
       </c>
       <c r="Z64" s="37" t="n">
-        <v>-5498.63</v>
+        <v>632.9299999999999</v>
       </c>
       <c r="AA64" s="18" t="n">
-        <v>-37.85</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AB64" s="19" t="n">
-        <v>-1216.33</v>
+        <v>71.5</v>
       </c>
       <c r="AC64" s="10" t="n"/>
       <c r="AD64" s="10" t="n"/>
@@ -26609,78 +26687,78 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>기타영업외수익</t>
+          <t>기타영업외비용</t>
         </is>
       </c>
       <c r="E65" s="18" t="n">
-        <v>945.77</v>
+        <v>1073.19</v>
       </c>
       <c r="F65" s="9" t="n"/>
       <c r="G65" s="18" t="n">
-        <v>56.01</v>
+        <v>124.65</v>
       </c>
       <c r="H65" s="18" t="n">
-        <v>153.92</v>
+        <v>115.98</v>
       </c>
       <c r="I65" s="18" t="n">
-        <v>979.62</v>
+        <v>69</v>
       </c>
       <c r="J65" s="18" t="n">
-        <v>-685.39</v>
+        <v>1925.07</v>
       </c>
       <c r="K65" s="37" t="n">
-        <v>504.16</v>
+        <v>2234.7</v>
       </c>
       <c r="L65" s="18" t="n">
-        <v>76.53</v>
+        <v>256.46</v>
       </c>
       <c r="M65" s="18" t="n">
-        <v>248.25</v>
+        <v>-6.5</v>
       </c>
       <c r="N65" s="18" t="n">
-        <v>10340.31</v>
+        <v>35.97</v>
       </c>
       <c r="O65" s="18" t="n">
-        <v>1570.96</v>
+        <v>-3.57</v>
       </c>
       <c r="P65" s="37" t="n">
-        <v>12236.05</v>
+        <v>282.36</v>
       </c>
       <c r="Q65" s="18" t="n">
-        <v>317.14</v>
+        <v>364.89</v>
       </c>
       <c r="R65" s="18" t="n">
-        <v>207.98</v>
+        <v>1.74</v>
       </c>
       <c r="S65" s="18" t="n">
-        <v>93.92</v>
+        <v>3.32</v>
       </c>
       <c r="T65" s="18" t="n">
-        <v>113.62</v>
+        <v>3.63</v>
       </c>
       <c r="U65" s="37" t="n">
-        <v>732.66</v>
+        <v>373.58</v>
       </c>
       <c r="V65" s="18" t="n">
-        <v>349.18</v>
+        <v>153.37</v>
       </c>
       <c r="W65" s="18" t="n">
-        <v>167.04</v>
+        <v>105.12</v>
       </c>
       <c r="X65" s="18" t="n">
-        <v>74.13</v>
+        <v>16.54</v>
       </c>
       <c r="Y65" s="18" t="n">
-        <v>42.58</v>
+        <v>5856.53</v>
       </c>
       <c r="Z65" s="37" t="n">
-        <v>632.9299999999999</v>
+        <v>6131.56</v>
       </c>
       <c r="AA65" s="18" t="n">
-        <v>65.34999999999999</v>
+        <v>103.2</v>
       </c>
       <c r="AB65" s="19" t="n">
-        <v>71.5</v>
+        <v>1287.83</v>
       </c>
       <c r="AC65" s="10" t="n"/>
       <c r="AD65" s="10" t="n"/>
@@ -26702,78 +26780,78 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>기타영업외비용</t>
+          <t>금융손익</t>
         </is>
       </c>
       <c r="E66" s="18" t="n">
-        <v>1073.19</v>
+        <v>-738.75</v>
       </c>
       <c r="F66" s="9" t="n"/>
       <c r="G66" s="18" t="n">
-        <v>124.65</v>
+        <v>-2664.54</v>
       </c>
       <c r="H66" s="18" t="n">
-        <v>115.98</v>
+        <v>2520.92</v>
       </c>
       <c r="I66" s="18" t="n">
-        <v>69</v>
+        <v>473.39</v>
       </c>
       <c r="J66" s="18" t="n">
-        <v>1925.07</v>
+        <v>-4760.78</v>
       </c>
       <c r="K66" s="37" t="n">
-        <v>2234.7</v>
+        <v>-4431.01</v>
       </c>
       <c r="L66" s="18" t="n">
-        <v>256.46</v>
+        <v>-1008.06</v>
       </c>
       <c r="M66" s="18" t="n">
-        <v>-6.5</v>
+        <v>-1725.58</v>
       </c>
       <c r="N66" s="18" t="n">
-        <v>35.97</v>
+        <v>-1620.24</v>
       </c>
       <c r="O66" s="18" t="n">
-        <v>-3.57</v>
+        <v>-2262.35</v>
       </c>
       <c r="P66" s="37" t="n">
-        <v>282.36</v>
+        <v>-6616.23</v>
       </c>
       <c r="Q66" s="18" t="n">
-        <v>364.89</v>
+        <v>-1214.64</v>
       </c>
       <c r="R66" s="18" t="n">
-        <v>1.74</v>
+        <v>-1526.59</v>
       </c>
       <c r="S66" s="18" t="n">
-        <v>3.32</v>
+        <v>-1855.91</v>
       </c>
       <c r="T66" s="18" t="n">
-        <v>3.63</v>
+        <v>-1098.5</v>
       </c>
       <c r="U66" s="37" t="n">
-        <v>373.58</v>
+        <v>-5695.64</v>
       </c>
       <c r="V66" s="18" t="n">
-        <v>153.37</v>
+        <v>-502.12</v>
       </c>
       <c r="W66" s="18" t="n">
-        <v>105.12</v>
+        <v>-1293.68</v>
       </c>
       <c r="X66" s="18" t="n">
-        <v>16.54</v>
+        <v>168.66</v>
       </c>
       <c r="Y66" s="18" t="n">
-        <v>5856.53</v>
+        <v>1284.68</v>
       </c>
       <c r="Z66" s="37" t="n">
-        <v>6131.56</v>
+        <v>-342.46</v>
       </c>
       <c r="AA66" s="18" t="n">
-        <v>103.2</v>
+        <v>5269.61</v>
       </c>
       <c r="AB66" s="19" t="n">
-        <v>1287.83</v>
+        <v>3973.19</v>
       </c>
       <c r="AC66" s="10" t="n"/>
       <c r="AD66" s="10" t="n"/>
@@ -26795,78 +26873,78 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>금융손익</t>
+          <t>금융수익</t>
         </is>
       </c>
       <c r="E67" s="18" t="n">
-        <v>-738.75</v>
+        <v>285.24</v>
       </c>
       <c r="F67" s="9" t="n"/>
       <c r="G67" s="18" t="n">
-        <v>-2664.54</v>
+        <v>880.65</v>
       </c>
       <c r="H67" s="18" t="n">
-        <v>2520.92</v>
+        <v>2015.26</v>
       </c>
       <c r="I67" s="18" t="n">
-        <v>473.39</v>
+        <v>1793.78</v>
       </c>
       <c r="J67" s="18" t="n">
-        <v>-4760.78</v>
+        <v>550.49</v>
       </c>
       <c r="K67" s="37" t="n">
-        <v>-4431.01</v>
+        <v>5240.18</v>
       </c>
       <c r="L67" s="18" t="n">
-        <v>-1008.06</v>
+        <v>1235.1</v>
       </c>
       <c r="M67" s="18" t="n">
-        <v>-1725.58</v>
+        <v>487.59</v>
       </c>
       <c r="N67" s="18" t="n">
-        <v>-1620.24</v>
+        <v>642.37</v>
       </c>
       <c r="O67" s="18" t="n">
-        <v>-2262.35</v>
+        <v>292.93</v>
       </c>
       <c r="P67" s="37" t="n">
-        <v>-6616.23</v>
+        <v>2657.99</v>
       </c>
       <c r="Q67" s="18" t="n">
-        <v>-1214.64</v>
+        <v>1007.93</v>
       </c>
       <c r="R67" s="18" t="n">
-        <v>-1526.59</v>
+        <v>916.45</v>
       </c>
       <c r="S67" s="18" t="n">
-        <v>-1855.91</v>
+        <v>800.92</v>
       </c>
       <c r="T67" s="18" t="n">
-        <v>-1098.5</v>
+        <v>1501.25</v>
       </c>
       <c r="U67" s="37" t="n">
-        <v>-5695.64</v>
+        <v>4226.55</v>
       </c>
       <c r="V67" s="18" t="n">
-        <v>-502.12</v>
+        <v>1681.11</v>
       </c>
       <c r="W67" s="18" t="n">
-        <v>-1293.68</v>
+        <v>1374.9</v>
       </c>
       <c r="X67" s="18" t="n">
-        <v>168.66</v>
+        <v>1994.24</v>
       </c>
       <c r="Y67" s="18" t="n">
-        <v>1284.68</v>
+        <v>3426.25</v>
       </c>
       <c r="Z67" s="37" t="n">
-        <v>-342.46</v>
+        <v>8476.5</v>
       </c>
       <c r="AA67" s="18" t="n">
-        <v>5269.61</v>
+        <v>7068.63</v>
       </c>
       <c r="AB67" s="19" t="n">
-        <v>3973.19</v>
+        <v>5446.73</v>
       </c>
       <c r="AC67" s="10" t="n"/>
       <c r="AD67" s="10" t="n"/>
@@ -26888,78 +26966,78 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>금융수익</t>
+          <t>금융비용</t>
         </is>
       </c>
       <c r="E68" s="18" t="n">
-        <v>285.24</v>
+        <v>1023.99</v>
       </c>
       <c r="F68" s="9" t="n"/>
       <c r="G68" s="18" t="n">
-        <v>880.65</v>
+        <v>3545.19</v>
       </c>
       <c r="H68" s="18" t="n">
-        <v>2015.26</v>
+        <v>-505.65</v>
       </c>
       <c r="I68" s="18" t="n">
-        <v>1793.78</v>
+        <v>1320.39</v>
       </c>
       <c r="J68" s="18" t="n">
-        <v>550.49</v>
+        <v>5311.27</v>
       </c>
       <c r="K68" s="37" t="n">
-        <v>5240.18</v>
+        <v>9671.200000000001</v>
       </c>
       <c r="L68" s="18" t="n">
-        <v>1235.1</v>
+        <v>2243.16</v>
       </c>
       <c r="M68" s="18" t="n">
-        <v>487.59</v>
+        <v>2213.17</v>
       </c>
       <c r="N68" s="18" t="n">
-        <v>642.37</v>
+        <v>2262.61</v>
       </c>
       <c r="O68" s="18" t="n">
-        <v>292.93</v>
+        <v>2555.28</v>
       </c>
       <c r="P68" s="37" t="n">
-        <v>2657.99</v>
+        <v>9274.219999999999</v>
       </c>
       <c r="Q68" s="18" t="n">
-        <v>1007.93</v>
+        <v>2222.57</v>
       </c>
       <c r="R68" s="18" t="n">
-        <v>916.45</v>
+        <v>2443.05</v>
       </c>
       <c r="S68" s="18" t="n">
-        <v>800.92</v>
+        <v>2656.82</v>
       </c>
       <c r="T68" s="18" t="n">
-        <v>1501.25</v>
+        <v>2599.75</v>
       </c>
       <c r="U68" s="37" t="n">
-        <v>4226.55</v>
+        <v>9922.190000000001</v>
       </c>
       <c r="V68" s="18" t="n">
-        <v>1681.11</v>
+        <v>2183.23</v>
       </c>
       <c r="W68" s="18" t="n">
-        <v>1374.9</v>
+        <v>2668.58</v>
       </c>
       <c r="X68" s="18" t="n">
-        <v>1994.24</v>
+        <v>1825.58</v>
       </c>
       <c r="Y68" s="18" t="n">
-        <v>3426.25</v>
+        <v>2141.57</v>
       </c>
       <c r="Z68" s="37" t="n">
-        <v>8476.5</v>
+        <v>8818.959999999999</v>
       </c>
       <c r="AA68" s="18" t="n">
-        <v>7068.63</v>
+        <v>1799.01</v>
       </c>
       <c r="AB68" s="19" t="n">
-        <v>5446.73</v>
+        <v>1473.54</v>
       </c>
       <c r="AC68" s="10" t="n"/>
       <c r="AD68" s="10" t="n"/>
@@ -26981,78 +27059,78 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>금융비용</t>
+          <t>법인세비용차감전계속사업이익</t>
         </is>
       </c>
       <c r="E69" s="18" t="n">
-        <v>1023.99</v>
+        <v>-13076.18</v>
       </c>
       <c r="F69" s="9" t="n"/>
       <c r="G69" s="18" t="n">
-        <v>3545.19</v>
+        <v>-9179.870000000001</v>
       </c>
       <c r="H69" s="18" t="n">
-        <v>-505.65</v>
+        <v>14127.13</v>
       </c>
       <c r="I69" s="18" t="n">
-        <v>1320.39</v>
+        <v>3816.19</v>
       </c>
       <c r="J69" s="18" t="n">
-        <v>5311.27</v>
+        <v>7330.48</v>
       </c>
       <c r="K69" s="37" t="n">
-        <v>9671.200000000001</v>
+        <v>16093.93</v>
       </c>
       <c r="L69" s="18" t="n">
-        <v>2243.16</v>
+        <v>-6729.18</v>
       </c>
       <c r="M69" s="18" t="n">
-        <v>2213.17</v>
+        <v>17449.69</v>
       </c>
       <c r="N69" s="18" t="n">
-        <v>2262.61</v>
+        <v>2860.98</v>
       </c>
       <c r="O69" s="18" t="n">
-        <v>2555.28</v>
+        <v>20235.91</v>
       </c>
       <c r="P69" s="37" t="n">
-        <v>9274.219999999999</v>
+        <v>33817.4</v>
       </c>
       <c r="Q69" s="18" t="n">
-        <v>2222.57</v>
+        <v>2731.21</v>
       </c>
       <c r="R69" s="18" t="n">
-        <v>2443.05</v>
+        <v>5665.71</v>
       </c>
       <c r="S69" s="18" t="n">
-        <v>2656.82</v>
+        <v>-3947.47</v>
       </c>
       <c r="T69" s="18" t="n">
-        <v>2599.75</v>
+        <v>19436.5</v>
       </c>
       <c r="U69" s="37" t="n">
-        <v>9922.190000000001</v>
+        <v>23885.95</v>
       </c>
       <c r="V69" s="18" t="n">
-        <v>2183.23</v>
+        <v>16788</v>
       </c>
       <c r="W69" s="18" t="n">
-        <v>2668.58</v>
+        <v>6646.87</v>
       </c>
       <c r="X69" s="18" t="n">
-        <v>1825.58</v>
+        <v>8920.75</v>
       </c>
       <c r="Y69" s="18" t="n">
-        <v>2141.57</v>
+        <v>25594.45</v>
       </c>
       <c r="Z69" s="37" t="n">
-        <v>8818.959999999999</v>
+        <v>57950.07</v>
       </c>
       <c r="AA69" s="18" t="n">
-        <v>1799.01</v>
+        <v>15870.74</v>
       </c>
       <c r="AB69" s="19" t="n">
-        <v>1473.54</v>
+        <v>17631.95</v>
       </c>
       <c r="AC69" s="10" t="n"/>
       <c r="AD69" s="10" t="n"/>
@@ -27074,78 +27152,78 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>법인세비용차감전계속사업이익</t>
+          <t>법인세비용</t>
         </is>
       </c>
       <c r="E70" s="18" t="n">
-        <v>-13076.18</v>
+        <v>-2072.23</v>
       </c>
       <c r="F70" s="9" t="n"/>
       <c r="G70" s="18" t="n">
-        <v>-9179.870000000001</v>
+        <v>-1981.53</v>
       </c>
       <c r="H70" s="18" t="n">
-        <v>14127.13</v>
+        <v>3422.69</v>
       </c>
       <c r="I70" s="18" t="n">
-        <v>3816.19</v>
+        <v>886.03</v>
       </c>
       <c r="J70" s="18" t="n">
-        <v>7330.48</v>
+        <v>813.37</v>
       </c>
       <c r="K70" s="37" t="n">
-        <v>16093.93</v>
+        <v>3140.56</v>
       </c>
       <c r="L70" s="18" t="n">
-        <v>-6729.18</v>
+        <v>-1538.46</v>
       </c>
       <c r="M70" s="18" t="n">
-        <v>17449.69</v>
+        <v>3776.05</v>
       </c>
       <c r="N70" s="18" t="n">
-        <v>2860.98</v>
+        <v>584.4400000000001</v>
       </c>
       <c r="O70" s="18" t="n">
-        <v>20235.91</v>
+        <v>4278.56</v>
       </c>
       <c r="P70" s="37" t="n">
-        <v>33817.4</v>
+        <v>7100.59</v>
       </c>
       <c r="Q70" s="18" t="n">
-        <v>2731.21</v>
+        <v>199.78</v>
       </c>
       <c r="R70" s="18" t="n">
-        <v>5665.71</v>
+        <v>1530.22</v>
       </c>
       <c r="S70" s="18" t="n">
-        <v>-3947.47</v>
+        <v>-816.5599999999999</v>
       </c>
       <c r="T70" s="18" t="n">
-        <v>19436.5</v>
+        <v>4537.28</v>
       </c>
       <c r="U70" s="37" t="n">
-        <v>23885.95</v>
+        <v>5450.72</v>
       </c>
       <c r="V70" s="18" t="n">
-        <v>16788</v>
+        <v>3762.53</v>
       </c>
       <c r="W70" s="18" t="n">
-        <v>6646.87</v>
+        <v>1915.15</v>
       </c>
       <c r="X70" s="18" t="n">
-        <v>8920.75</v>
+        <v>2393.54</v>
       </c>
       <c r="Y70" s="18" t="n">
-        <v>25594.45</v>
+        <v>6375.23</v>
       </c>
       <c r="Z70" s="37" t="n">
-        <v>57950.07</v>
+        <v>14446.45</v>
       </c>
       <c r="AA70" s="18" t="n">
-        <v>15870.74</v>
+        <v>3895.44</v>
       </c>
       <c r="AB70" s="19" t="n">
-        <v>17631.95</v>
+        <v>4099.32</v>
       </c>
       <c r="AC70" s="10" t="n"/>
       <c r="AD70" s="10" t="n"/>
@@ -27167,78 +27245,78 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>법인세비용</t>
+          <t>당기순이익</t>
         </is>
       </c>
       <c r="E71" s="18" t="n">
-        <v>-2072.23</v>
+        <v>-11003.96</v>
       </c>
       <c r="F71" s="9" t="n"/>
       <c r="G71" s="18" t="n">
-        <v>-1981.53</v>
+        <v>-7198.35</v>
       </c>
       <c r="H71" s="18" t="n">
-        <v>3422.69</v>
+        <v>10704.45</v>
       </c>
       <c r="I71" s="18" t="n">
-        <v>886.03</v>
+        <v>2930.16</v>
       </c>
       <c r="J71" s="18" t="n">
-        <v>813.37</v>
+        <v>6517.1</v>
       </c>
       <c r="K71" s="37" t="n">
-        <v>3140.56</v>
+        <v>12953.36</v>
       </c>
       <c r="L71" s="18" t="n">
-        <v>-1538.46</v>
+        <v>-5190.72</v>
       </c>
       <c r="M71" s="18" t="n">
-        <v>3776.05</v>
+        <v>13673.63</v>
       </c>
       <c r="N71" s="18" t="n">
-        <v>584.4400000000001</v>
+        <v>2276.54</v>
       </c>
       <c r="O71" s="18" t="n">
-        <v>4278.56</v>
+        <v>15957.35</v>
       </c>
       <c r="P71" s="37" t="n">
-        <v>7100.59</v>
+        <v>26716.8</v>
       </c>
       <c r="Q71" s="18" t="n">
-        <v>199.78</v>
+        <v>2531.44</v>
       </c>
       <c r="R71" s="18" t="n">
-        <v>1530.22</v>
+        <v>4135.49</v>
       </c>
       <c r="S71" s="18" t="n">
-        <v>-816.5599999999999</v>
+        <v>-3130.91</v>
       </c>
       <c r="T71" s="18" t="n">
-        <v>4537.28</v>
+        <v>14899.22</v>
       </c>
       <c r="U71" s="37" t="n">
-        <v>5450.72</v>
+        <v>18435.24</v>
       </c>
       <c r="V71" s="18" t="n">
-        <v>3762.53</v>
+        <v>13025.47</v>
       </c>
       <c r="W71" s="18" t="n">
-        <v>1915.15</v>
+        <v>4731.72</v>
       </c>
       <c r="X71" s="18" t="n">
-        <v>2393.54</v>
+        <v>6527.21</v>
       </c>
       <c r="Y71" s="18" t="n">
-        <v>6375.23</v>
+        <v>19219.23</v>
       </c>
       <c r="Z71" s="37" t="n">
-        <v>14446.45</v>
+        <v>43503.63</v>
       </c>
       <c r="AA71" s="18" t="n">
-        <v>3895.44</v>
+        <v>11975.3</v>
       </c>
       <c r="AB71" s="19" t="n">
-        <v>4099.32</v>
+        <v>13532.62</v>
       </c>
       <c r="AC71" s="10" t="n"/>
       <c r="AD71" s="10" t="n"/>
@@ -27260,78 +27338,78 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>당기순이익</t>
+          <t>총포괄손익</t>
         </is>
       </c>
       <c r="E72" s="18" t="n">
-        <v>-11003.96</v>
+        <v>-10616.6</v>
       </c>
       <c r="F72" s="9" t="n"/>
       <c r="G72" s="18" t="n">
-        <v>-7198.35</v>
+        <v>-7165.22</v>
       </c>
       <c r="H72" s="18" t="n">
-        <v>10704.45</v>
+        <v>11142.12</v>
       </c>
       <c r="I72" s="18" t="n">
-        <v>2930.16</v>
+        <v>2892.79</v>
       </c>
       <c r="J72" s="18" t="n">
-        <v>6517.1</v>
+        <v>6117.94</v>
       </c>
       <c r="K72" s="37" t="n">
-        <v>12953.36</v>
+        <v>12987.63</v>
       </c>
       <c r="L72" s="18" t="n">
-        <v>-5190.72</v>
+        <v>-5578.4</v>
       </c>
       <c r="M72" s="18" t="n">
-        <v>13673.63</v>
+        <v>13906.48</v>
       </c>
       <c r="N72" s="18" t="n">
-        <v>2276.54</v>
+        <v>2563.1</v>
       </c>
       <c r="O72" s="18" t="n">
-        <v>15957.35</v>
+        <v>13894.33</v>
       </c>
       <c r="P72" s="37" t="n">
-        <v>26716.8</v>
+        <v>24785.51</v>
       </c>
       <c r="Q72" s="18" t="n">
-        <v>2531.44</v>
+        <v>2905.3</v>
       </c>
       <c r="R72" s="18" t="n">
-        <v>4135.49</v>
+        <v>4001.14</v>
       </c>
       <c r="S72" s="18" t="n">
-        <v>-3130.91</v>
+        <v>-3286.51</v>
       </c>
       <c r="T72" s="18" t="n">
-        <v>14899.22</v>
+        <v>13435.78</v>
       </c>
       <c r="U72" s="37" t="n">
-        <v>18435.24</v>
+        <v>17055.71</v>
       </c>
       <c r="V72" s="18" t="n">
-        <v>13025.47</v>
+        <v>13206.62</v>
       </c>
       <c r="W72" s="18" t="n">
-        <v>4731.72</v>
+        <v>5001.56</v>
       </c>
       <c r="X72" s="18" t="n">
-        <v>6527.21</v>
+        <v>7776.1</v>
       </c>
       <c r="Y72" s="18" t="n">
-        <v>19219.23</v>
+        <v>18807.76</v>
       </c>
       <c r="Z72" s="37" t="n">
-        <v>43503.63</v>
+        <v>44792.04</v>
       </c>
       <c r="AA72" s="18" t="n">
-        <v>11975.3</v>
+        <v>10835.52</v>
       </c>
       <c r="AB72" s="19" t="n">
-        <v>13532.62</v>
+        <v>13951.42</v>
       </c>
       <c r="AC72" s="10" t="n"/>
       <c r="AD72" s="10" t="n"/>
@@ -27353,78 +27431,78 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>총포괄손익</t>
+          <t>(지배주주지분)당기순이익</t>
         </is>
       </c>
       <c r="E73" s="18" t="n">
-        <v>-10616.6</v>
+        <v>-11003.96</v>
       </c>
       <c r="F73" s="9" t="n"/>
       <c r="G73" s="18" t="n">
-        <v>-7165.22</v>
+        <v>-7198.35</v>
       </c>
       <c r="H73" s="18" t="n">
-        <v>11142.12</v>
+        <v>10704.45</v>
       </c>
       <c r="I73" s="18" t="n">
-        <v>2892.79</v>
+        <v>2930.16</v>
       </c>
       <c r="J73" s="18" t="n">
-        <v>6117.94</v>
+        <v>6517.1</v>
       </c>
       <c r="K73" s="37" t="n">
-        <v>12987.63</v>
+        <v>12953.36</v>
       </c>
       <c r="L73" s="18" t="n">
-        <v>-5578.4</v>
+        <v>-5190.72</v>
       </c>
       <c r="M73" s="18" t="n">
-        <v>13906.48</v>
+        <v>13673.63</v>
       </c>
       <c r="N73" s="18" t="n">
-        <v>2563.1</v>
+        <v>2276.54</v>
       </c>
       <c r="O73" s="18" t="n">
-        <v>13894.33</v>
+        <v>15957.35</v>
       </c>
       <c r="P73" s="37" t="n">
-        <v>24785.51</v>
+        <v>26716.8</v>
       </c>
       <c r="Q73" s="18" t="n">
-        <v>2905.3</v>
+        <v>2531.44</v>
       </c>
       <c r="R73" s="18" t="n">
-        <v>4001.14</v>
+        <v>4135.49</v>
       </c>
       <c r="S73" s="18" t="n">
-        <v>-3286.51</v>
+        <v>-3130.91</v>
       </c>
       <c r="T73" s="18" t="n">
-        <v>13435.78</v>
+        <v>14899.22</v>
       </c>
       <c r="U73" s="37" t="n">
-        <v>17055.71</v>
+        <v>18435.24</v>
       </c>
       <c r="V73" s="18" t="n">
-        <v>13206.62</v>
+        <v>13025.47</v>
       </c>
       <c r="W73" s="18" t="n">
-        <v>5001.56</v>
+        <v>4731.72</v>
       </c>
       <c r="X73" s="18" t="n">
-        <v>7776.1</v>
+        <v>6527.21</v>
       </c>
       <c r="Y73" s="18" t="n">
-        <v>18807.76</v>
+        <v>19219.23</v>
       </c>
       <c r="Z73" s="37" t="n">
-        <v>44792.04</v>
+        <v>43503.63</v>
       </c>
       <c r="AA73" s="18" t="n">
-        <v>10835.52</v>
+        <v>11975.3</v>
       </c>
       <c r="AB73" s="19" t="n">
-        <v>13951.42</v>
+        <v>13532.62</v>
       </c>
       <c r="AC73" s="10" t="n"/>
       <c r="AD73" s="10" t="n"/>
@@ -27446,7 +27524,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>(지배주주지분)당기순이익</t>
+          <t>계속사업이익</t>
         </is>
       </c>
       <c r="E74" s="18" t="n">
@@ -27539,78 +27617,78 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>계속사업이익</t>
+          <t>영업활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E75" s="18" t="n">
-        <v>-11003.96</v>
+        <v>-12410.61</v>
       </c>
       <c r="F75" s="9" t="n"/>
       <c r="G75" s="18" t="n">
-        <v>-7198.35</v>
+        <v>-17364.91</v>
       </c>
       <c r="H75" s="18" t="n">
-        <v>10704.45</v>
+        <v>11172.5</v>
       </c>
       <c r="I75" s="18" t="n">
-        <v>2930.16</v>
+        <v>3676.47</v>
       </c>
       <c r="J75" s="18" t="n">
-        <v>6517.1</v>
+        <v>26300.65</v>
       </c>
       <c r="K75" s="37" t="n">
-        <v>12953.36</v>
+        <v>23784.71</v>
       </c>
       <c r="L75" s="18" t="n">
-        <v>-5190.72</v>
+        <v>-15248.65</v>
       </c>
       <c r="M75" s="18" t="n">
-        <v>13673.63</v>
+        <v>41024.24</v>
       </c>
       <c r="N75" s="18" t="n">
-        <v>2276.54</v>
+        <v>9517.629999999999</v>
       </c>
       <c r="O75" s="18" t="n">
-        <v>15957.35</v>
+        <v>24026.35</v>
       </c>
       <c r="P75" s="37" t="n">
-        <v>26716.8</v>
+        <v>59319.57</v>
       </c>
       <c r="Q75" s="18" t="n">
-        <v>2531.44</v>
+        <v>10539.85</v>
       </c>
       <c r="R75" s="18" t="n">
-        <v>4135.49</v>
+        <v>7189.76</v>
       </c>
       <c r="S75" s="18" t="n">
-        <v>-3130.91</v>
+        <v>821.97</v>
       </c>
       <c r="T75" s="18" t="n">
-        <v>14899.22</v>
+        <v>2492.57</v>
       </c>
       <c r="U75" s="37" t="n">
-        <v>18435.24</v>
+        <v>21044.15</v>
       </c>
       <c r="V75" s="18" t="n">
-        <v>13025.47</v>
+        <v>2470.1</v>
       </c>
       <c r="W75" s="18" t="n">
-        <v>4731.72</v>
+        <v>33726.72</v>
       </c>
       <c r="X75" s="18" t="n">
-        <v>6527.21</v>
+        <v>25211.65</v>
       </c>
       <c r="Y75" s="18" t="n">
-        <v>19219.23</v>
+        <v>-6863.84</v>
       </c>
       <c r="Z75" s="37" t="n">
-        <v>43503.63</v>
+        <v>54544.63</v>
       </c>
       <c r="AA75" s="18" t="n">
-        <v>11975.3</v>
+        <v>22010.81</v>
       </c>
       <c r="AB75" s="19" t="n">
-        <v>13532.62</v>
+        <v>10035.46</v>
       </c>
       <c r="AC75" s="10" t="n"/>
       <c r="AD75" s="10" t="n"/>
@@ -27632,78 +27710,78 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>영업활동으로인한현금흐름</t>
+          <t>법인세납부(CF)</t>
         </is>
       </c>
       <c r="E76" s="18" t="n">
-        <v>-12410.61</v>
+        <v>-90.83</v>
       </c>
       <c r="F76" s="9" t="n"/>
       <c r="G76" s="18" t="n">
-        <v>-17364.91</v>
+        <v>-5383.76</v>
       </c>
       <c r="H76" s="18" t="n">
-        <v>11172.5</v>
+        <v>-6488.55</v>
       </c>
       <c r="I76" s="18" t="n">
-        <v>3676.47</v>
+        <v>0</v>
       </c>
       <c r="J76" s="18" t="n">
-        <v>26300.65</v>
+        <v>-15.7</v>
       </c>
       <c r="K76" s="37" t="n">
-        <v>23784.71</v>
+        <v>-11888.01</v>
       </c>
       <c r="L76" s="18" t="n">
-        <v>-15248.65</v>
+        <v>-221.59</v>
       </c>
       <c r="M76" s="18" t="n">
-        <v>41024.24</v>
+        <v>431.59</v>
       </c>
       <c r="N76" s="18" t="n">
-        <v>9517.629999999999</v>
+        <v>-909.0700000000001</v>
       </c>
       <c r="O76" s="18" t="n">
-        <v>24026.35</v>
+        <v>-15.28</v>
       </c>
       <c r="P76" s="37" t="n">
-        <v>59319.57</v>
+        <v>-714.35</v>
       </c>
       <c r="Q76" s="18" t="n">
-        <v>10539.85</v>
+        <v>-4166.48</v>
       </c>
       <c r="R76" s="18" t="n">
-        <v>7189.76</v>
+        <v>-4413.6</v>
       </c>
       <c r="S76" s="18" t="n">
-        <v>821.97</v>
+        <v>-3357.13</v>
       </c>
       <c r="T76" s="18" t="n">
-        <v>2492.57</v>
+        <v>-73.86</v>
       </c>
       <c r="U76" s="37" t="n">
-        <v>21044.15</v>
+        <v>-12011.07</v>
       </c>
       <c r="V76" s="18" t="n">
-        <v>2470.1</v>
+        <v>-2256.87</v>
       </c>
       <c r="W76" s="18" t="n">
-        <v>33726.72</v>
+        <v>-2239.25</v>
       </c>
       <c r="X76" s="18" t="n">
-        <v>25211.65</v>
+        <v>-5245.96</v>
       </c>
       <c r="Y76" s="18" t="n">
-        <v>-6863.84</v>
+        <v>151.59</v>
       </c>
       <c r="Z76" s="37" t="n">
-        <v>54544.63</v>
+        <v>-9590.49</v>
       </c>
       <c r="AA76" s="18" t="n">
-        <v>22010.81</v>
+        <v>-3418.15</v>
       </c>
       <c r="AB76" s="19" t="n">
-        <v>10035.46</v>
+        <v>-3681.67</v>
       </c>
       <c r="AC76" s="10" t="n"/>
       <c r="AD76" s="10" t="n"/>
@@ -27725,78 +27803,78 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>법인세납부(CF)</t>
+          <t>투자활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E77" s="18" t="n">
-        <v>-90.83</v>
+        <v>-1436.76</v>
       </c>
       <c r="F77" s="9" t="n"/>
       <c r="G77" s="18" t="n">
-        <v>-5383.76</v>
+        <v>-3771.25</v>
       </c>
       <c r="H77" s="18" t="n">
-        <v>-6488.55</v>
+        <v>-20320.41</v>
       </c>
       <c r="I77" s="18" t="n">
-        <v>0</v>
+        <v>10653.47</v>
       </c>
       <c r="J77" s="18" t="n">
-        <v>-15.7</v>
+        <v>-3272.39</v>
       </c>
       <c r="K77" s="37" t="n">
-        <v>-11888.01</v>
+        <v>-16710.58</v>
       </c>
       <c r="L77" s="18" t="n">
-        <v>-221.59</v>
+        <v>-6108.53</v>
       </c>
       <c r="M77" s="18" t="n">
-        <v>431.59</v>
+        <v>-4336.81</v>
       </c>
       <c r="N77" s="18" t="n">
-        <v>-909.0700000000001</v>
+        <v>-25919.23</v>
       </c>
       <c r="O77" s="18" t="n">
-        <v>-15.28</v>
+        <v>-2868.61</v>
       </c>
       <c r="P77" s="37" t="n">
-        <v>-714.35</v>
+        <v>-39233.18</v>
       </c>
       <c r="Q77" s="18" t="n">
-        <v>-4166.48</v>
+        <v>-4835.19</v>
       </c>
       <c r="R77" s="18" t="n">
-        <v>-4413.6</v>
+        <v>-15773.64</v>
       </c>
       <c r="S77" s="18" t="n">
-        <v>-3357.13</v>
+        <v>-5749.24</v>
       </c>
       <c r="T77" s="18" t="n">
-        <v>-73.86</v>
+        <v>-14569.83</v>
       </c>
       <c r="U77" s="37" t="n">
-        <v>-12011.07</v>
+        <v>-40927.9</v>
       </c>
       <c r="V77" s="18" t="n">
-        <v>-2256.87</v>
+        <v>-2392.26</v>
       </c>
       <c r="W77" s="18" t="n">
-        <v>-2239.25</v>
+        <v>-5760.72</v>
       </c>
       <c r="X77" s="18" t="n">
-        <v>-5245.96</v>
+        <v>-13190.34</v>
       </c>
       <c r="Y77" s="18" t="n">
-        <v>151.59</v>
+        <v>-11161.62</v>
       </c>
       <c r="Z77" s="37" t="n">
-        <v>-9590.49</v>
+        <v>-32504.94</v>
       </c>
       <c r="AA77" s="18" t="n">
-        <v>-3418.15</v>
+        <v>-4305.79</v>
       </c>
       <c r="AB77" s="19" t="n">
-        <v>-3681.67</v>
+        <v>-19083.89</v>
       </c>
       <c r="AC77" s="10" t="n"/>
       <c r="AD77" s="10" t="n"/>
@@ -27818,79 +27896,66 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>투자활동으로인한현금흐름</t>
+          <t>유형자산의감소</t>
         </is>
       </c>
       <c r="E78" s="18" t="n">
-        <v>-1436.76</v>
+        <v>0</v>
       </c>
       <c r="F78" s="9" t="n"/>
       <c r="G78" s="18" t="n">
-        <v>-3771.25</v>
+        <v>1</v>
       </c>
       <c r="H78" s="18" t="n">
-        <v>-20320.41</v>
+        <v>11.09</v>
       </c>
       <c r="I78" s="18" t="n">
-        <v>10653.47</v>
+        <v>0</v>
       </c>
       <c r="J78" s="18" t="n">
-        <v>-3272.39</v>
+        <v>2.6</v>
       </c>
       <c r="K78" s="37" t="n">
-        <v>-16710.58</v>
+        <v>14.69</v>
       </c>
       <c r="L78" s="18" t="n">
-        <v>-6108.53</v>
+        <v>2343.53</v>
       </c>
       <c r="M78" s="18" t="n">
-        <v>-4336.81</v>
+        <v>0</v>
       </c>
       <c r="N78" s="18" t="n">
-        <v>-25919.23</v>
+        <v>0</v>
       </c>
       <c r="O78" s="18" t="n">
-        <v>-2868.61</v>
+        <v>0</v>
       </c>
       <c r="P78" s="37" t="n">
-        <v>-39233.18</v>
+        <v>2343.53</v>
       </c>
       <c r="Q78" s="18" t="n">
-        <v>-4835.19</v>
+        <v>0</v>
       </c>
       <c r="R78" s="18" t="n">
-        <v>-15773.64</v>
+        <v>0</v>
       </c>
       <c r="S78" s="18" t="n">
-        <v>-5749.24</v>
+        <v>1.8</v>
       </c>
       <c r="T78" s="18" t="n">
-        <v>-14569.83</v>
+        <v>0</v>
       </c>
       <c r="U78" s="37" t="n">
-        <v>-40927.9</v>
-      </c>
-      <c r="V78" s="18" t="n">
-        <v>-2392.26</v>
-      </c>
-      <c r="W78" s="18" t="n">
-        <v>-5760.72</v>
+        <v>1.8</v>
       </c>
       <c r="X78" s="18" t="n">
-        <v>-13190.34</v>
+        <v>0</v>
       </c>
       <c r="Y78" s="18" t="n">
-        <v>-11161.62</v>
-      </c>
-      <c r="Z78" s="37" t="n">
-        <v>-32504.94</v>
-      </c>
-      <c r="AA78" s="18" t="n">
-        <v>-4305.79</v>
-      </c>
-      <c r="AB78" s="19" t="n">
-        <v>-19083.89</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z78" s="9" t="n"/>
+      <c r="AB78" s="5" t="n"/>
       <c r="AC78" s="10" t="n"/>
       <c r="AD78" s="10" t="n"/>
       <c r="AE78" s="11" t="n"/>
@@ -27911,66 +27976,79 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>유형자산의감소</t>
+          <t>유형자산의증가</t>
         </is>
       </c>
       <c r="E79" s="18" t="n">
-        <v>0</v>
+        <v>1692.22</v>
       </c>
       <c r="F79" s="9" t="n"/>
       <c r="G79" s="18" t="n">
-        <v>1</v>
+        <v>3841.43</v>
       </c>
       <c r="H79" s="18" t="n">
-        <v>11.09</v>
+        <v>2405.5</v>
       </c>
       <c r="I79" s="18" t="n">
-        <v>0</v>
+        <v>6644.12</v>
       </c>
       <c r="J79" s="18" t="n">
-        <v>2.6</v>
+        <v>2624.27</v>
       </c>
       <c r="K79" s="37" t="n">
-        <v>14.69</v>
+        <v>15515.32</v>
       </c>
       <c r="L79" s="18" t="n">
-        <v>2343.53</v>
+        <v>1483.08</v>
       </c>
       <c r="M79" s="18" t="n">
-        <v>0</v>
+        <v>3568.18</v>
       </c>
       <c r="N79" s="18" t="n">
-        <v>0</v>
+        <v>37637.11</v>
       </c>
       <c r="O79" s="18" t="n">
-        <v>0</v>
+        <v>196.4</v>
       </c>
       <c r="P79" s="37" t="n">
-        <v>2343.53</v>
+        <v>42884.77</v>
       </c>
       <c r="Q79" s="18" t="n">
-        <v>0</v>
+        <v>3230.19</v>
       </c>
       <c r="R79" s="18" t="n">
-        <v>0</v>
+        <v>2692.3</v>
       </c>
       <c r="S79" s="18" t="n">
-        <v>1.8</v>
+        <v>4586.04</v>
       </c>
       <c r="T79" s="18" t="n">
-        <v>0</v>
+        <v>7221.73</v>
       </c>
       <c r="U79" s="37" t="n">
-        <v>1.8</v>
+        <v>17730.26</v>
+      </c>
+      <c r="V79" s="18" t="n">
+        <v>2469.29</v>
+      </c>
+      <c r="W79" s="18" t="n">
+        <v>1004.01</v>
       </c>
       <c r="X79" s="18" t="n">
-        <v>0</v>
+        <v>1405.23</v>
       </c>
       <c r="Y79" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z79" s="9" t="n"/>
-      <c r="AB79" s="5" t="n"/>
+        <v>3428.12</v>
+      </c>
+      <c r="Z79" s="37" t="n">
+        <v>8306.65</v>
+      </c>
+      <c r="AA79" s="18" t="n">
+        <v>2279.43</v>
+      </c>
+      <c r="AB79" s="19" t="n">
+        <v>6139.5</v>
+      </c>
       <c r="AC79" s="10" t="n"/>
       <c r="AD79" s="10" t="n"/>
       <c r="AE79" s="11" t="n"/>
@@ -27991,7 +28069,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>유형자산의증가</t>
+          <t>CAPEX</t>
         </is>
       </c>
       <c r="E80" s="18" t="n">
@@ -28005,34 +28083,34 @@
         <v>2405.5</v>
       </c>
       <c r="I80" s="18" t="n">
-        <v>6644.12</v>
+        <v>7056.97</v>
       </c>
       <c r="J80" s="18" t="n">
         <v>2624.27</v>
       </c>
       <c r="K80" s="37" t="n">
-        <v>15515.32</v>
+        <v>15928.17</v>
       </c>
       <c r="L80" s="18" t="n">
         <v>1483.08</v>
       </c>
       <c r="M80" s="18" t="n">
-        <v>3568.18</v>
+        <v>3962.18</v>
       </c>
       <c r="N80" s="18" t="n">
-        <v>37637.11</v>
+        <v>37645.78</v>
       </c>
       <c r="O80" s="18" t="n">
         <v>196.4</v>
       </c>
       <c r="P80" s="37" t="n">
-        <v>42884.77</v>
+        <v>43287.44</v>
       </c>
       <c r="Q80" s="18" t="n">
         <v>3230.19</v>
       </c>
       <c r="R80" s="18" t="n">
-        <v>2692.3</v>
+        <v>2792.3</v>
       </c>
       <c r="S80" s="18" t="n">
         <v>4586.04</v>
@@ -28041,7 +28119,7 @@
         <v>7221.73</v>
       </c>
       <c r="U80" s="37" t="n">
-        <v>17730.26</v>
+        <v>17830.26</v>
       </c>
       <c r="V80" s="18" t="n">
         <v>2469.29</v>
@@ -28084,79 +28162,36 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>CAPEX</t>
+          <t>무형자산의증가</t>
         </is>
       </c>
       <c r="E81" s="18" t="n">
-        <v>1692.22</v>
+        <v>0</v>
       </c>
       <c r="F81" s="9" t="n"/>
-      <c r="G81" s="18" t="n">
-        <v>3841.43</v>
-      </c>
-      <c r="H81" s="18" t="n">
-        <v>2405.5</v>
-      </c>
-      <c r="I81" s="18" t="n">
-        <v>7056.97</v>
-      </c>
       <c r="J81" s="18" t="n">
-        <v>2624.27</v>
-      </c>
-      <c r="K81" s="37" t="n">
-        <v>15928.17</v>
-      </c>
-      <c r="L81" s="18" t="n">
-        <v>1483.08</v>
-      </c>
-      <c r="M81" s="18" t="n">
-        <v>3962.18</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K81" s="9" t="n"/>
       <c r="N81" s="18" t="n">
-        <v>37645.78</v>
+        <v>8.67</v>
       </c>
       <c r="O81" s="18" t="n">
-        <v>196.4</v>
-      </c>
-      <c r="P81" s="37" t="n">
-        <v>43287.44</v>
-      </c>
-      <c r="Q81" s="18" t="n">
-        <v>3230.19</v>
-      </c>
-      <c r="R81" s="18" t="n">
-        <v>2792.3</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P81" s="9" t="n"/>
       <c r="S81" s="18" t="n">
-        <v>4586.04</v>
+        <v>0</v>
       </c>
       <c r="T81" s="18" t="n">
-        <v>7221.73</v>
-      </c>
-      <c r="U81" s="37" t="n">
-        <v>17830.26</v>
-      </c>
-      <c r="V81" s="18" t="n">
-        <v>2469.29</v>
-      </c>
-      <c r="W81" s="18" t="n">
-        <v>1004.01</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="U81" s="9" t="n"/>
       <c r="X81" s="18" t="n">
-        <v>1405.23</v>
-      </c>
-      <c r="Y81" s="18" t="n">
-        <v>3428.12</v>
-      </c>
-      <c r="Z81" s="37" t="n">
-        <v>8306.65</v>
-      </c>
-      <c r="AA81" s="18" t="n">
-        <v>2279.43</v>
-      </c>
-      <c r="AB81" s="19" t="n">
-        <v>6139.5</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="Z81" s="9" t="n"/>
+      <c r="AB81" s="5" t="n"/>
       <c r="AC81" s="10" t="n"/>
       <c r="AD81" s="10" t="n"/>
       <c r="AE81" s="11" t="n"/>
@@ -28177,36 +28212,79 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>무형자산의증가</t>
+          <t>재무활동으로인한현금흐름</t>
         </is>
       </c>
       <c r="E82" s="18" t="n">
-        <v>0</v>
+        <v>13643.42</v>
       </c>
       <c r="F82" s="9" t="n"/>
+      <c r="G82" s="18" t="n">
+        <v>23476.97</v>
+      </c>
+      <c r="H82" s="18" t="n">
+        <v>-11702.81</v>
+      </c>
+      <c r="I82" s="18" t="n">
+        <v>1032.37</v>
+      </c>
       <c r="J82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K82" s="9" t="n"/>
+        <v>-4189.6</v>
+      </c>
+      <c r="K82" s="37" t="n">
+        <v>8616.93</v>
+      </c>
+      <c r="L82" s="18" t="n">
+        <v>-772.77</v>
+      </c>
+      <c r="M82" s="18" t="n">
+        <v>-32018.97</v>
+      </c>
       <c r="N82" s="18" t="n">
-        <v>8.67</v>
+        <v>16178.66</v>
       </c>
       <c r="O82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" s="9" t="n"/>
+        <v>-10904.13</v>
+      </c>
+      <c r="P82" s="37" t="n">
+        <v>-27517.21</v>
+      </c>
+      <c r="Q82" s="18" t="n">
+        <v>8382.43</v>
+      </c>
+      <c r="R82" s="18" t="n">
+        <v>-16894.3</v>
+      </c>
       <c r="S82" s="18" t="n">
-        <v>0</v>
+        <v>36489.85</v>
       </c>
       <c r="T82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" s="9" t="n"/>
+        <v>4137.18</v>
+      </c>
+      <c r="U82" s="37" t="n">
+        <v>32115.16</v>
+      </c>
+      <c r="V82" s="18" t="n">
+        <v>-1992.35</v>
+      </c>
+      <c r="W82" s="18" t="n">
+        <v>-13324.52</v>
+      </c>
       <c r="X82" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" s="9" t="n"/>
-      <c r="AB82" s="5" t="n"/>
+        <v>-1934.4</v>
+      </c>
+      <c r="Y82" s="18" t="n">
+        <v>-26154.69</v>
+      </c>
+      <c r="Z82" s="37" t="n">
+        <v>-43405.96</v>
+      </c>
+      <c r="AA82" s="18" t="n">
+        <v>-1678.09</v>
+      </c>
+      <c r="AB82" s="19" t="n">
+        <v>-14470.03</v>
+      </c>
       <c r="AC82" s="10" t="n"/>
       <c r="AD82" s="10" t="n"/>
       <c r="AE82" s="11" t="n"/>
@@ -28227,78 +28305,78 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>재무활동으로인한현금흐름</t>
+          <t>단기차입금의증가</t>
         </is>
       </c>
       <c r="E83" s="18" t="n">
-        <v>13643.42</v>
+        <v>0</v>
       </c>
       <c r="F83" s="9" t="n"/>
       <c r="G83" s="18" t="n">
-        <v>23476.97</v>
+        <v>45905.2</v>
       </c>
       <c r="H83" s="18" t="n">
-        <v>-11702.81</v>
+        <v>15550</v>
       </c>
       <c r="I83" s="18" t="n">
-        <v>1032.37</v>
+        <v>24914.06</v>
       </c>
       <c r="J83" s="18" t="n">
-        <v>-4189.6</v>
+        <v>20888</v>
       </c>
       <c r="K83" s="37" t="n">
-        <v>8616.93</v>
+        <v>107257.26</v>
       </c>
       <c r="L83" s="18" t="n">
-        <v>-772.77</v>
+        <v>0</v>
       </c>
       <c r="M83" s="18" t="n">
-        <v>-32018.97</v>
+        <v>55000</v>
       </c>
       <c r="N83" s="18" t="n">
-        <v>16178.66</v>
+        <v>36200</v>
       </c>
       <c r="O83" s="18" t="n">
-        <v>-10904.13</v>
+        <v>5000</v>
       </c>
       <c r="P83" s="37" t="n">
-        <v>-27517.21</v>
+        <v>96200</v>
       </c>
       <c r="Q83" s="18" t="n">
-        <v>8382.43</v>
+        <v>50000</v>
       </c>
       <c r="R83" s="18" t="n">
-        <v>-16894.3</v>
+        <v>40000</v>
       </c>
       <c r="S83" s="18" t="n">
-        <v>36489.85</v>
+        <v>66200</v>
       </c>
       <c r="T83" s="18" t="n">
-        <v>4137.18</v>
+        <v>0</v>
       </c>
       <c r="U83" s="37" t="n">
-        <v>32115.16</v>
+        <v>156200</v>
       </c>
       <c r="V83" s="18" t="n">
-        <v>-1992.35</v>
+        <v>70000</v>
       </c>
       <c r="W83" s="18" t="n">
-        <v>-13324.52</v>
+        <v>0</v>
       </c>
       <c r="X83" s="18" t="n">
-        <v>-1934.4</v>
+        <v>50000</v>
       </c>
       <c r="Y83" s="18" t="n">
-        <v>-26154.69</v>
+        <v>520</v>
       </c>
       <c r="Z83" s="37" t="n">
-        <v>-43405.96</v>
+        <v>120520</v>
       </c>
       <c r="AA83" s="18" t="n">
-        <v>-1678.09</v>
+        <v>45000</v>
       </c>
       <c r="AB83" s="19" t="n">
-        <v>-14470.03</v>
+        <v>30000</v>
       </c>
       <c r="AC83" s="10" t="n"/>
       <c r="AD83" s="10" t="n"/>
@@ -28320,79 +28398,44 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>단기차입금의증가</t>
+          <t>장기차입금의증가</t>
         </is>
       </c>
       <c r="E84" s="18" t="n">
-        <v>0</v>
+        <v>15000</v>
       </c>
       <c r="F84" s="9" t="n"/>
       <c r="G84" s="18" t="n">
-        <v>45905.2</v>
+        <v>30000</v>
       </c>
       <c r="H84" s="18" t="n">
-        <v>15550</v>
+        <v>10000</v>
       </c>
       <c r="I84" s="18" t="n">
-        <v>24914.06</v>
+        <v>0</v>
       </c>
       <c r="J84" s="18" t="n">
-        <v>20888</v>
+        <v>28000</v>
       </c>
       <c r="K84" s="37" t="n">
-        <v>107257.26</v>
+        <v>68000</v>
       </c>
       <c r="L84" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="M84" s="18" t="n">
-        <v>55000</v>
-      </c>
-      <c r="N84" s="18" t="n">
-        <v>36200</v>
-      </c>
       <c r="O84" s="18" t="n">
-        <v>5000</v>
-      </c>
-      <c r="P84" s="37" t="n">
-        <v>96200</v>
-      </c>
-      <c r="Q84" s="18" t="n">
-        <v>50000</v>
-      </c>
-      <c r="R84" s="18" t="n">
-        <v>40000</v>
-      </c>
-      <c r="S84" s="18" t="n">
-        <v>66200</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P84" s="9" t="n"/>
       <c r="T84" s="18" t="n">
+        <v>5800</v>
+      </c>
+      <c r="U84" s="9" t="n"/>
+      <c r="Y84" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U84" s="37" t="n">
-        <v>156200</v>
-      </c>
-      <c r="V84" s="18" t="n">
-        <v>70000</v>
-      </c>
-      <c r="W84" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="X84" s="18" t="n">
-        <v>50000</v>
-      </c>
-      <c r="Y84" s="18" t="n">
-        <v>520</v>
-      </c>
-      <c r="Z84" s="37" t="n">
-        <v>120520</v>
-      </c>
-      <c r="AA84" s="18" t="n">
-        <v>45000</v>
-      </c>
-      <c r="AB84" s="19" t="n">
-        <v>30000</v>
-      </c>
+      <c r="Z84" s="9" t="n"/>
+      <c r="AB84" s="5" t="n"/>
       <c r="AC84" s="10" t="n"/>
       <c r="AD84" s="10" t="n"/>
       <c r="AE84" s="11" t="n"/>
@@ -28413,44 +28456,79 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>장기차입금의증가</t>
+          <t>리스부채의상환</t>
         </is>
       </c>
       <c r="E85" s="18" t="n">
-        <v>15000</v>
+        <v>634.77</v>
       </c>
       <c r="F85" s="9" t="n"/>
       <c r="G85" s="18" t="n">
-        <v>30000</v>
+        <v>523.03</v>
       </c>
       <c r="H85" s="18" t="n">
-        <v>10000</v>
+        <v>479.69</v>
       </c>
       <c r="I85" s="18" t="n">
-        <v>0</v>
+        <v>280.64</v>
       </c>
       <c r="J85" s="18" t="n">
-        <v>28000</v>
+        <v>176.59</v>
       </c>
       <c r="K85" s="37" t="n">
-        <v>68000</v>
+        <v>1459.95</v>
       </c>
       <c r="L85" s="18" t="n">
-        <v>0</v>
+        <v>172.77</v>
+      </c>
+      <c r="M85" s="18" t="n">
+        <v>184.31</v>
+      </c>
+      <c r="N85" s="18" t="n">
+        <v>221.34</v>
       </c>
       <c r="O85" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" s="9" t="n"/>
+        <v>304.13</v>
+      </c>
+      <c r="P85" s="37" t="n">
+        <v>882.55</v>
+      </c>
+      <c r="Q85" s="18" t="n">
+        <v>307.58</v>
+      </c>
+      <c r="R85" s="18" t="n">
+        <v>314.74</v>
+      </c>
+      <c r="S85" s="18" t="n">
+        <v>310.15</v>
+      </c>
       <c r="T85" s="18" t="n">
-        <v>5800</v>
-      </c>
-      <c r="U85" s="9" t="n"/>
+        <v>312.82</v>
+      </c>
+      <c r="U85" s="37" t="n">
+        <v>1245.29</v>
+      </c>
+      <c r="V85" s="18" t="n">
+        <v>642.35</v>
+      </c>
+      <c r="W85" s="18" t="n">
+        <v>604.62</v>
+      </c>
+      <c r="X85" s="18" t="n">
+        <v>584.41</v>
+      </c>
       <c r="Y85" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z85" s="9" t="n"/>
-      <c r="AB85" s="5" t="n"/>
+        <v>624.6900000000001</v>
+      </c>
+      <c r="Z85" s="37" t="n">
+        <v>2456.07</v>
+      </c>
+      <c r="AA85" s="18" t="n">
+        <v>628.09</v>
+      </c>
+      <c r="AB85" s="19" t="n">
+        <v>628.9</v>
+      </c>
       <c r="AC85" s="10" t="n"/>
       <c r="AD85" s="10" t="n"/>
       <c r="AE85" s="11" t="n"/>
@@ -28471,79 +28549,24 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>리스부채의상환</t>
+          <t>자기주식의취득</t>
         </is>
       </c>
       <c r="E86" s="18" t="n">
-        <v>634.77</v>
+        <v>0</v>
       </c>
       <c r="F86" s="9" t="n"/>
       <c r="G86" s="18" t="n">
-        <v>523.03</v>
-      </c>
-      <c r="H86" s="18" t="n">
-        <v>479.69</v>
-      </c>
-      <c r="I86" s="18" t="n">
-        <v>280.64</v>
+        <v>0</v>
       </c>
       <c r="J86" s="18" t="n">
-        <v>176.59</v>
-      </c>
-      <c r="K86" s="37" t="n">
-        <v>1459.95</v>
-      </c>
-      <c r="L86" s="18" t="n">
-        <v>172.77</v>
-      </c>
-      <c r="M86" s="18" t="n">
-        <v>184.31</v>
-      </c>
-      <c r="N86" s="18" t="n">
-        <v>221.34</v>
-      </c>
-      <c r="O86" s="18" t="n">
-        <v>304.13</v>
-      </c>
-      <c r="P86" s="37" t="n">
-        <v>882.55</v>
-      </c>
-      <c r="Q86" s="18" t="n">
-        <v>307.58</v>
-      </c>
-      <c r="R86" s="18" t="n">
-        <v>314.74</v>
-      </c>
-      <c r="S86" s="18" t="n">
-        <v>310.15</v>
-      </c>
-      <c r="T86" s="18" t="n">
-        <v>312.82</v>
-      </c>
-      <c r="U86" s="37" t="n">
-        <v>1245.29</v>
-      </c>
-      <c r="V86" s="18" t="n">
-        <v>642.35</v>
-      </c>
-      <c r="W86" s="18" t="n">
-        <v>604.62</v>
-      </c>
-      <c r="X86" s="18" t="n">
-        <v>584.41</v>
-      </c>
-      <c r="Y86" s="18" t="n">
-        <v>624.6900000000001</v>
-      </c>
-      <c r="Z86" s="37" t="n">
-        <v>2456.07</v>
-      </c>
-      <c r="AA86" s="18" t="n">
-        <v>628.09</v>
-      </c>
-      <c r="AB86" s="19" t="n">
-        <v>628.9</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="K86" s="9" t="n"/>
+      <c r="P86" s="9" t="n"/>
+      <c r="U86" s="9" t="n"/>
+      <c r="Z86" s="9" t="n"/>
+      <c r="AB86" s="5" t="n"/>
       <c r="AC86" s="10" t="n"/>
       <c r="AD86" s="10" t="n"/>
       <c r="AE86" s="11" t="n"/>
@@ -28564,22 +28587,40 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>자기주식의취득</t>
+          <t>배당금지급</t>
         </is>
       </c>
       <c r="E87" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F87" s="9" t="n"/>
-      <c r="G87" s="18" t="n">
+      <c r="I87" s="18" t="n">
         <v>0</v>
       </c>
       <c r="J87" s="18" t="n">
         <v>0</v>
       </c>
       <c r="K87" s="9" t="n"/>
+      <c r="N87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="P87" s="9" t="n"/>
+      <c r="S87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="U87" s="9" t="n"/>
+      <c r="X87" s="18" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="Z87" s="9" t="n"/>
       <c r="AB87" s="5" t="n"/>
       <c r="AC87" s="10" t="n"/>
@@ -28602,42 +28643,79 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>배당금지급</t>
+          <t>단기차입금의감소</t>
         </is>
       </c>
       <c r="E88" s="18" t="n">
         <v>0</v>
       </c>
       <c r="F88" s="9" t="n"/>
+      <c r="G88" s="18" t="n">
+        <v>35905.2</v>
+      </c>
+      <c r="H88" s="18" t="n">
+        <v>17550</v>
+      </c>
       <c r="I88" s="18" t="n">
+        <v>21501.06</v>
+      </c>
+      <c r="J88" s="18" t="n">
+        <v>24301</v>
+      </c>
+      <c r="K88" s="37" t="n">
+        <v>99257.25999999999</v>
+      </c>
+      <c r="L88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="J88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="K88" s="9" t="n"/>
+      <c r="M88" s="18" t="n">
+        <v>33000</v>
+      </c>
       <c r="N88" s="18" t="n">
-        <v>0</v>
+        <v>20000</v>
       </c>
       <c r="O88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="P88" s="9" t="n"/>
+      <c r="P88" s="37" t="n">
+        <v>53000</v>
+      </c>
+      <c r="Q88" s="18" t="n">
+        <v>10000</v>
+      </c>
+      <c r="R88" s="18" t="n">
+        <v>45000</v>
+      </c>
       <c r="S88" s="18" t="n">
-        <v>0</v>
+        <v>41200</v>
       </c>
       <c r="T88" s="18" t="n">
         <v>0</v>
       </c>
-      <c r="U88" s="9" t="n"/>
+      <c r="U88" s="37" t="n">
+        <v>96200</v>
+      </c>
+      <c r="V88" s="18" t="n">
+        <v>70000</v>
+      </c>
+      <c r="W88" s="18" t="n">
+        <v>0</v>
+      </c>
       <c r="X88" s="18" t="n">
-        <v>0</v>
+        <v>116200</v>
       </c>
       <c r="Y88" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z88" s="9" t="n"/>
-      <c r="AB88" s="5" t="n"/>
+        <v>25000</v>
+      </c>
+      <c r="Z88" s="37" t="n">
+        <v>211200</v>
+      </c>
+      <c r="AA88" s="18" t="n">
+        <v>45000</v>
+      </c>
+      <c r="AB88" s="19" t="n">
+        <v>30000</v>
+      </c>
       <c r="AC88" s="10" t="n"/>
       <c r="AD88" s="10" t="n"/>
       <c r="AE88" s="11" t="n"/>
@@ -28658,78 +28736,78 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>단기차입금의감소</t>
+          <t>유동성장기부채의감소</t>
         </is>
       </c>
       <c r="E89" s="18" t="n">
-        <v>0</v>
+        <v>700</v>
       </c>
       <c r="F89" s="9" t="n"/>
       <c r="G89" s="18" t="n">
-        <v>35905.2</v>
+        <v>16000</v>
       </c>
       <c r="H89" s="18" t="n">
-        <v>17550</v>
+        <v>11000</v>
       </c>
       <c r="I89" s="18" t="n">
-        <v>21501.06</v>
+        <v>2100</v>
       </c>
       <c r="J89" s="18" t="n">
-        <v>24301</v>
+        <v>15600</v>
       </c>
       <c r="K89" s="37" t="n">
-        <v>99257.25999999999</v>
+        <v>44700</v>
       </c>
       <c r="L89" s="18" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="M89" s="18" t="n">
-        <v>33000</v>
+        <v>30600</v>
       </c>
       <c r="N89" s="18" t="n">
-        <v>20000</v>
+        <v>26800</v>
       </c>
       <c r="O89" s="18" t="n">
-        <v>0</v>
+        <v>15600</v>
       </c>
       <c r="P89" s="37" t="n">
-        <v>53000</v>
+        <v>73600</v>
       </c>
       <c r="Q89" s="18" t="n">
-        <v>10000</v>
+        <v>40600</v>
       </c>
       <c r="R89" s="18" t="n">
-        <v>45000</v>
+        <v>600</v>
       </c>
       <c r="S89" s="18" t="n">
-        <v>41200</v>
+        <v>15600</v>
       </c>
       <c r="T89" s="18" t="n">
-        <v>0</v>
+        <v>600</v>
       </c>
       <c r="U89" s="37" t="n">
-        <v>96200</v>
+        <v>57400</v>
       </c>
       <c r="V89" s="18" t="n">
-        <v>70000</v>
+        <v>1350</v>
       </c>
       <c r="W89" s="18" t="n">
-        <v>0</v>
+        <v>1350</v>
       </c>
       <c r="X89" s="18" t="n">
-        <v>116200</v>
+        <v>41350</v>
       </c>
       <c r="Y89" s="18" t="n">
-        <v>25000</v>
+        <v>1050</v>
       </c>
       <c r="Z89" s="37" t="n">
-        <v>211200</v>
+        <v>45100</v>
       </c>
       <c r="AA89" s="18" t="n">
-        <v>45000</v>
+        <v>1050</v>
       </c>
       <c r="AB89" s="19" t="n">
-        <v>30000</v>
+        <v>1050</v>
       </c>
       <c r="AC89" s="10" t="n"/>
       <c r="AD89" s="10" t="n"/>
@@ -28751,78 +28829,78 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>유동성장기부채의감소</t>
+          <t>현금및현금성자산의증감</t>
         </is>
       </c>
       <c r="E90" s="18" t="n">
-        <v>700</v>
+        <v>-265.87</v>
       </c>
       <c r="F90" s="9" t="n"/>
       <c r="G90" s="18" t="n">
-        <v>16000</v>
+        <v>2746.19</v>
       </c>
       <c r="H90" s="18" t="n">
-        <v>11000</v>
+        <v>-21131.04</v>
       </c>
       <c r="I90" s="18" t="n">
-        <v>2100</v>
+        <v>16251.66</v>
       </c>
       <c r="J90" s="18" t="n">
-        <v>15600</v>
+        <v>15638.71</v>
       </c>
       <c r="K90" s="37" t="n">
-        <v>44700</v>
+        <v>13505.52</v>
       </c>
       <c r="L90" s="18" t="n">
-        <v>600</v>
+        <v>-21842.26</v>
       </c>
       <c r="M90" s="18" t="n">
-        <v>30600</v>
+        <v>4372.7</v>
       </c>
       <c r="N90" s="18" t="n">
-        <v>26800</v>
+        <v>27.1</v>
       </c>
       <c r="O90" s="18" t="n">
-        <v>15600</v>
+        <v>9844.09</v>
       </c>
       <c r="P90" s="37" t="n">
-        <v>73600</v>
+        <v>-7598.37</v>
       </c>
       <c r="Q90" s="18" t="n">
-        <v>40600</v>
+        <v>14193.74</v>
       </c>
       <c r="R90" s="18" t="n">
-        <v>600</v>
+        <v>-25563.62</v>
       </c>
       <c r="S90" s="18" t="n">
-        <v>15600</v>
+        <v>31405.01</v>
       </c>
       <c r="T90" s="18" t="n">
-        <v>600</v>
+        <v>-7685.52</v>
       </c>
       <c r="U90" s="37" t="n">
-        <v>57400</v>
+        <v>12349.61</v>
       </c>
       <c r="V90" s="18" t="n">
-        <v>1350</v>
+        <v>-1837.06</v>
       </c>
       <c r="W90" s="18" t="n">
-        <v>1350</v>
+        <v>14067.22</v>
       </c>
       <c r="X90" s="18" t="n">
-        <v>41350</v>
+        <v>10591.9</v>
       </c>
       <c r="Y90" s="18" t="n">
-        <v>1050</v>
+        <v>-44205.18</v>
       </c>
       <c r="Z90" s="37" t="n">
-        <v>45100</v>
+        <v>-21383.12</v>
       </c>
       <c r="AA90" s="18" t="n">
-        <v>1050</v>
+        <v>16082.94</v>
       </c>
       <c r="AB90" s="19" t="n">
-        <v>1050</v>
+        <v>-23404.37</v>
       </c>
       <c r="AC90" s="10" t="n"/>
       <c r="AD90" s="10" t="n"/>
@@ -28844,7 +28922,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>현금및현금성자산의증감</t>
+          <t>기말현금및현금성자산</t>
         </is>
       </c>
       <c r="E91" s="18" t="n">
@@ -28852,22 +28930,22 @@
       </c>
       <c r="F91" s="9" t="n"/>
       <c r="G91" s="18" t="n">
-        <v>2746.19</v>
+        <v>29348.29</v>
       </c>
       <c r="H91" s="18" t="n">
-        <v>-21131.04</v>
+        <v>-21131.05</v>
       </c>
       <c r="I91" s="18" t="n">
-        <v>16251.66</v>
+        <v>16251.67</v>
       </c>
       <c r="J91" s="18" t="n">
         <v>15638.71</v>
       </c>
       <c r="K91" s="37" t="n">
-        <v>13505.52</v>
+        <v>40107.62</v>
       </c>
       <c r="L91" s="18" t="n">
-        <v>-21842.26</v>
+        <v>18265.36</v>
       </c>
       <c r="M91" s="18" t="n">
         <v>4372.7</v>
@@ -28879,10 +28957,10 @@
         <v>9844.09</v>
       </c>
       <c r="P91" s="37" t="n">
-        <v>-7598.37</v>
+        <v>32509.25</v>
       </c>
       <c r="Q91" s="18" t="n">
-        <v>14193.74</v>
+        <v>46702.99</v>
       </c>
       <c r="R91" s="18" t="n">
         <v>-25563.62</v>
@@ -28894,10 +28972,10 @@
         <v>-7685.52</v>
       </c>
       <c r="U91" s="37" t="n">
-        <v>12349.61</v>
+        <v>44858.86</v>
       </c>
       <c r="V91" s="18" t="n">
-        <v>-1837.06</v>
+        <v>43021.8</v>
       </c>
       <c r="W91" s="18" t="n">
         <v>14067.22</v>
@@ -28906,16 +28984,16 @@
         <v>10591.9</v>
       </c>
       <c r="Y91" s="18" t="n">
-        <v>-44205.18</v>
+        <v>-44205.17</v>
       </c>
       <c r="Z91" s="37" t="n">
-        <v>-21383.12</v>
+        <v>23475.75</v>
       </c>
       <c r="AA91" s="18" t="n">
-        <v>16082.94</v>
+        <v>39558.69</v>
       </c>
       <c r="AB91" s="19" t="n">
-        <v>-23404.37</v>
+        <v>-23404.38</v>
       </c>
       <c r="AC91" s="10" t="n"/>
       <c r="AD91" s="10" t="n"/>
@@ -28937,79 +29015,18 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>기말현금및현금성자산</t>
-        </is>
-      </c>
-      <c r="E92" s="18" t="n">
-        <v>-265.87</v>
+          <t>배당금수취(CF)</t>
+        </is>
       </c>
       <c r="F92" s="9" t="n"/>
-      <c r="G92" s="18" t="n">
-        <v>29348.29</v>
-      </c>
-      <c r="H92" s="18" t="n">
-        <v>-21131.05</v>
-      </c>
-      <c r="I92" s="18" t="n">
-        <v>16251.67</v>
-      </c>
-      <c r="J92" s="18" t="n">
-        <v>15638.71</v>
-      </c>
-      <c r="K92" s="37" t="n">
-        <v>40107.62</v>
-      </c>
+      <c r="K92" s="9" t="n"/>
       <c r="L92" s="18" t="n">
-        <v>18265.36</v>
-      </c>
-      <c r="M92" s="18" t="n">
-        <v>4372.7</v>
-      </c>
-      <c r="N92" s="18" t="n">
-        <v>27.1</v>
-      </c>
-      <c r="O92" s="18" t="n">
-        <v>9844.09</v>
-      </c>
-      <c r="P92" s="37" t="n">
-        <v>32509.25</v>
-      </c>
-      <c r="Q92" s="18" t="n">
-        <v>46702.99</v>
-      </c>
-      <c r="R92" s="18" t="n">
-        <v>-25563.62</v>
-      </c>
-      <c r="S92" s="18" t="n">
-        <v>31405.01</v>
-      </c>
-      <c r="T92" s="18" t="n">
-        <v>-7685.52</v>
-      </c>
-      <c r="U92" s="37" t="n">
-        <v>44858.86</v>
-      </c>
-      <c r="V92" s="18" t="n">
-        <v>43021.8</v>
-      </c>
-      <c r="W92" s="18" t="n">
-        <v>14067.22</v>
-      </c>
-      <c r="X92" s="18" t="n">
-        <v>10591.9</v>
-      </c>
-      <c r="Y92" s="18" t="n">
-        <v>-44205.17</v>
-      </c>
-      <c r="Z92" s="37" t="n">
-        <v>23475.75</v>
-      </c>
-      <c r="AA92" s="18" t="n">
-        <v>39558.69</v>
-      </c>
-      <c r="AB92" s="19" t="n">
-        <v>-23404.38</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="P92" s="9" t="n"/>
+      <c r="U92" s="9" t="n"/>
+      <c r="Z92" s="9" t="n"/>
+      <c r="AB92" s="5" t="n"/>
       <c r="AC92" s="10" t="n"/>
       <c r="AD92" s="10" t="n"/>
       <c r="AE92" s="11" t="n"/>
@@ -29030,18 +29047,51 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>배당금수취(CF)</t>
+          <t>이자수취(CF)</t>
         </is>
       </c>
       <c r="F93" s="9" t="n"/>
       <c r="K93" s="9" t="n"/>
-      <c r="L93" s="18" t="n">
-        <v>0</v>
+      <c r="O93" s="18" t="n">
+        <v>98.20999999999999</v>
       </c>
       <c r="P93" s="9" t="n"/>
-      <c r="U93" s="9" t="n"/>
-      <c r="Z93" s="9" t="n"/>
-      <c r="AB93" s="5" t="n"/>
+      <c r="Q93" s="18" t="n">
+        <v>134.5</v>
+      </c>
+      <c r="R93" s="18" t="n">
+        <v>415.6</v>
+      </c>
+      <c r="S93" s="18" t="n">
+        <v>466.3</v>
+      </c>
+      <c r="T93" s="18" t="n">
+        <v>408.43</v>
+      </c>
+      <c r="U93" s="37" t="n">
+        <v>1424.83</v>
+      </c>
+      <c r="V93" s="18" t="n">
+        <v>237.21</v>
+      </c>
+      <c r="W93" s="18" t="n">
+        <v>223.72</v>
+      </c>
+      <c r="X93" s="18" t="n">
+        <v>188.14</v>
+      </c>
+      <c r="Y93" s="18" t="n">
+        <v>1704.35</v>
+      </c>
+      <c r="Z93" s="37" t="n">
+        <v>2353.42</v>
+      </c>
+      <c r="AA93" s="18" t="n">
+        <v>1303.54</v>
+      </c>
+      <c r="AB93" s="19" t="n">
+        <v>86.56</v>
+      </c>
       <c r="AC93" s="10" t="n"/>
       <c r="AD93" s="10" t="n"/>
       <c r="AE93" s="11" t="n"/>
@@ -29062,51 +29112,21 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>이자수취(CF)</t>
+          <t>장기차입금의감소</t>
         </is>
       </c>
       <c r="F94" s="9" t="n"/>
       <c r="K94" s="9" t="n"/>
       <c r="O94" s="18" t="n">
-        <v>98.20999999999999</v>
+        <v>0</v>
       </c>
       <c r="P94" s="9" t="n"/>
-      <c r="Q94" s="18" t="n">
-        <v>134.5</v>
-      </c>
-      <c r="R94" s="18" t="n">
-        <v>415.6</v>
-      </c>
-      <c r="S94" s="18" t="n">
-        <v>466.3</v>
-      </c>
       <c r="T94" s="18" t="n">
-        <v>408.43</v>
-      </c>
-      <c r="U94" s="37" t="n">
-        <v>1424.83</v>
-      </c>
-      <c r="V94" s="18" t="n">
-        <v>237.21</v>
-      </c>
-      <c r="W94" s="18" t="n">
-        <v>223.72</v>
-      </c>
-      <c r="X94" s="18" t="n">
-        <v>188.14</v>
-      </c>
-      <c r="Y94" s="18" t="n">
-        <v>1704.35</v>
-      </c>
-      <c r="Z94" s="37" t="n">
-        <v>2353.42</v>
-      </c>
-      <c r="AA94" s="18" t="n">
-        <v>1303.54</v>
-      </c>
-      <c r="AB94" s="19" t="n">
-        <v>86.56</v>
-      </c>
+        <v>750</v>
+      </c>
+      <c r="U94" s="9" t="n"/>
+      <c r="Z94" s="9" t="n"/>
+      <c r="AB94" s="5" t="n"/>
       <c r="AC94" s="10" t="n"/>
       <c r="AD94" s="10" t="n"/>
       <c r="AE94" s="11" t="n"/>
@@ -29127,21 +29147,34 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>장기차입금의감소</t>
+          <t>이자지급(CF)</t>
         </is>
       </c>
       <c r="F95" s="9" t="n"/>
       <c r="K95" s="9" t="n"/>
-      <c r="O95" s="18" t="n">
-        <v>0</v>
-      </c>
       <c r="P95" s="9" t="n"/>
-      <c r="T95" s="18" t="n">
-        <v>750</v>
-      </c>
       <c r="U95" s="9" t="n"/>
-      <c r="Z95" s="9" t="n"/>
-      <c r="AB95" s="5" t="n"/>
+      <c r="V95" s="18" t="n">
+        <v>-2479.94</v>
+      </c>
+      <c r="W95" s="18" t="n">
+        <v>-1723.12</v>
+      </c>
+      <c r="X95" s="18" t="n">
+        <v>712.1900000000001</v>
+      </c>
+      <c r="Y95" s="18" t="n">
+        <v>-1811.62</v>
+      </c>
+      <c r="Z95" s="37" t="n">
+        <v>-5302.49</v>
+      </c>
+      <c r="AA95" s="18" t="n">
+        <v>-1547.36</v>
+      </c>
+      <c r="AB95" s="19" t="n">
+        <v>-1549.62</v>
+      </c>
       <c r="AC95" s="10" t="n"/>
       <c r="AD95" s="10" t="n"/>
       <c r="AE95" s="11" t="n"/>
@@ -29155,54 +29188,6 @@
       <c r="AM95" s="10" t="n"/>
       <c r="AN95" s="10" t="n"/>
       <c r="AO95" s="11" t="n"/>
-    </row>
-    <row r="96">
-      <c r="A96" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>이자지급(CF)</t>
-        </is>
-      </c>
-      <c r="F96" s="9" t="n"/>
-      <c r="K96" s="9" t="n"/>
-      <c r="P96" s="9" t="n"/>
-      <c r="U96" s="9" t="n"/>
-      <c r="V96" s="18" t="n">
-        <v>-2479.94</v>
-      </c>
-      <c r="W96" s="18" t="n">
-        <v>-1723.12</v>
-      </c>
-      <c r="X96" s="18" t="n">
-        <v>712.1900000000001</v>
-      </c>
-      <c r="Y96" s="18" t="n">
-        <v>-1811.62</v>
-      </c>
-      <c r="Z96" s="37" t="n">
-        <v>-5302.49</v>
-      </c>
-      <c r="AA96" s="18" t="n">
-        <v>-1547.36</v>
-      </c>
-      <c r="AB96" s="19" t="n">
-        <v>-1549.62</v>
-      </c>
-      <c r="AC96" s="10" t="n"/>
-      <c r="AD96" s="10" t="n"/>
-      <c r="AE96" s="11" t="n"/>
-      <c r="AF96" s="10" t="n"/>
-      <c r="AG96" s="10" t="n"/>
-      <c r="AH96" s="10" t="n"/>
-      <c r="AI96" s="10" t="n"/>
-      <c r="AJ96" s="11" t="n"/>
-      <c r="AK96" s="10" t="n"/>
-      <c r="AL96" s="10" t="n"/>
-      <c r="AM96" s="10" t="n"/>
-      <c r="AN96" s="10" t="n"/>
-      <c r="AO96" s="11" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -4989,7 +4989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-09</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
         </is>
       </c>
     </row>
@@ -5860,35 +5860,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.74</v>
+        <v>1345.14</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.79</v>
+        <v>1457.21</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5979,35 +5979,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1343.46</v>
+        <v>1341.49</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6098,35 +6098,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>851.3099999999999</v>
+        <v>850.79</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.5700000000001</v>
+        <v>919.21</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6217,35 +6217,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.79</v>
+        <v>847.7</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6336,35 +6336,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1510.82</v>
+        <v>1509.74</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1690.9</v>
+        <v>1689.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6455,35 +6455,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1502.8</v>
+        <v>1503.27</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6574,35 +6574,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.73</v>
+        <v>200.69</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.82</v>
+        <v>213.75</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6693,35 +6693,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.45</v>
+        <v>200.46</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -8485,36 +8485,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.004572831</v>
+        <v>-0.004745846</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.00339074</v>
+        <v>0.003166362</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.0008957700000000001</v>
+        <v>0.000747268</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>127.904129595</v>
+        <v>127.913976859</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.002107971</v>
+        <v>0.001884205</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.009509101000000001</v>
+        <v>-0.000694683</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.002175437</v>
+        <v>-0.000389381</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>127.915413511</v>
+        <v>127.915209983</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.006800535</v>
+        <v>0.006599894</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.000733468</v>
+        <v>-0.009077514</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -8613,36 +8613,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.007632917</v>
+        <v>-0.005677755</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.006506994</v>
+        <v>0.009206343000000001</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.002298533</v>
+        <v>-0.000350788</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>127.909113587</v>
+        <v>127.911231508</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.006948149</v>
+        <v>-0.004915576</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.000634592</v>
+        <v>0.012223017</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>0.000175846</v>
+        <v>-0.004382108</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>127.910085166</v>
+        <v>127.912299344</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.003562679</v>
+        <v>0.005749598</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.003875063</v>
+        <v>0.000210204</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -8882,23 +8882,23 @@
         <v>0.003511428</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>-0.111409018</v>
+        <v>-0.111399929</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>-0.171097178</v>
+        <v>-0.171105656</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>-0.149578608</v>
+        <v>-0.149566269</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>-0.005484699</v>
+        <v>-0.00548462</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>-0.189740447</v>
+        <v>-0.189737679</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>-0.317847882</v>
+        <v>-0.317842159</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -9007,26 +9007,26 @@
         <v>0.068886655</v>
       </c>
       <c r="AG33" s="32" t="n">
-        <v>-0.002162126</v>
+        <v>-0.002167756</v>
       </c>
       <c r="AH33" s="32" t="n">
-        <v>0.069163013</v>
+        <v>0.069169046</v>
       </c>
       <c r="AI33" s="32" t="n">
         <v>0.088285588</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="32" t="n">
-        <v>0.058786444</v>
+        <v>0.058781595</v>
       </c>
       <c r="AL33" s="32" t="n">
-        <v>0.001731356</v>
+        <v>0.001731364</v>
       </c>
       <c r="AM33" s="32" t="n">
-        <v>0.059463933</v>
+        <v>0.059464205</v>
       </c>
       <c r="AN33" s="32" t="n">
-        <v>0.076181762</v>
+        <v>0.07618209099999999</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9988,33 +9988,33 @@
         <v>-0.010274649</v>
       </c>
       <c r="AD41" s="32" t="n">
-        <v>0.246403958</v>
+        <v>0.246368616</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="32" t="n">
-        <v>0.163893589</v>
+        <v>0.163846588</v>
       </c>
       <c r="AG41" s="32" t="n">
-        <v>-0.007422281</v>
+        <v>-0.007493994</v>
       </c>
       <c r="AH41" s="32" t="n">
-        <v>0.179437013</v>
+        <v>0.179357157</v>
       </c>
       <c r="AI41" s="32" t="n">
-        <v>0.165934159</v>
+        <v>0.165825441</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="32" t="n">
-        <v>0.190041594</v>
+        <v>0.1899685</v>
       </c>
       <c r="AL41" s="32" t="n">
-        <v>0.221479662</v>
+        <v>0.221459538</v>
       </c>
       <c r="AM41" s="32" t="n">
-        <v>0.245742916</v>
+        <v>0.245691844</v>
       </c>
       <c r="AN41" s="32" t="n">
-        <v>0.245433984</v>
+        <v>0.245463832</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -10134,39 +10134,39 @@
         <v>0.188141346</v>
       </c>
       <c r="AD42" s="32" t="n">
-        <v>0.188221283</v>
+        <v>0.188226621</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="32" t="n">
-        <v>0.188708961</v>
+        <v>0.188716582</v>
       </c>
       <c r="AG42" s="32" t="n">
-        <v>0.18857019</v>
+        <v>0.188583815</v>
       </c>
       <c r="AH42" s="32" t="n">
-        <v>0.188158028</v>
+        <v>0.188170769</v>
       </c>
       <c r="AI42" s="32" t="n">
-        <v>0.18820983</v>
+        <v>0.188208396</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="32" t="n">
-        <v>0.188706777</v>
+        <v>0.188725989</v>
       </c>
       <c r="AL42" s="32" t="n">
-        <v>0.188566528</v>
+        <v>0.188583259</v>
       </c>
       <c r="AM42" s="32" t="n">
-        <v>0.188135225</v>
+        <v>0.188155678</v>
       </c>
       <c r="AN42" s="32" t="n">
-        <v>0.188201754</v>
+        <v>0.18822013</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO39,"")</f>
@@ -10289,39 +10289,39 @@
         <v>-0.625154722</v>
       </c>
       <c r="AD43" s="32" t="n">
-        <v>-0.62514532</v>
+        <v>-0.625163047</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF43" s="32" t="n">
-        <v>-0.6251665789999999</v>
+        <v>-0.6251514419999999</v>
       </c>
       <c r="AG43" s="32" t="n">
-        <v>-0.6251715920000001</v>
+        <v>-0.625144509</v>
       </c>
       <c r="AH43" s="32" t="n">
-        <v>-0.625139646</v>
+        <v>-0.625148119</v>
       </c>
       <c r="AI43" s="32" t="n">
-        <v>-0.625161118</v>
+        <v>-0.625164178</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK43" s="32" t="n">
-        <v>-0.625165428</v>
+        <v>-0.625161203</v>
       </c>
       <c r="AL43" s="32" t="n">
-        <v>-0.625144175</v>
+        <v>-0.625170068</v>
       </c>
       <c r="AM43" s="32" t="n">
-        <v>-0.625142671</v>
+        <v>-0.625156275</v>
       </c>
       <c r="AN43" s="32" t="n">
-        <v>-0.625158657</v>
+        <v>-0.625161114</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -10451,32 +10451,32 @@
         <v/>
       </c>
       <c r="AF44" s="32" t="n">
-        <v>0.142497255</v>
+        <v>0.14250646</v>
       </c>
       <c r="AG44" s="32" t="n">
-        <v>0.144920837</v>
+        <v>0.144937587</v>
       </c>
       <c r="AH44" s="32" t="n">
-        <v>0.14886819</v>
+        <v>0.148876252</v>
       </c>
       <c r="AI44" s="32" t="n">
-        <v>0.151132031</v>
+        <v>0.151110765</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ42/subQ!AJ41,"")</f>
         <v/>
       </c>
       <c r="AK44" s="32" t="n">
-        <v>0.151115454</v>
+        <v>0.151186146</v>
       </c>
       <c r="AL44" s="32" t="n">
-        <v>0.154413852</v>
+        <v>0.154421157</v>
       </c>
       <c r="AM44" s="32" t="n">
-        <v>0.158624587</v>
+        <v>0.158638379</v>
       </c>
       <c r="AN44" s="32" t="n">
-        <v>0.160487272</v>
+        <v>0.16053355</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO42/subQ!AO41,"")</f>
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.1911635578337843</v>
+        <v>0.1911646919923347</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.06131744718026529</v>
+        <v>0.06131815203522122</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.8217452854407958</v>
+        <v>0.8217633682975135</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.03609646464754426</v>
+        <v>0.03609686562459834</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03869698415983145</v>
+        <v>0.03869722625608072</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-09</t>
+          <t>UPDATE: 26-10-10</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -4989,7 +4989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-10</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
         </is>
       </c>
     </row>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-10</t>
+          <t>UPDATE: 26-10-11</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -4989,7 +4989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-11</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
         <v>9770</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>9310</v>
+        <v>8750</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -7010,7 +7010,7 @@
         <v>8500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>9290</v>
+        <v>8600</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -7101,7 +7101,7 @@
         <v>10929</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>9826</v>
+        <v>9646.700000000001</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -10547,7 +10547,7 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>9310</v>
+        <v>8750</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-11</t>
+          <t>UPDATE: 26-10-12</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36454,7 +36454,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42099,7 +42099,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261008</t>
+          <t>20261012</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -44415,7 +44415,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>12.53</v>
+        <v>11.78</v>
       </c>
     </row>
     <row r="32">
@@ -44425,7 +44425,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.15</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -1791,7 +1791,7 @@
     <comment ref="AK43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 295억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 294억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AL43" authorId="0" shapeId="0">
@@ -1920,7 +1920,7 @@
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 813 + 종속사 295 + 연결조정 -184
+        <t>추정: 별도(조선기자재) 813 + 종속사 294 + 연결조정 -184
 [identity]</t>
       </text>
     </comment>
@@ -4503,7 +4503,7 @@
     </comment>
     <comment ref="AK41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 295억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 294억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
@@ -4989,7 +4989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-12</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
         </is>
       </c>
     </row>
@@ -5860,35 +5860,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1345.14</v>
+        <v>1343.63</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1457.21</v>
+        <v>1456.58</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5979,35 +5979,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.49</v>
+        <v>1333.09</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6098,35 +6098,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>850.79</v>
+        <v>849.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>919.21</v>
+        <v>918.8099999999999</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6217,35 +6217,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>847.7</v>
+        <v>840.54</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6336,35 +6336,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1509.74</v>
+        <v>1507.34</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1689.95</v>
+        <v>1688.95</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6455,35 +6455,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1503.27</v>
+        <v>1490.54</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6574,35 +6574,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.69</v>
+        <v>200.5</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.75</v>
+        <v>213.68</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6693,35 +6693,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.46</v>
+        <v>199.18</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6828,7 +6828,7 @@
         <v>9770</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8750</v>
+        <v>8520</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -7010,7 +7010,7 @@
         <v>8500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>8600</v>
+        <v>8120</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -7101,7 +7101,7 @@
         <v>10929</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>9646.700000000001</v>
+        <v>9475.700000000001</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8485,36 +8485,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.004745846</v>
+        <v>-0.003575811</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.003166362</v>
+        <v>0.004854239</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.000747268</v>
+        <v>0.002016771</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>127.913976859</v>
+        <v>127.907309787</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.001884205</v>
+        <v>0.005199222</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>-0.000694683</v>
+        <v>0.004920042</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.000389381</v>
+        <v>-0.007186162</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>127.915209983</v>
+        <v>127.918577479</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.006599894</v>
+        <v>0.009878022</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.009077514</v>
+        <v>-0.005316086</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -8613,36 +8613,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.005677755</v>
+        <v>-0.004775327</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.009206343000000001</v>
+        <v>0.01051217</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.000350788</v>
+        <v>0.000634156</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>127.911231508</v>
+        <v>127.90568958</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.004915576</v>
+        <v>0.009528534999999999</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.012223017</v>
+        <v>0.000316545</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.004382108</v>
+        <v>-2.9173e-05</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>127.912299344</v>
+        <v>127.916781936</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.005749598</v>
+        <v>0.000159585</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.000210204</v>
+        <v>0.004993693</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -8882,23 +8882,23 @@
         <v>0.003511428</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>-0.111399929</v>
+        <v>-0.11139084</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>-0.171105656</v>
+        <v>-0.17108345</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>-0.149566269</v>
+        <v>-0.149560732</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>-0.00548462</v>
+        <v>-0.005469872</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>-0.189737679</v>
+        <v>-0.189712018</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>-0.317842159</v>
+        <v>-0.317777538</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -9010,23 +9010,23 @@
         <v>-0.002167756</v>
       </c>
       <c r="AH33" s="32" t="n">
-        <v>0.069169046</v>
+        <v>0.06915776</v>
       </c>
       <c r="AI33" s="32" t="n">
-        <v>0.088285588</v>
+        <v>0.088281242</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="32" t="n">
-        <v>0.058781595</v>
+        <v>0.05878245</v>
       </c>
       <c r="AL33" s="32" t="n">
-        <v>0.001731364</v>
+        <v>0.001726807</v>
       </c>
       <c r="AM33" s="32" t="n">
-        <v>0.059464205</v>
+        <v>0.05946072</v>
       </c>
       <c r="AN33" s="32" t="n">
-        <v>0.07618209099999999</v>
+        <v>0.076179419</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9988,33 +9988,33 @@
         <v>-0.010274649</v>
       </c>
       <c r="AD41" s="32" t="n">
-        <v>0.246368616</v>
+        <v>0.246333274</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="32" t="n">
-        <v>0.163846588</v>
+        <v>0.163658582</v>
       </c>
       <c r="AG41" s="32" t="n">
-        <v>-0.007493994</v>
+        <v>-0.007780845</v>
       </c>
       <c r="AH41" s="32" t="n">
-        <v>0.179357157</v>
+        <v>0.178798163</v>
       </c>
       <c r="AI41" s="32" t="n">
-        <v>0.165825441</v>
+        <v>0.165206295</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="32" t="n">
-        <v>0.1899685</v>
+        <v>0.1895145</v>
       </c>
       <c r="AL41" s="32" t="n">
-        <v>0.221459538</v>
+        <v>0.221198323</v>
       </c>
       <c r="AM41" s="32" t="n">
-        <v>0.245691844</v>
+        <v>0.245740609</v>
       </c>
       <c r="AN41" s="32" t="n">
-        <v>0.245463832</v>
+        <v>0.245674235</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -10134,39 +10134,39 @@
         <v>0.188141346</v>
       </c>
       <c r="AD42" s="32" t="n">
-        <v>0.188226621</v>
+        <v>0.188231958</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="32" t="n">
-        <v>0.188716582</v>
+        <v>0.188747072</v>
       </c>
       <c r="AG42" s="32" t="n">
-        <v>0.188583815</v>
+        <v>0.18856606</v>
       </c>
       <c r="AH42" s="32" t="n">
-        <v>0.188170769</v>
+        <v>0.188158385</v>
       </c>
       <c r="AI42" s="32" t="n">
-        <v>0.188208396</v>
+        <v>0.188216398</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="32" t="n">
-        <v>0.188725989</v>
+        <v>0.188726655</v>
       </c>
       <c r="AL42" s="32" t="n">
-        <v>0.188583259</v>
+        <v>0.188589353</v>
       </c>
       <c r="AM42" s="32" t="n">
-        <v>0.188155678</v>
+        <v>0.188155963</v>
       </c>
       <c r="AN42" s="32" t="n">
-        <v>0.18822013</v>
+        <v>0.188215528</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO39,"")</f>
@@ -10289,39 +10289,39 @@
         <v>-0.625154722</v>
       </c>
       <c r="AD43" s="32" t="n">
-        <v>-0.625163047</v>
+        <v>-0.625152417</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF43" s="32" t="n">
-        <v>-0.6251514419999999</v>
+        <v>-0.625171662</v>
       </c>
       <c r="AG43" s="32" t="n">
-        <v>-0.625144509</v>
+        <v>-0.62514455</v>
       </c>
       <c r="AH43" s="32" t="n">
-        <v>-0.625148119</v>
+        <v>-0.625139722</v>
       </c>
       <c r="AI43" s="32" t="n">
-        <v>-0.625164178</v>
+        <v>-0.625149059</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK43" s="32" t="n">
-        <v>-0.625161203</v>
+        <v>-0.62516129</v>
       </c>
       <c r="AL43" s="32" t="n">
-        <v>-0.625170068</v>
+        <v>-0.625159057</v>
       </c>
       <c r="AM43" s="32" t="n">
-        <v>-0.625156275</v>
+        <v>-0.625156343</v>
       </c>
       <c r="AN43" s="32" t="n">
-        <v>-0.625161114</v>
+        <v>-0.625151409</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -10444,39 +10444,39 @@
         <v>0.140448362</v>
       </c>
       <c r="AD44" s="32" t="n">
-        <v>0.143783735</v>
+        <v>0.143790257</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE42/subQ!AE41,"")</f>
         <v/>
       </c>
       <c r="AF44" s="32" t="n">
-        <v>0.14250646</v>
+        <v>0.142524874</v>
       </c>
       <c r="AG44" s="32" t="n">
-        <v>0.144937587</v>
+        <v>0.144921672</v>
       </c>
       <c r="AH44" s="32" t="n">
-        <v>0.148876252</v>
+        <v>0.148840485</v>
       </c>
       <c r="AI44" s="32" t="n">
-        <v>0.151110765</v>
+        <v>0.151121146</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ42/subQ!AJ41,"")</f>
         <v/>
       </c>
       <c r="AK44" s="32" t="n">
-        <v>0.151186146</v>
+        <v>0.151159633</v>
       </c>
       <c r="AL44" s="32" t="n">
-        <v>0.154421157</v>
+        <v>0.154406892</v>
       </c>
       <c r="AM44" s="32" t="n">
-        <v>0.158638379</v>
+        <v>0.15862039</v>
       </c>
       <c r="AN44" s="32" t="n">
-        <v>0.16053355</v>
+        <v>0.160505016</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO42/subQ!AO41,"")</f>
@@ -10547,11 +10547,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>8750</v>
+        <v>8520</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 9,810원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 9,300원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.1911646919923347</v>
+        <v>0.1911559661332717</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.06131815203522122</v>
+        <v>0.06131684601479298</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.8217633682975135</v>
+        <v>0.8217628590710369</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.03609686562459834</v>
+        <v>0.03609894589546821</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03869722625608072</v>
+        <v>0.03869853624089498</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-12</t>
+          <t>UPDATE: 26-10-13</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36454,7 +36454,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42099,7 +42099,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261012</t>
+          <t>20261013</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -44415,7 +44415,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.78</v>
+        <v>11.47</v>
       </c>
     </row>
     <row r="32">
@@ -44425,7 +44425,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -1791,7 +1791,7 @@
     <comment ref="AK43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 294억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 295억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AL43" authorId="0" shapeId="0">
@@ -1920,7 +1920,7 @@
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 813 + 종속사 294 + 연결조정 -184
+        <t>추정: 별도(조선기자재) 813 + 종속사 295 + 연결조정 -184
 [identity]</t>
       </text>
     </comment>
@@ -4503,7 +4503,7 @@
     </comment>
     <comment ref="AK41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 294억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 295억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
@@ -4989,7 +4989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-13</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
         </is>
       </c>
     </row>
@@ -5860,35 +5860,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.63</v>
+        <v>1343.39</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.58</v>
+        <v>1456.01</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5979,35 +5979,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1333.09</v>
+        <v>1341.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6098,35 +6098,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.51</v>
+        <v>849.39</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.8099999999999</v>
+        <v>918.46</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6217,35 +6217,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>840.54</v>
+        <v>848.37</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6336,35 +6336,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1507.34</v>
+        <v>1506.62</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.95</v>
+        <v>1688.01</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6455,35 +6455,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1490.54</v>
+        <v>1500.82</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6574,35 +6574,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.5</v>
+        <v>200.49</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.68</v>
+        <v>213.61</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6693,35 +6693,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.18</v>
+        <v>200.4</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6828,7 +6828,7 @@
         <v>9770</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8520</v>
+        <v>8710</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -7101,7 +7101,7 @@
         <v>10929</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>9475.700000000001</v>
+        <v>9386.200000000001</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8485,36 +8485,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.003575811</v>
+        <v>-0.004051246</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.004854239</v>
+        <v>0.004119066</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.002016771</v>
+        <v>0.001433243</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>127.907309787</v>
+        <v>127.914720028</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.005199222</v>
+        <v>0.002618455</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.004920042</v>
+        <v>0.002143904</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.007186162</v>
+        <v>-0.009662611</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>127.918577479</v>
+        <v>127.917910697</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.009878022</v>
+        <v>0.007379189</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.005316086</v>
+        <v>-0.008022117</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -8613,36 +8613,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.004775327</v>
+        <v>-0.004407822</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.01051217</v>
+        <v>0.010950517</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.000634156</v>
+        <v>0.000902872</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>127.90568958</v>
+        <v>127.912590054</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.009528534999999999</v>
+        <v>0.006426646</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.000316545</v>
+        <v>-0.002653627</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-2.9173e-05</v>
+        <v>-0.003054244</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>127.916781936</v>
+        <v>127.917094847</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.000159585</v>
+        <v>0.007173953</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.004993693</v>
+        <v>0.002141468</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -8882,23 +8882,23 @@
         <v>0.003511428</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>-0.11139084</v>
+        <v>-0.111399929</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>-0.17108345</v>
+        <v>-0.171095428</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>-0.149560732</v>
+        <v>-0.149576763</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>-0.005469872</v>
+        <v>-0.00547011</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>-0.189712018</v>
+        <v>-0.189734911</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>-0.317777538</v>
+        <v>-0.317836436</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -9010,23 +9010,23 @@
         <v>-0.002167756</v>
       </c>
       <c r="AH33" s="32" t="n">
-        <v>0.06915776</v>
+        <v>0.069163403</v>
       </c>
       <c r="AI33" s="32" t="n">
-        <v>0.088281242</v>
+        <v>0.088291331</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="32" t="n">
-        <v>0.05878245</v>
+        <v>0.058781595</v>
       </c>
       <c r="AL33" s="32" t="n">
-        <v>0.001726807</v>
+        <v>0.001731364</v>
       </c>
       <c r="AM33" s="32" t="n">
-        <v>0.05946072</v>
+        <v>0.059464205</v>
       </c>
       <c r="AN33" s="32" t="n">
-        <v>0.076179419</v>
+        <v>0.076177775</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9992,29 +9992,29 @@
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="32" t="n">
-        <v>0.163658582</v>
+        <v>0.163799586</v>
       </c>
       <c r="AG41" s="32" t="n">
-        <v>-0.007780845</v>
+        <v>-0.00752985</v>
       </c>
       <c r="AH41" s="32" t="n">
-        <v>0.178798163</v>
+        <v>0.179277301</v>
       </c>
       <c r="AI41" s="32" t="n">
-        <v>0.165206295</v>
+        <v>0.16577343</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="32" t="n">
-        <v>0.1895145</v>
+        <v>0.189935786</v>
       </c>
       <c r="AL41" s="32" t="n">
-        <v>0.221198323</v>
+        <v>0.221395282</v>
       </c>
       <c r="AM41" s="32" t="n">
-        <v>0.245740609</v>
+        <v>0.245674623</v>
       </c>
       <c r="AN41" s="32" t="n">
-        <v>0.245674235</v>
+        <v>0.245481745</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -10141,32 +10141,32 @@
         <v/>
       </c>
       <c r="AF42" s="32" t="n">
-        <v>0.188747072</v>
+        <v>0.188724203</v>
       </c>
       <c r="AG42" s="32" t="n">
-        <v>0.18856606</v>
+        <v>0.188590628</v>
       </c>
       <c r="AH42" s="32" t="n">
-        <v>0.188158385</v>
+        <v>0.188149653</v>
       </c>
       <c r="AI42" s="32" t="n">
-        <v>0.188216398</v>
+        <v>0.188197806</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="32" t="n">
-        <v>0.188726655</v>
+        <v>0.1887388</v>
       </c>
       <c r="AL42" s="32" t="n">
-        <v>0.188589353</v>
+        <v>0.188570414</v>
       </c>
       <c r="AM42" s="32" t="n">
-        <v>0.188155963</v>
+        <v>0.18814384</v>
       </c>
       <c r="AN42" s="32" t="n">
-        <v>0.188215528</v>
+        <v>0.188211628</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO39,"")</f>
@@ -10296,32 +10296,32 @@
         <v/>
       </c>
       <c r="AF43" s="32" t="n">
-        <v>-0.625171662</v>
+        <v>-0.625136303</v>
       </c>
       <c r="AG43" s="32" t="n">
-        <v>-0.62514455</v>
+        <v>-0.625167094</v>
       </c>
       <c r="AH43" s="32" t="n">
-        <v>-0.625139722</v>
+        <v>-0.625156594</v>
       </c>
       <c r="AI43" s="32" t="n">
-        <v>-0.625149059</v>
+        <v>-0.625161149</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK43" s="32" t="n">
-        <v>-0.62516129</v>
+        <v>-0.625169699</v>
       </c>
       <c r="AL43" s="32" t="n">
-        <v>-0.625159057</v>
+        <v>-0.625166386</v>
       </c>
       <c r="AM43" s="32" t="n">
-        <v>-0.625156343</v>
+        <v>-0.625152891</v>
       </c>
       <c r="AN43" s="32" t="n">
-        <v>-0.625151409</v>
+        <v>-0.625158682</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -10451,32 +10451,32 @@
         <v/>
       </c>
       <c r="AF44" s="32" t="n">
-        <v>0.142524874</v>
+        <v>0.142515666</v>
       </c>
       <c r="AG44" s="32" t="n">
-        <v>0.144921672</v>
+        <v>0.144937587</v>
       </c>
       <c r="AH44" s="32" t="n">
-        <v>0.148840485</v>
+        <v>0.148830156</v>
       </c>
       <c r="AI44" s="32" t="n">
-        <v>0.151121146</v>
+        <v>0.151122524</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ42/subQ!AJ41,"")</f>
         <v/>
       </c>
       <c r="AK44" s="32" t="n">
-        <v>0.151159633</v>
+        <v>0.151194354</v>
       </c>
       <c r="AL44" s="32" t="n">
-        <v>0.154406892</v>
+        <v>0.15443577</v>
       </c>
       <c r="AM44" s="32" t="n">
-        <v>0.15862039</v>
+        <v>0.158608696</v>
       </c>
       <c r="AN44" s="32" t="n">
-        <v>0.160505016</v>
+        <v>0.16051234</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO42/subQ!AO41,"")</f>
@@ -10547,11 +10547,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>8520</v>
+        <v>8710</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 9,300원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,640원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.1911559661332717</v>
+        <v>0.1911598932067636</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.06131684601479298</v>
+        <v>0.06131748779349964</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.8217628590710369</v>
+        <v>0.8217693960932745</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.03609894589546821</v>
+        <v>0.0360968740530241</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03869853624089498</v>
+        <v>0.0386972181612924</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-13</t>
+          <t>UPDATE: 26-10-14</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36454,7 +36454,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42099,7 +42099,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261013</t>
+          <t>20261014</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -44415,7 +44415,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.47</v>
+        <v>11.72</v>
       </c>
     </row>
     <row r="32">
@@ -44425,7 +44425,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.97</v>
+        <v>2.02</v>
       </c>
     </row>
     <row r="33">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -1779,7 +1779,7 @@
     <comment ref="AH43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 295억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 296억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AI43" authorId="0" shapeId="0">
@@ -1791,25 +1791,25 @@
     <comment ref="AK43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 295억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 294억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AL43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 338억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 337억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AM43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 368억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 366억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AN43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 512억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 510억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AC44" authorId="0" shapeId="0">
@@ -1890,7 +1890,7 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1101 + 종속사 353 + 연결조정 -220
+        <t>추정: 별도(조선기자재) 1101 + 종속사 353 + 연결조정 -221
 [identity]</t>
       </text>
     </comment>
@@ -1908,7 +1908,7 @@
     </comment>
     <comment ref="AH5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 838 + 종속사 295 + 연결조정 -185
+        <t>추정: 별도(조선기자재) 838 + 종속사 296 + 연결조정 -185
 [identity]</t>
       </text>
     </comment>
@@ -1920,25 +1920,25 @@
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 813 + 종속사 295 + 연결조정 -184
+        <t>추정: 별도(조선기자재) 813 + 종속사 294 + 연결조정 -184
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 867 + 종속사 338 + 연결조정 -211
+        <t>추정: 별도(조선기자재) 867 + 종속사 337 + 연결조정 -211
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 843 + 종속사 368 + 연결조정 -230
+        <t>추정: 별도(조선기자재) 843 + 종속사 366 + 연결조정 -229
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1123 + 종속사 512 + 연결조정 -320
+        <t>추정: 별도(조선기자재) 1123 + 종속사 510 + 연결조정 -319
 [identity]</t>
       </text>
     </comment>
@@ -4491,7 +4491,7 @@
     </comment>
     <comment ref="AH41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 295억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 296억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
@@ -4503,25 +4503,25 @@
     </comment>
     <comment ref="AK41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 295억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 294억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AL41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 338억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 337억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 368억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 366억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 512억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 510억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
@@ -4989,7 +4989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-14</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
         </is>
       </c>
     </row>
@@ -5860,35 +5860,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1343.39</v>
+        <v>1342.11</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1456.01</v>
+        <v>1454.27</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5979,35 +5979,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1341.45</v>
+        <v>1332.1</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6098,35 +6098,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>849.39</v>
+        <v>848.59</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>918.46</v>
+        <v>917.39</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6217,35 +6217,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>848.37</v>
+        <v>842.99</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6336,35 +6336,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1506.62</v>
+        <v>1505.3</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1688.01</v>
+        <v>1685.25</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6455,35 +6455,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1500.82</v>
+        <v>1499.02</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6574,35 +6574,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.49</v>
+        <v>200.38</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.61</v>
+        <v>213.41</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6693,35 +6693,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>200.4</v>
+        <v>199.23</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6828,7 +6828,7 @@
         <v>9770</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8710</v>
+        <v>8410</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -7010,7 +7010,7 @@
         <v>8500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>8120</v>
+        <v>7830</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -7101,7 +7101,7 @@
         <v>10929</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>9386.200000000001</v>
+        <v>9064.5</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8485,36 +8485,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.004051246</v>
+        <v>-0.00385175</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.004119066</v>
+        <v>0.008790164</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.001433243</v>
+        <v>0.004158579</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>127.914720028</v>
+        <v>127.907720771</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.002618455</v>
+        <v>0.007815545</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.002143904</v>
+        <v>0.005345672</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.009662611</v>
+        <v>-0.009071355</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>127.917910697</v>
+        <v>127.922093923</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>0.007379189</v>
+        <v>-0.003147549</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.008022117</v>
+        <v>-0.003176859</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -8613,36 +8613,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.004407822</v>
+        <v>-0.005819443</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.010950517</v>
+        <v>0.009057823</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>0.000902872</v>
+        <v>-0.003759749</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>127.912590054</v>
+        <v>127.918023299</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>0.006426646</v>
+        <v>-0.004532538</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>-0.002653627</v>
+        <v>0.009487508</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.003054244</v>
+        <v>-0.007085141</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>127.917094847</v>
+        <v>127.919438226</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>0.007173953</v>
+        <v>-0.000766075</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.002141468</v>
+        <v>0.003332192</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -8872,33 +8872,33 @@
         <v>-0.078038257</v>
       </c>
       <c r="AD32" s="32" t="n">
-        <v>-0.11637173</v>
+        <v>-0.116386325</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="32" t="n">
-        <v>-0.094526295</v>
+        <v>-0.094552632</v>
       </c>
       <c r="AG32" s="32" t="n">
-        <v>0.003511428</v>
+        <v>0.003475104</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>-0.111399929</v>
+        <v>-0.111427221</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>-0.171095428</v>
+        <v>-0.171104451</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>-0.149576763</v>
+        <v>-0.149545858</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>-0.00547011</v>
+        <v>-0.005383521</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>-0.189734911</v>
+        <v>-0.189632785</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>-0.317836436</v>
+        <v>-0.31758034</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -9000,33 +9000,33 @@
         <v>0.083679367</v>
       </c>
       <c r="AD33" s="32" t="n">
-        <v>0.106164703</v>
+        <v>0.106178017</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="32" t="n">
-        <v>0.068886655</v>
+        <v>0.068903881</v>
       </c>
       <c r="AG33" s="32" t="n">
-        <v>-0.002167756</v>
+        <v>-0.002145174</v>
       </c>
       <c r="AH33" s="32" t="n">
-        <v>0.069163403</v>
+        <v>0.069171176</v>
       </c>
       <c r="AI33" s="32" t="n">
-        <v>0.088291331</v>
+        <v>0.08828092799999999</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="32" t="n">
-        <v>0.058781595</v>
+        <v>0.058759347</v>
       </c>
       <c r="AL33" s="32" t="n">
-        <v>0.001731364</v>
+        <v>0.001703835</v>
       </c>
       <c r="AM33" s="32" t="n">
-        <v>0.059464205</v>
+        <v>0.059427626</v>
       </c>
       <c r="AN33" s="32" t="n">
-        <v>0.076177775</v>
+        <v>0.07613724600000001</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9988,33 +9988,33 @@
         <v>-0.010274649</v>
       </c>
       <c r="AD41" s="32" t="n">
-        <v>0.246333274</v>
+        <v>0.248100371</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="32" t="n">
-        <v>0.163799586</v>
+        <v>0.16643166</v>
       </c>
       <c r="AG41" s="32" t="n">
-        <v>-0.00752985</v>
+        <v>-0.005270895</v>
       </c>
       <c r="AH41" s="32" t="n">
-        <v>0.179277301</v>
+        <v>0.181193851</v>
       </c>
       <c r="AI41" s="32" t="n">
-        <v>0.16577343</v>
+        <v>0.163414979</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="32" t="n">
-        <v>0.189935786</v>
+        <v>0.184228553</v>
       </c>
       <c r="AL41" s="32" t="n">
-        <v>0.221395282</v>
+        <v>0.214151828</v>
       </c>
       <c r="AM41" s="32" t="n">
-        <v>0.245674623</v>
+        <v>0.23858297</v>
       </c>
       <c r="AN41" s="32" t="n">
-        <v>0.245481745</v>
+        <v>0.2412744</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -10134,39 +10134,39 @@
         <v>0.188141346</v>
       </c>
       <c r="AD42" s="32" t="n">
-        <v>0.188231958</v>
+        <v>0.188191986</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="32" t="n">
-        <v>0.188724203</v>
+        <v>0.188741588</v>
       </c>
       <c r="AG42" s="32" t="n">
-        <v>0.188590628</v>
+        <v>0.188558864</v>
       </c>
       <c r="AH42" s="32" t="n">
-        <v>0.188149653</v>
+        <v>0.188148599</v>
       </c>
       <c r="AI42" s="32" t="n">
-        <v>0.188197806</v>
+        <v>0.188214964</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="32" t="n">
-        <v>0.1887388</v>
+        <v>0.188710062</v>
       </c>
       <c r="AL42" s="32" t="n">
-        <v>0.188570414</v>
+        <v>0.188581777</v>
       </c>
       <c r="AM42" s="32" t="n">
-        <v>0.18814384</v>
+        <v>0.188149887</v>
       </c>
       <c r="AN42" s="32" t="n">
-        <v>0.188211628</v>
+        <v>0.188219377</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO39,"")</f>
@@ -10289,39 +10289,39 @@
         <v>-0.625154722</v>
       </c>
       <c r="AD43" s="32" t="n">
-        <v>-0.625152417</v>
+        <v>-0.6251451220000001</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF43" s="32" t="n">
-        <v>-0.625136303</v>
+        <v>-0.6251359950000001</v>
       </c>
       <c r="AG43" s="32" t="n">
-        <v>-0.625167094</v>
+        <v>-0.625153197</v>
       </c>
       <c r="AH43" s="32" t="n">
-        <v>-0.625156594</v>
+        <v>-0.62515634</v>
       </c>
       <c r="AI43" s="32" t="n">
-        <v>-0.625161149</v>
+        <v>-0.62515212</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK43" s="32" t="n">
-        <v>-0.625169699</v>
+        <v>-0.625165878</v>
       </c>
       <c r="AL43" s="32" t="n">
-        <v>-0.625166386</v>
+        <v>-0.625152154</v>
       </c>
       <c r="AM43" s="32" t="n">
-        <v>-0.625152891</v>
+        <v>-0.625146694</v>
       </c>
       <c r="AN43" s="32" t="n">
-        <v>-0.625158682</v>
+        <v>-0.625149513</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -10444,39 +10444,39 @@
         <v>0.140448362</v>
       </c>
       <c r="AD44" s="32" t="n">
-        <v>0.143790257</v>
+        <v>0.14381483</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE42/subQ!AE41,"")</f>
         <v/>
       </c>
       <c r="AF44" s="32" t="n">
-        <v>0.142515666</v>
+        <v>0.142645353</v>
       </c>
       <c r="AG44" s="32" t="n">
-        <v>0.144937587</v>
+        <v>0.14501528</v>
       </c>
       <c r="AH44" s="32" t="n">
-        <v>0.148830156</v>
+        <v>0.148913161</v>
       </c>
       <c r="AI44" s="32" t="n">
-        <v>0.151122524</v>
+        <v>0.151099864</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ42/subQ!AJ41,"")</f>
         <v/>
       </c>
       <c r="AK44" s="32" t="n">
-        <v>0.151194354</v>
+        <v>0.151036848</v>
       </c>
       <c r="AL44" s="32" t="n">
-        <v>0.15443577</v>
+        <v>0.154247994</v>
       </c>
       <c r="AM44" s="32" t="n">
-        <v>0.158608696</v>
+        <v>0.158473762</v>
       </c>
       <c r="AN44" s="32" t="n">
-        <v>0.16051234</v>
+        <v>0.160372624</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO42/subQ!AO41,"")</f>
@@ -10547,11 +10547,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>8710</v>
+        <v>8410</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 8,640원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,960원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.1911598932067636</v>
+        <v>0.1911563132317077</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.06131748779349964</v>
+        <v>0.06131769525482933</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.8217693960932745</v>
+        <v>0.8217558119915195</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.0360968740530241</v>
+        <v>0.03609746561647491</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.0386972181612924</v>
+        <v>0.03869816405745791</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-14</t>
+          <t>UPDATE: 26-10-19</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36454,7 +36454,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42099,7 +42099,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261014</t>
+          <t>20261019</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -44395,7 +44395,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>743</v>
+        <v>743.2</v>
       </c>
     </row>
     <row r="30">
@@ -44415,7 +44415,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.72</v>
+        <v>11.32</v>
       </c>
     </row>
     <row r="32">
@@ -44425,7 +44425,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
     </row>
     <row r="33">
@@ -44435,7 +44435,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>0.1719</v>
+        <v>0.172</v>
       </c>
     </row>
     <row r="34">

--- a/argus/kship/models/075580_model.xlsx
+++ b/argus/kship/models/075580_model.xlsx
@@ -1761,19 +1761,19 @@
     <comment ref="AD43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 353억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 354억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AF43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 248억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 249억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AG43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 277억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 278억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AH43" authorId="0" shapeId="0">
@@ -1797,19 +1797,19 @@
     <comment ref="AL43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 337억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 336억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AM43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 366억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 365억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AN43" authorId="0" shapeId="0">
       <text>
         <t>모델값 역산(implied): v / 매출종속사
-종속사 매출 510억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
+종속사 매출 509억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)</t>
       </text>
     </comment>
     <comment ref="AC44" authorId="0" shapeId="0">
@@ -1890,19 +1890,19 @@
     </comment>
     <comment ref="AD5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1101 + 종속사 353 + 연결조정 -221
+        <t>추정: 별도(조선기자재) 1101 + 종속사 354 + 연결조정 -221
 [identity]</t>
       </text>
     </comment>
     <comment ref="AF5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 802 + 종속사 248 + 연결조정 -155
+        <t>추정: 별도(조선기자재) 802 + 종속사 249 + 연결조정 -155
 [identity]</t>
       </text>
     </comment>
     <comment ref="AG5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 855 + 종속사 277 + 연결조정 -173
+        <t>추정: 별도(조선기자재) 855 + 종속사 278 + 연결조정 -174
 [identity]</t>
       </text>
     </comment>
@@ -1920,25 +1920,25 @@
     </comment>
     <comment ref="AK5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 813 + 종속사 294 + 연결조정 -184
+        <t>추정: 별도(조선기자재) 813 + 종속사 294 + 연결조정 -183
 [identity]</t>
       </text>
     </comment>
     <comment ref="AL5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 867 + 종속사 337 + 연결조정 -211
+        <t>추정: 별도(조선기자재) 867 + 종속사 336 + 연결조정 -210
 [identity]</t>
       </text>
     </comment>
     <comment ref="AM5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 843 + 종속사 366 + 연결조정 -229
+        <t>추정: 별도(조선기자재) 843 + 종속사 365 + 연결조정 -228
 [identity]</t>
       </text>
     </comment>
     <comment ref="AN5" authorId="0" shapeId="0">
       <text>
-        <t>추정: 별도(조선기자재) 1123 + 종속사 510 + 연결조정 -319
+        <t>추정: 별도(조선기자재) 1123 + 종속사 509 + 연결조정 -318
 [identity]</t>
       </text>
     </comment>
@@ -4473,19 +4473,19 @@
     </comment>
     <comment ref="AD41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 353억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 354억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AF41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 248억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 249억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AG41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 277억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 278억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
@@ -4509,19 +4509,19 @@
     </comment>
     <comment ref="AL41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 337억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 336억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AM41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 366억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 365억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
     <comment ref="AN41" authorId="0" shapeId="0">
       <text>
-        <t>추정: 종속사 매출 510억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
+        <t>추정: 종속사 매출 509억 × 잔차/종속사 매출 최근 4분기(2025Q3~2026Q2) 중위 -0.6252(내부거래·베트남)
 [ratio]</t>
       </text>
     </comment>
@@ -4989,7 +4989,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-19</t>
+          <t>기준 분기 2026Q2 · 마지막 실적 2026Q2 · 생성 2026-10-26</t>
         </is>
       </c>
     </row>
@@ -5860,35 +5860,35 @@
         <v>1418.75</v>
       </c>
       <c r="AD6" s="16" t="n">
-        <v>1342.11</v>
+        <v>1337.49</v>
       </c>
       <c r="AE6" s="17" t="n">
-        <v>1454.27</v>
+        <v>1451.19</v>
       </c>
       <c r="AF6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ6" s="11" t="n"/>
       <c r="AK6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN6" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO6" s="11" t="n"/>
     </row>
@@ -5979,35 +5979,35 @@
         <v>1355.4</v>
       </c>
       <c r="AD7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AE7" s="17" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AF7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AG7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AH7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AI7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AJ7" s="11" t="n"/>
       <c r="AK7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AL7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AM7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AN7" s="16" t="n">
-        <v>1332.1</v>
+        <v>1324.45</v>
       </c>
       <c r="AO7" s="11" t="n"/>
     </row>
@@ -6098,35 +6098,35 @@
         <v>890.41</v>
       </c>
       <c r="AD8" s="16" t="n">
-        <v>848.59</v>
+        <v>846.51</v>
       </c>
       <c r="AE8" s="17" t="n">
-        <v>917.39</v>
+        <v>915.5700000000001</v>
       </c>
       <c r="AF8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ8" s="11" t="n"/>
       <c r="AK8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN8" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO8" s="11" t="n"/>
     </row>
@@ -6217,35 +6217,35 @@
         <v>863.3099999999999</v>
       </c>
       <c r="AD9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AE9" s="17" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AF9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AG9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AH9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AI9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AJ9" s="11" t="n"/>
       <c r="AK9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AL9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AM9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AN9" s="16" t="n">
-        <v>842.99</v>
+        <v>844.67</v>
       </c>
       <c r="AO9" s="11" t="n"/>
     </row>
@@ -6336,35 +6336,35 @@
         <v>1631.97</v>
       </c>
       <c r="AD10" s="16" t="n">
-        <v>1505.3</v>
+        <v>1500.06</v>
       </c>
       <c r="AE10" s="17" t="n">
-        <v>1685.25</v>
+        <v>1680.5</v>
       </c>
       <c r="AF10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ10" s="11" t="n"/>
       <c r="AK10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN10" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO10" s="11" t="n"/>
     </row>
@@ -6455,35 +6455,35 @@
         <v>1539.06</v>
       </c>
       <c r="AD11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AE11" s="17" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AF11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AG11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AH11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AI11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AJ11" s="11" t="n"/>
       <c r="AK11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AL11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AM11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AN11" s="16" t="n">
-        <v>1499.02</v>
+        <v>1482.45</v>
       </c>
       <c r="AO11" s="11" t="n"/>
     </row>
@@ -6574,35 +6574,35 @@
         <v>210.43</v>
       </c>
       <c r="AD12" s="16" t="n">
-        <v>200.38</v>
+        <v>199.88</v>
       </c>
       <c r="AE12" s="17" t="n">
-        <v>213.41</v>
+        <v>213.06</v>
       </c>
       <c r="AF12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ12" s="11" t="n"/>
       <c r="AK12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN12" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO12" s="11" t="n"/>
     </row>
@@ -6693,35 +6693,35 @@
         <v>202.16</v>
       </c>
       <c r="AD13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AE13" s="17" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AF13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AG13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AH13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AI13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AJ13" s="11" t="n"/>
       <c r="AK13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AL13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AM13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AN13" s="16" t="n">
-        <v>199.23</v>
+        <v>198.56</v>
       </c>
       <c r="AO13" s="11" t="n"/>
     </row>
@@ -6828,7 +6828,7 @@
         <v>9770</v>
       </c>
       <c r="AD15" s="20" t="n">
-        <v>8410</v>
+        <v>7180</v>
       </c>
       <c r="AE15" s="11" t="n"/>
       <c r="AF15" s="10" t="n"/>
@@ -7010,7 +7010,7 @@
         <v>8500</v>
       </c>
       <c r="AD17" s="20" t="n">
-        <v>7830</v>
+        <v>7130</v>
       </c>
       <c r="AE17" s="11" t="n"/>
       <c r="AF17" s="10" t="n"/>
@@ -7101,7 +7101,7 @@
         <v>10929</v>
       </c>
       <c r="AD18" s="20" t="n">
-        <v>9064.5</v>
+        <v>8625.6</v>
       </c>
       <c r="AE18" s="11" t="n"/>
       <c r="AF18" s="10" t="n"/>
@@ -8485,36 +8485,36 @@
         <v/>
       </c>
       <c r="AC29" s="29" t="n">
-        <v>-0.00385175</v>
+        <v>-0.004461673</v>
       </c>
       <c r="AD29" s="29" t="n">
-        <v>0.008790164</v>
+        <v>0.012229656</v>
       </c>
       <c r="AE29" s="30" t="n"/>
       <c r="AF29" s="29" t="n">
-        <v>0.004158579</v>
+        <v>-0.002146131</v>
       </c>
       <c r="AG29" s="29" t="n">
-        <v>127.907720771</v>
+        <v>127.911551192</v>
       </c>
       <c r="AH29" s="29" t="n">
-        <v>0.007815545</v>
+        <v>-0.008200541</v>
       </c>
       <c r="AI29" s="29" t="n">
-        <v>0.005345672</v>
+        <v>0.005132979</v>
       </c>
       <c r="AJ29" s="30" t="n"/>
       <c r="AK29" s="29" t="n">
-        <v>-0.009071355</v>
+        <v>-0.005422788</v>
       </c>
       <c r="AL29" s="29" t="n">
-        <v>127.922093923</v>
+        <v>127.9213149</v>
       </c>
       <c r="AM29" s="29" t="n">
-        <v>-0.003147549</v>
+        <v>-0.002302191</v>
       </c>
       <c r="AN29" s="29" t="n">
-        <v>-0.003176859</v>
+        <v>0.000893715</v>
       </c>
       <c r="AO29" s="30" t="n"/>
     </row>
@@ -8613,36 +8613,36 @@
         <v/>
       </c>
       <c r="AC30" s="29" t="n">
-        <v>-0.005819443</v>
+        <v>-0.007382348</v>
       </c>
       <c r="AD30" s="29" t="n">
-        <v>0.009057823</v>
+        <v>0.006859138</v>
       </c>
       <c r="AE30" s="30" t="n"/>
       <c r="AF30" s="29" t="n">
-        <v>-0.003759749</v>
+        <v>0.004663727</v>
       </c>
       <c r="AG30" s="29" t="n">
-        <v>127.918023299</v>
+        <v>127.906469909</v>
       </c>
       <c r="AH30" s="29" t="n">
-        <v>-0.004532538</v>
+        <v>-0.005946065</v>
       </c>
       <c r="AI30" s="29" t="n">
-        <v>0.009487508</v>
+        <v>-0.002218465</v>
       </c>
       <c r="AJ30" s="30" t="n"/>
       <c r="AK30" s="29" t="n">
-        <v>-0.007085141</v>
+        <v>-0.001631044</v>
       </c>
       <c r="AL30" s="29" t="n">
-        <v>127.919438226</v>
+        <v>127.914723274</v>
       </c>
       <c r="AM30" s="29" t="n">
-        <v>-0.000766075</v>
+        <v>-0.002348511</v>
       </c>
       <c r="AN30" s="29" t="n">
-        <v>0.003332192</v>
+        <v>-0.002459876</v>
       </c>
       <c r="AO30" s="30" t="n"/>
     </row>
@@ -8872,33 +8872,33 @@
         <v>-0.078038257</v>
       </c>
       <c r="AD32" s="32" t="n">
-        <v>-0.116386325</v>
+        <v>-0.116400919</v>
       </c>
       <c r="AE32" s="25" t="n"/>
       <c r="AF32" s="32" t="n">
-        <v>-0.094552632</v>
+        <v>-0.09457897</v>
       </c>
       <c r="AG32" s="32" t="n">
-        <v>0.003475104</v>
+        <v>0.00345702</v>
       </c>
       <c r="AH32" s="32" t="n">
-        <v>-0.111427221</v>
+        <v>-0.111461581</v>
       </c>
       <c r="AI32" s="32" t="n">
-        <v>-0.171104451</v>
+        <v>-0.171132185</v>
       </c>
       <c r="AJ32" s="25" t="n"/>
       <c r="AK32" s="32" t="n">
-        <v>-0.149545858</v>
+        <v>-0.149541477</v>
       </c>
       <c r="AL32" s="32" t="n">
-        <v>-0.005383521</v>
+        <v>-0.005326174</v>
       </c>
       <c r="AM32" s="32" t="n">
-        <v>-0.189632785</v>
+        <v>-0.189573667</v>
       </c>
       <c r="AN32" s="32" t="n">
-        <v>-0.31758034</v>
+        <v>-0.31747232</v>
       </c>
       <c r="AO32" s="25" t="n"/>
     </row>
@@ -9000,33 +9000,33 @@
         <v>0.083679367</v>
       </c>
       <c r="AD33" s="32" t="n">
-        <v>0.106178017</v>
+        <v>0.106191332</v>
       </c>
       <c r="AE33" s="25" t="n"/>
       <c r="AF33" s="32" t="n">
-        <v>0.068903881</v>
+        <v>0.068921107</v>
       </c>
       <c r="AG33" s="32" t="n">
-        <v>-0.002145174</v>
+        <v>-0.002133853</v>
       </c>
       <c r="AH33" s="32" t="n">
-        <v>0.069171176</v>
+        <v>0.069191013</v>
       </c>
       <c r="AI33" s="32" t="n">
-        <v>0.08828092799999999</v>
+        <v>0.088270527</v>
       </c>
       <c r="AJ33" s="25" t="n"/>
       <c r="AK33" s="32" t="n">
-        <v>0.058759347</v>
+        <v>0.058751649</v>
       </c>
       <c r="AL33" s="32" t="n">
-        <v>0.001703835</v>
+        <v>0.001685445</v>
       </c>
       <c r="AM33" s="32" t="n">
-        <v>0.059427626</v>
+        <v>0.059403405</v>
       </c>
       <c r="AN33" s="32" t="n">
-        <v>0.07613724600000001</v>
+        <v>0.076107035</v>
       </c>
       <c r="AO33" s="25" t="n"/>
     </row>
@@ -9988,33 +9988,33 @@
         <v>-0.010274649</v>
       </c>
       <c r="AD41" s="32" t="n">
-        <v>0.248100371</v>
+        <v>0.249443365</v>
       </c>
       <c r="AE41" s="25" t="n"/>
       <c r="AF41" s="32" t="n">
-        <v>0.16643166</v>
+        <v>0.168687723</v>
       </c>
       <c r="AG41" s="32" t="n">
-        <v>-0.005270895</v>
+        <v>-0.003191222</v>
       </c>
       <c r="AH41" s="32" t="n">
-        <v>0.181193851</v>
+        <v>0.183310042</v>
       </c>
       <c r="AI41" s="32" t="n">
-        <v>0.163414979</v>
+        <v>0.162390745</v>
       </c>
       <c r="AJ41" s="25" t="n"/>
       <c r="AK41" s="32" t="n">
-        <v>0.184228553</v>
+        <v>0.18037402</v>
       </c>
       <c r="AL41" s="32" t="n">
-        <v>0.214151828</v>
+        <v>0.208956835</v>
       </c>
       <c r="AM41" s="32" t="n">
-        <v>0.23858297</v>
+        <v>0.23316237</v>
       </c>
       <c r="AN41" s="32" t="n">
-        <v>0.2412744</v>
+        <v>0.23789361</v>
       </c>
       <c r="AO41" s="25" t="n"/>
     </row>
@@ -10134,39 +10134,39 @@
         <v>0.188141346</v>
       </c>
       <c r="AD42" s="32" t="n">
-        <v>0.188191986</v>
+        <v>0.188187707</v>
       </c>
       <c r="AE42" s="25">
         <f>IFERROR(subQ!AE40/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF42" s="32" t="n">
-        <v>0.188741588</v>
+        <v>0.188698974</v>
       </c>
       <c r="AG42" s="32" t="n">
-        <v>0.188558864</v>
+        <v>0.188597122</v>
       </c>
       <c r="AH42" s="32" t="n">
-        <v>0.188148599</v>
+        <v>0.188149548</v>
       </c>
       <c r="AI42" s="32" t="n">
-        <v>0.188214964</v>
+        <v>0.188202657</v>
       </c>
       <c r="AJ42" s="25">
         <f>IFERROR(subQ!AJ40/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK42" s="32" t="n">
-        <v>0.188710062</v>
+        <v>0.188756388</v>
       </c>
       <c r="AL42" s="32" t="n">
-        <v>0.188581777</v>
+        <v>0.18858044</v>
       </c>
       <c r="AM42" s="32" t="n">
-        <v>0.188149887</v>
+        <v>0.188146446</v>
       </c>
       <c r="AN42" s="32" t="n">
-        <v>0.188219377</v>
+        <v>0.188205229</v>
       </c>
       <c r="AO42" s="25">
         <f>IFERROR(subQ!AO40/subQ!AO39,"")</f>
@@ -10289,39 +10289,39 @@
         <v>-0.625154722</v>
       </c>
       <c r="AD43" s="32" t="n">
-        <v>-0.6251451220000001</v>
+        <v>-0.625152038</v>
       </c>
       <c r="AE43" s="25">
         <f>IFERROR(subQ!AE41/subQ!AE39,"")</f>
         <v/>
       </c>
       <c r="AF43" s="32" t="n">
-        <v>-0.6251359950000001</v>
+        <v>-0.625135733</v>
       </c>
       <c r="AG43" s="32" t="n">
-        <v>-0.625153197</v>
+        <v>-0.625143885</v>
       </c>
       <c r="AH43" s="32" t="n">
-        <v>-0.62515634</v>
+        <v>-0.625151842</v>
       </c>
       <c r="AI43" s="32" t="n">
-        <v>-0.62515212</v>
+        <v>-0.62515209</v>
       </c>
       <c r="AJ43" s="25">
         <f>IFERROR(subQ!AJ41/subQ!AJ39,"")</f>
         <v/>
       </c>
       <c r="AK43" s="32" t="n">
-        <v>-0.625165878</v>
+        <v>-0.6251448040000001</v>
       </c>
       <c r="AL43" s="32" t="n">
-        <v>-0.625152154</v>
+        <v>-0.625159927</v>
       </c>
       <c r="AM43" s="32" t="n">
-        <v>-0.625146694</v>
+        <v>-0.625157336</v>
       </c>
       <c r="AN43" s="32" t="n">
-        <v>-0.625149513</v>
+        <v>-0.625162178</v>
       </c>
       <c r="AO43" s="25">
         <f>IFERROR(subQ!AO41/subQ!AO39,"")</f>
@@ -10444,39 +10444,39 @@
         <v>0.140448362</v>
       </c>
       <c r="AD44" s="32" t="n">
-        <v>0.14381483</v>
+        <v>0.143839645</v>
       </c>
       <c r="AE44" s="25">
         <f>IFERROR(subQ!AE42/subQ!AE41,"")</f>
         <v/>
       </c>
       <c r="AF44" s="32" t="n">
-        <v>0.142645353</v>
+        <v>0.142691714</v>
       </c>
       <c r="AG44" s="32" t="n">
-        <v>0.14501528</v>
+        <v>0.145232752</v>
       </c>
       <c r="AH44" s="32" t="n">
-        <v>0.148913161</v>
+        <v>0.149025746</v>
       </c>
       <c r="AI44" s="32" t="n">
-        <v>0.151099864</v>
+        <v>0.151109381</v>
       </c>
       <c r="AJ44" s="25">
         <f>IFERROR(subQ!AJ42/subQ!AJ41,"")</f>
         <v/>
       </c>
       <c r="AK44" s="32" t="n">
-        <v>0.151036848</v>
+        <v>0.151024635</v>
       </c>
       <c r="AL44" s="32" t="n">
-        <v>0.154247994</v>
+        <v>0.154157346</v>
       </c>
       <c r="AM44" s="32" t="n">
-        <v>0.158473762</v>
+        <v>0.158357771</v>
       </c>
       <c r="AN44" s="32" t="n">
-        <v>0.160372624</v>
+        <v>0.160241494</v>
       </c>
       <c r="AO44" s="25">
         <f>IFERROR(subQ!AO42/subQ!AO41,"")</f>
@@ -10547,11 +10547,11 @@
         </is>
       </c>
       <c r="D47" s="34" t="n">
-        <v>8410</v>
+        <v>7180</v>
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,960원)</t>
+          <t>원 — 네이버 정규장 종가(aik 확정종가 대조 · aik 7,720원)</t>
         </is>
       </c>
       <c r="F47" s="9" t="n"/>
@@ -10587,7 +10587,7 @@
       </c>
       <c r="D48" s="35" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E48" s="2" t="inlineStr">
@@ -10822,7 +10822,7 @@
         </is>
       </c>
       <c r="D54" s="36" t="n">
-        <v>0.1911563132317077</v>
+        <v>0.1911594538301319</v>
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
@@ -10861,7 +10861,7 @@
         </is>
       </c>
       <c r="D55" s="36" t="n">
-        <v>0.06131769525482933</v>
+        <v>0.06131685902238711</v>
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
@@ -10900,7 +10900,7 @@
         </is>
       </c>
       <c r="D56" s="36" t="n">
-        <v>0.8217558119915195</v>
+        <v>0.8217466582542221</v>
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
@@ -10939,7 +10939,7 @@
         </is>
       </c>
       <c r="D57" s="36" t="n">
-        <v>0.03609746561647491</v>
+        <v>0.03609545892439203</v>
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
@@ -10978,7 +10978,7 @@
         </is>
       </c>
       <c r="D58" s="36" t="n">
-        <v>0.03869816405745791</v>
+        <v>0.03869736959401655</v>
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
@@ -11415,7 +11415,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -20963,7 +20963,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>UPDATE: 26-10-19</t>
+          <t>UPDATE: 26-10-26</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -36454,7 +36454,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -42099,7 +42099,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>20261019</t>
+          <t>20261026</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
@@ -44415,7 +44415,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.32</v>
+        <v>9.66</v>
       </c>
     </row>
     <row r="32">
@@ -44425,7 +44425,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1.95</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="33">
